--- a/events.xlsx
+++ b/events.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\cantolaoaqp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FB88639-5E43-4F24-8C66-6C4FA4A94ED7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A85F4F0B-EB85-4E75-A164-F1E033AD3D6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="800" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1474" uniqueCount="515">
   <si>
     <t>XY</t>
   </si>
@@ -890,6 +890,681 @@
   </si>
   <si>
     <t>https://youtu.be/fE4Ma9vXx1w</t>
+  </si>
+  <si>
+    <t>20:26</t>
+  </si>
+  <si>
+    <t>20:34</t>
+  </si>
+  <si>
+    <t>20:42</t>
+  </si>
+  <si>
+    <t>89;32</t>
+  </si>
+  <si>
+    <t>20:47</t>
+  </si>
+  <si>
+    <t>20:51</t>
+  </si>
+  <si>
+    <t>20:54</t>
+  </si>
+  <si>
+    <t>36;18</t>
+  </si>
+  <si>
+    <t>20:52</t>
+  </si>
+  <si>
+    <t>20:56</t>
+  </si>
+  <si>
+    <t>21:00</t>
+  </si>
+  <si>
+    <t>29;40</t>
+  </si>
+  <si>
+    <t>20:59</t>
+  </si>
+  <si>
+    <t>21:02</t>
+  </si>
+  <si>
+    <t>21:05</t>
+  </si>
+  <si>
+    <t>64;39</t>
+  </si>
+  <si>
+    <t>21:04</t>
+  </si>
+  <si>
+    <t>21:13</t>
+  </si>
+  <si>
+    <t>21:22</t>
+  </si>
+  <si>
+    <t>55;51</t>
+  </si>
+  <si>
+    <t>21:26</t>
+  </si>
+  <si>
+    <t>21:38</t>
+  </si>
+  <si>
+    <t>21:50</t>
+  </si>
+  <si>
+    <t>74;56</t>
+  </si>
+  <si>
+    <t>21:49</t>
+  </si>
+  <si>
+    <t>21:55</t>
+  </si>
+  <si>
+    <t>22:02</t>
+  </si>
+  <si>
+    <t>18;12</t>
+  </si>
+  <si>
+    <t>22:10</t>
+  </si>
+  <si>
+    <t>22:19</t>
+  </si>
+  <si>
+    <t>56;32</t>
+  </si>
+  <si>
+    <t>22:18</t>
+  </si>
+  <si>
+    <t>22:22</t>
+  </si>
+  <si>
+    <t>22:27</t>
+  </si>
+  <si>
+    <t>30;70</t>
+  </si>
+  <si>
+    <t>22:37</t>
+  </si>
+  <si>
+    <t>22:45</t>
+  </si>
+  <si>
+    <t>22:52</t>
+  </si>
+  <si>
+    <t>21;75</t>
+  </si>
+  <si>
+    <t>22:51</t>
+  </si>
+  <si>
+    <t>23:00</t>
+  </si>
+  <si>
+    <t>23:08</t>
+  </si>
+  <si>
+    <t>65;13</t>
+  </si>
+  <si>
+    <t>23:11</t>
+  </si>
+  <si>
+    <t>23:16</t>
+  </si>
+  <si>
+    <t>23:21</t>
+  </si>
+  <si>
+    <t>69;89</t>
+  </si>
+  <si>
+    <t>23:29</t>
+  </si>
+  <si>
+    <t>23:34</t>
+  </si>
+  <si>
+    <t>23:40</t>
+  </si>
+  <si>
+    <t>89;66</t>
+  </si>
+  <si>
+    <t>23:59</t>
+  </si>
+  <si>
+    <t>24:02</t>
+  </si>
+  <si>
+    <t>24:05</t>
+  </si>
+  <si>
+    <t>75;82</t>
+  </si>
+  <si>
+    <t>24:04</t>
+  </si>
+  <si>
+    <t>24:10</t>
+  </si>
+  <si>
+    <t>24:15</t>
+  </si>
+  <si>
+    <t>64;44</t>
+  </si>
+  <si>
+    <t>24:32</t>
+  </si>
+  <si>
+    <t>24:36</t>
+  </si>
+  <si>
+    <t>24:41</t>
+  </si>
+  <si>
+    <t>94;46</t>
+  </si>
+  <si>
+    <t>24:38</t>
+  </si>
+  <si>
+    <t>24:46</t>
+  </si>
+  <si>
+    <t>24:54</t>
+  </si>
+  <si>
+    <t>64;28</t>
+  </si>
+  <si>
+    <t>25:12</t>
+  </si>
+  <si>
+    <t>25:21</t>
+  </si>
+  <si>
+    <t>25:30</t>
+  </si>
+  <si>
+    <t>90;87</t>
+  </si>
+  <si>
+    <t>25:35</t>
+  </si>
+  <si>
+    <t>25:40</t>
+  </si>
+  <si>
+    <t>25:45</t>
+  </si>
+  <si>
+    <t>14;53</t>
+  </si>
+  <si>
+    <t>25:51</t>
+  </si>
+  <si>
+    <t>26:04</t>
+  </si>
+  <si>
+    <t>26:17</t>
+  </si>
+  <si>
+    <t>28;8</t>
+  </si>
+  <si>
+    <t>27:05</t>
+  </si>
+  <si>
+    <t>27:14</t>
+  </si>
+  <si>
+    <t>27:24</t>
+  </si>
+  <si>
+    <t>54;47</t>
+  </si>
+  <si>
+    <t>27:43</t>
+  </si>
+  <si>
+    <t>27:50</t>
+  </si>
+  <si>
+    <t>27:57</t>
+  </si>
+  <si>
+    <t>65;9</t>
+  </si>
+  <si>
+    <t>28:00</t>
+  </si>
+  <si>
+    <t>28:06</t>
+  </si>
+  <si>
+    <t>28:12</t>
+  </si>
+  <si>
+    <t>35;51</t>
+  </si>
+  <si>
+    <t>28:17</t>
+  </si>
+  <si>
+    <t>28:21</t>
+  </si>
+  <si>
+    <t>55;90</t>
+  </si>
+  <si>
+    <t>28:22</t>
+  </si>
+  <si>
+    <t>28:26</t>
+  </si>
+  <si>
+    <t>28:30</t>
+  </si>
+  <si>
+    <t>66;39</t>
+  </si>
+  <si>
+    <t>28:33</t>
+  </si>
+  <si>
+    <t>28:41</t>
+  </si>
+  <si>
+    <t>28:49</t>
+  </si>
+  <si>
+    <t>89;71</t>
+  </si>
+  <si>
+    <t>28:47</t>
+  </si>
+  <si>
+    <t>28:51</t>
+  </si>
+  <si>
+    <t>28:54</t>
+  </si>
+  <si>
+    <t>76;52</t>
+  </si>
+  <si>
+    <t>28:52</t>
+  </si>
+  <si>
+    <t>28:57</t>
+  </si>
+  <si>
+    <t>29:01</t>
+  </si>
+  <si>
+    <t>72;77</t>
+  </si>
+  <si>
+    <t>29:18</t>
+  </si>
+  <si>
+    <t>29:27</t>
+  </si>
+  <si>
+    <t>72;17</t>
+  </si>
+  <si>
+    <t>29:22</t>
+  </si>
+  <si>
+    <t>29:28</t>
+  </si>
+  <si>
+    <t>29:33</t>
+  </si>
+  <si>
+    <t>35;69</t>
+  </si>
+  <si>
+    <t>29:30</t>
+  </si>
+  <si>
+    <t>29:34</t>
+  </si>
+  <si>
+    <t>29:37</t>
+  </si>
+  <si>
+    <t>88;91</t>
+  </si>
+  <si>
+    <t>29:45</t>
+  </si>
+  <si>
+    <t>30:00</t>
+  </si>
+  <si>
+    <t>30:16</t>
+  </si>
+  <si>
+    <t>95;86</t>
+  </si>
+  <si>
+    <t>30:37</t>
+  </si>
+  <si>
+    <t>31:01</t>
+  </si>
+  <si>
+    <t>31:26</t>
+  </si>
+  <si>
+    <t>27;85</t>
+  </si>
+  <si>
+    <t>Ocasión rival</t>
+  </si>
+  <si>
+    <t>31:54</t>
+  </si>
+  <si>
+    <t>32:05</t>
+  </si>
+  <si>
+    <t>32:16</t>
+  </si>
+  <si>
+    <t>75;91</t>
+  </si>
+  <si>
+    <t>32:15</t>
+  </si>
+  <si>
+    <t>32:23</t>
+  </si>
+  <si>
+    <t>32:30</t>
+  </si>
+  <si>
+    <t>30;59</t>
+  </si>
+  <si>
+    <t>32:45</t>
+  </si>
+  <si>
+    <t>32:57</t>
+  </si>
+  <si>
+    <t>33:09</t>
+  </si>
+  <si>
+    <t>79;51</t>
+  </si>
+  <si>
+    <t>33:29</t>
+  </si>
+  <si>
+    <t>33:32</t>
+  </si>
+  <si>
+    <t>33:35</t>
+  </si>
+  <si>
+    <t>47;46</t>
+  </si>
+  <si>
+    <t>33:34</t>
+  </si>
+  <si>
+    <t>33:39</t>
+  </si>
+  <si>
+    <t>33:44</t>
+  </si>
+  <si>
+    <t>55;23</t>
+  </si>
+  <si>
+    <t>33:43</t>
+  </si>
+  <si>
+    <t>33:52</t>
+  </si>
+  <si>
+    <t>34:01</t>
+  </si>
+  <si>
+    <t>34:35</t>
+  </si>
+  <si>
+    <t>34:54</t>
+  </si>
+  <si>
+    <t>35:12</t>
+  </si>
+  <si>
+    <t>40;14</t>
+  </si>
+  <si>
+    <t>35:20</t>
+  </si>
+  <si>
+    <t>35:27</t>
+  </si>
+  <si>
+    <t>35:34</t>
+  </si>
+  <si>
+    <t>7;87</t>
+  </si>
+  <si>
+    <t>35:46</t>
+  </si>
+  <si>
+    <t>35:49</t>
+  </si>
+  <si>
+    <t>35:52</t>
+  </si>
+  <si>
+    <t>41;94</t>
+  </si>
+  <si>
+    <t>36:06</t>
+  </si>
+  <si>
+    <t>36:15</t>
+  </si>
+  <si>
+    <t>36:23</t>
+  </si>
+  <si>
+    <t>36;22</t>
+  </si>
+  <si>
+    <t>37:01</t>
+  </si>
+  <si>
+    <t>37:04</t>
+  </si>
+  <si>
+    <t>37:07</t>
+  </si>
+  <si>
+    <t>19;72</t>
+  </si>
+  <si>
+    <t>37:13</t>
+  </si>
+  <si>
+    <t>37:18</t>
+  </si>
+  <si>
+    <t>37:33</t>
+  </si>
+  <si>
+    <t>37:38</t>
+  </si>
+  <si>
+    <t>37:43</t>
+  </si>
+  <si>
+    <t>41;77</t>
+  </si>
+  <si>
+    <t>37:41</t>
+  </si>
+  <si>
+    <t>37:45</t>
+  </si>
+  <si>
+    <t>37:49</t>
+  </si>
+  <si>
+    <t>55;79</t>
+  </si>
+  <si>
+    <t>37:47</t>
+  </si>
+  <si>
+    <t>37:51</t>
+  </si>
+  <si>
+    <t>37:55</t>
+  </si>
+  <si>
+    <t>51;23</t>
+  </si>
+  <si>
+    <t>38:29</t>
+  </si>
+  <si>
+    <t>38:33</t>
+  </si>
+  <si>
+    <t>38:37</t>
+  </si>
+  <si>
+    <t>55;10</t>
+  </si>
+  <si>
+    <t>38:44</t>
+  </si>
+  <si>
+    <t>38:50</t>
+  </si>
+  <si>
+    <t>38:56</t>
+  </si>
+  <si>
+    <t>91;47</t>
+  </si>
+  <si>
+    <t>38:57</t>
+  </si>
+  <si>
+    <t>39:01</t>
+  </si>
+  <si>
+    <t>39:04</t>
+  </si>
+  <si>
+    <t>14;6</t>
+  </si>
+  <si>
+    <t>39:12</t>
+  </si>
+  <si>
+    <t>39:15</t>
+  </si>
+  <si>
+    <t>39:18</t>
+  </si>
+  <si>
+    <t>60;17</t>
+  </si>
+  <si>
+    <t>39:23</t>
+  </si>
+  <si>
+    <t>39:28</t>
+  </si>
+  <si>
+    <t>65;26</t>
+  </si>
+  <si>
+    <t>39:34</t>
+  </si>
+  <si>
+    <t>39:41</t>
+  </si>
+  <si>
+    <t>55;19</t>
+  </si>
+  <si>
+    <t>39:38</t>
+  </si>
+  <si>
+    <t>39:46</t>
+  </si>
+  <si>
+    <t>39:54</t>
+  </si>
+  <si>
+    <t>41;44</t>
+  </si>
+  <si>
+    <t>39:51</t>
+  </si>
+  <si>
+    <t>39:58</t>
+  </si>
+  <si>
+    <t>40:05</t>
+  </si>
+  <si>
+    <t>31;14</t>
+  </si>
+  <si>
+    <t>40:31</t>
+  </si>
+  <si>
+    <t>40:35</t>
+  </si>
+  <si>
+    <t>40:39</t>
+  </si>
+  <si>
+    <t>3;9</t>
+  </si>
+  <si>
+    <t>Corner</t>
+  </si>
+  <si>
+    <t>GOL</t>
+  </si>
+  <si>
+    <t>2T</t>
+  </si>
+  <si>
+    <t>True</t>
   </si>
 </sst>
 </file>
@@ -972,8 +1647,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C1975CA6-E80E-40A4-A9D5-728F867A63BD}" name="Tabla1" displayName="Tabla1" ref="A1:O67" totalsRowShown="0">
-  <autoFilter ref="A1:O67" xr:uid="{C1975CA6-E80E-40A4-A9D5-728F867A63BD}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C1975CA6-E80E-40A4-A9D5-728F867A63BD}" name="Tabla1" displayName="Tabla1" ref="A1:O124" totalsRowShown="0">
+  <autoFilter ref="A1:O124" xr:uid="{C1975CA6-E80E-40A4-A9D5-728F867A63BD}"/>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{45CCCD5A-AFCF-487D-ADA1-0BFBB6505772}" name="Event"/>
     <tableColumn id="2" xr3:uid="{4A939A0F-B787-4665-B94F-35DE80E0B243}" name="start_time" dataDxfId="2"/>
@@ -1282,7 +1957,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77939FC4-FC73-4262-977F-310955BE7B1D}">
-  <dimension ref="A1:O67"/>
+  <dimension ref="A1:O124"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23.5703125" customWidth="1"/>
@@ -3896,6 +4571,2199 @@
         <v>55</v>
       </c>
     </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>14</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="E68" t="s">
+        <v>293</v>
+      </c>
+      <c r="F68" t="s">
+        <v>42</v>
+      </c>
+      <c r="G68" t="s">
+        <v>287</v>
+      </c>
+      <c r="H68" t="s">
+        <v>288</v>
+      </c>
+      <c r="I68" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J68" s="1"/>
+      <c r="M68" t="s">
+        <v>7</v>
+      </c>
+      <c r="N68" t="s">
+        <v>50</v>
+      </c>
+      <c r="O68" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>122</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="E69" t="s">
+        <v>297</v>
+      </c>
+      <c r="F69" t="s">
+        <v>20</v>
+      </c>
+      <c r="G69" t="s">
+        <v>46</v>
+      </c>
+      <c r="H69" t="s">
+        <v>288</v>
+      </c>
+      <c r="I69" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J69" s="1"/>
+      <c r="M69" t="s">
+        <v>7</v>
+      </c>
+      <c r="N69" t="s">
+        <v>50</v>
+      </c>
+      <c r="O69" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>127</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="E70" t="s">
+        <v>301</v>
+      </c>
+      <c r="F70" t="s">
+        <v>43</v>
+      </c>
+      <c r="G70" t="s">
+        <v>47</v>
+      </c>
+      <c r="H70" t="s">
+        <v>288</v>
+      </c>
+      <c r="I70" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J70" s="1"/>
+      <c r="M70" t="s">
+        <v>7</v>
+      </c>
+      <c r="N70" t="s">
+        <v>50</v>
+      </c>
+      <c r="O70" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>122</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="E71" t="s">
+        <v>305</v>
+      </c>
+      <c r="F71" t="s">
+        <v>20</v>
+      </c>
+      <c r="G71" t="s">
+        <v>46</v>
+      </c>
+      <c r="H71" t="s">
+        <v>288</v>
+      </c>
+      <c r="I71" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J71" s="1"/>
+      <c r="M71" t="s">
+        <v>7</v>
+      </c>
+      <c r="N71" t="s">
+        <v>50</v>
+      </c>
+      <c r="O71" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
+        <v>127</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="E72" t="s">
+        <v>309</v>
+      </c>
+      <c r="F72" t="s">
+        <v>43</v>
+      </c>
+      <c r="G72" t="s">
+        <v>45</v>
+      </c>
+      <c r="H72" t="s">
+        <v>288</v>
+      </c>
+      <c r="I72" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J72" s="1"/>
+      <c r="M72" t="s">
+        <v>7</v>
+      </c>
+      <c r="N72" t="s">
+        <v>50</v>
+      </c>
+      <c r="O72" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
+        <v>122</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="E73" t="s">
+        <v>313</v>
+      </c>
+      <c r="F73" t="s">
+        <v>20</v>
+      </c>
+      <c r="G73" t="s">
+        <v>287</v>
+      </c>
+      <c r="H73" t="s">
+        <v>288</v>
+      </c>
+      <c r="I73" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J73" s="1"/>
+      <c r="M73" t="s">
+        <v>7</v>
+      </c>
+      <c r="N73" t="s">
+        <v>50</v>
+      </c>
+      <c r="O73" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>127</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="E74" t="s">
+        <v>317</v>
+      </c>
+      <c r="F74" t="s">
+        <v>1</v>
+      </c>
+      <c r="G74" t="s">
+        <v>47</v>
+      </c>
+      <c r="H74" t="s">
+        <v>288</v>
+      </c>
+      <c r="I74" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J74" s="1"/>
+      <c r="M74" t="s">
+        <v>7</v>
+      </c>
+      <c r="N74" t="s">
+        <v>50</v>
+      </c>
+      <c r="O74" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
+        <v>122</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="E75" t="s">
+        <v>320</v>
+      </c>
+      <c r="F75" t="s">
+        <v>20</v>
+      </c>
+      <c r="G75" t="s">
+        <v>46</v>
+      </c>
+      <c r="H75" t="s">
+        <v>288</v>
+      </c>
+      <c r="I75" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J75" s="1"/>
+      <c r="M75" t="s">
+        <v>7</v>
+      </c>
+      <c r="N75" t="s">
+        <v>50</v>
+      </c>
+      <c r="O75" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
+        <v>127</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="E76" t="s">
+        <v>324</v>
+      </c>
+      <c r="F76" t="s">
+        <v>43</v>
+      </c>
+      <c r="G76" t="s">
+        <v>45</v>
+      </c>
+      <c r="H76" t="s">
+        <v>288</v>
+      </c>
+      <c r="I76" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J76" s="1"/>
+      <c r="M76" t="s">
+        <v>7</v>
+      </c>
+      <c r="N76" t="s">
+        <v>50</v>
+      </c>
+      <c r="O76" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
+        <v>2</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="E77" t="s">
+        <v>328</v>
+      </c>
+      <c r="F77" t="s">
+        <v>3</v>
+      </c>
+      <c r="G77" t="s">
+        <v>47</v>
+      </c>
+      <c r="H77" t="s">
+        <v>288</v>
+      </c>
+      <c r="I77" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J77" s="1"/>
+      <c r="M77" t="s">
+        <v>7</v>
+      </c>
+      <c r="N77" t="s">
+        <v>50</v>
+      </c>
+      <c r="O77" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
+        <v>122</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="E78" t="s">
+        <v>332</v>
+      </c>
+      <c r="F78" t="s">
+        <v>20</v>
+      </c>
+      <c r="G78" t="s">
+        <v>48</v>
+      </c>
+      <c r="H78" t="s">
+        <v>288</v>
+      </c>
+      <c r="I78" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J78" s="1"/>
+      <c r="M78" t="s">
+        <v>7</v>
+      </c>
+      <c r="N78" t="s">
+        <v>50</v>
+      </c>
+      <c r="O78" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A79" t="s">
+        <v>14</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="E79" t="s">
+        <v>336</v>
+      </c>
+      <c r="F79" t="s">
+        <v>42</v>
+      </c>
+      <c r="G79" t="s">
+        <v>48</v>
+      </c>
+      <c r="H79" t="s">
+        <v>288</v>
+      </c>
+      <c r="I79" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J79" s="1"/>
+      <c r="M79" t="s">
+        <v>7</v>
+      </c>
+      <c r="N79" t="s">
+        <v>50</v>
+      </c>
+      <c r="O79" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A80" t="s">
+        <v>14</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="E80" t="s">
+        <v>340</v>
+      </c>
+      <c r="F80" t="s">
+        <v>20</v>
+      </c>
+      <c r="G80" t="s">
+        <v>48</v>
+      </c>
+      <c r="H80" t="s">
+        <v>288</v>
+      </c>
+      <c r="I80" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J80" s="1"/>
+      <c r="M80" t="s">
+        <v>7</v>
+      </c>
+      <c r="N80" t="s">
+        <v>50</v>
+      </c>
+      <c r="O80" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A81" t="s">
+        <v>27</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="E81" t="s">
+        <v>344</v>
+      </c>
+      <c r="F81" t="s">
+        <v>15</v>
+      </c>
+      <c r="H81" t="s">
+        <v>288</v>
+      </c>
+      <c r="I81" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J81" s="1"/>
+      <c r="M81" t="s">
+        <v>7</v>
+      </c>
+      <c r="N81" t="s">
+        <v>50</v>
+      </c>
+      <c r="O81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A82" t="s">
+        <v>127</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="E82" t="s">
+        <v>348</v>
+      </c>
+      <c r="F82" t="s">
+        <v>45</v>
+      </c>
+      <c r="G82" t="s">
+        <v>43</v>
+      </c>
+      <c r="H82" t="s">
+        <v>288</v>
+      </c>
+      <c r="I82" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J82" s="1"/>
+      <c r="M82" t="s">
+        <v>7</v>
+      </c>
+      <c r="N82" t="s">
+        <v>50</v>
+      </c>
+      <c r="O82" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A83" t="s">
+        <v>14</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="E83" t="s">
+        <v>352</v>
+      </c>
+      <c r="G83" t="s">
+        <v>46</v>
+      </c>
+      <c r="H83" t="s">
+        <v>288</v>
+      </c>
+      <c r="I83" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J83" s="1"/>
+      <c r="M83" t="s">
+        <v>7</v>
+      </c>
+      <c r="N83" t="s">
+        <v>50</v>
+      </c>
+      <c r="O83" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A84" t="s">
+        <v>127</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E84" t="s">
+        <v>356</v>
+      </c>
+      <c r="F84" t="s">
+        <v>43</v>
+      </c>
+      <c r="G84" t="s">
+        <v>49</v>
+      </c>
+      <c r="H84" t="s">
+        <v>288</v>
+      </c>
+      <c r="I84" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J84" s="1"/>
+      <c r="M84" t="s">
+        <v>7</v>
+      </c>
+      <c r="N84" t="s">
+        <v>50</v>
+      </c>
+      <c r="O84" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A85" t="s">
+        <v>14</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="E85" t="s">
+        <v>360</v>
+      </c>
+      <c r="F85" t="s">
+        <v>20</v>
+      </c>
+      <c r="G85" t="s">
+        <v>287</v>
+      </c>
+      <c r="H85" t="s">
+        <v>288</v>
+      </c>
+      <c r="I85" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J85" s="1"/>
+      <c r="M85" t="s">
+        <v>7</v>
+      </c>
+      <c r="N85" t="s">
+        <v>50</v>
+      </c>
+      <c r="O85" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A86" t="s">
+        <v>2</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="E86" t="s">
+        <v>364</v>
+      </c>
+      <c r="F86" t="s">
+        <v>17</v>
+      </c>
+      <c r="G86" t="s">
+        <v>44</v>
+      </c>
+      <c r="H86" t="s">
+        <v>288</v>
+      </c>
+      <c r="I86" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J86" s="1"/>
+      <c r="M86" t="s">
+        <v>7</v>
+      </c>
+      <c r="N86" t="s">
+        <v>50</v>
+      </c>
+      <c r="O86" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A87" t="s">
+        <v>2</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="E87" t="s">
+        <v>368</v>
+      </c>
+      <c r="F87" t="s">
+        <v>18</v>
+      </c>
+      <c r="G87" t="s">
+        <v>49</v>
+      </c>
+      <c r="H87" t="s">
+        <v>288</v>
+      </c>
+      <c r="I87" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J87" s="1"/>
+      <c r="M87" t="s">
+        <v>7</v>
+      </c>
+      <c r="N87" t="s">
+        <v>50</v>
+      </c>
+      <c r="O87" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A88" t="s">
+        <v>14</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="E88" t="s">
+        <v>372</v>
+      </c>
+      <c r="F88" t="s">
+        <v>42</v>
+      </c>
+      <c r="G88" t="s">
+        <v>48</v>
+      </c>
+      <c r="H88" t="s">
+        <v>288</v>
+      </c>
+      <c r="I88" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J88" s="1"/>
+      <c r="M88" t="s">
+        <v>7</v>
+      </c>
+      <c r="N88" t="s">
+        <v>50</v>
+      </c>
+      <c r="O88" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A89" t="s">
+        <v>14</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="E89" t="s">
+        <v>376</v>
+      </c>
+      <c r="F89" t="s">
+        <v>42</v>
+      </c>
+      <c r="G89" t="s">
+        <v>46</v>
+      </c>
+      <c r="H89" t="s">
+        <v>288</v>
+      </c>
+      <c r="I89" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J89" s="1"/>
+      <c r="M89" t="s">
+        <v>7</v>
+      </c>
+      <c r="N89" t="s">
+        <v>50</v>
+      </c>
+      <c r="O89" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A90" t="s">
+        <v>127</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="E90" t="s">
+        <v>380</v>
+      </c>
+      <c r="F90" t="s">
+        <v>43</v>
+      </c>
+      <c r="G90" t="s">
+        <v>47</v>
+      </c>
+      <c r="H90" t="s">
+        <v>288</v>
+      </c>
+      <c r="I90" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J90" s="1"/>
+      <c r="M90" t="s">
+        <v>7</v>
+      </c>
+      <c r="N90" t="s">
+        <v>50</v>
+      </c>
+      <c r="O90" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A91" t="s">
+        <v>127</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="E91" t="s">
+        <v>383</v>
+      </c>
+      <c r="F91" t="s">
+        <v>43</v>
+      </c>
+      <c r="G91" t="s">
+        <v>47</v>
+      </c>
+      <c r="H91" t="s">
+        <v>288</v>
+      </c>
+      <c r="I91" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J91" s="1"/>
+      <c r="M91" t="s">
+        <v>7</v>
+      </c>
+      <c r="N91" t="s">
+        <v>50</v>
+      </c>
+      <c r="O91" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A92" t="s">
+        <v>127</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="E92" t="s">
+        <v>387</v>
+      </c>
+      <c r="F92" t="s">
+        <v>43</v>
+      </c>
+      <c r="G92" t="s">
+        <v>47</v>
+      </c>
+      <c r="H92" t="s">
+        <v>288</v>
+      </c>
+      <c r="I92" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J92" s="1"/>
+      <c r="M92" t="s">
+        <v>7</v>
+      </c>
+      <c r="N92" t="s">
+        <v>50</v>
+      </c>
+      <c r="O92" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A93" t="s">
+        <v>14</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="E93" t="s">
+        <v>391</v>
+      </c>
+      <c r="F93" t="s">
+        <v>42</v>
+      </c>
+      <c r="G93" t="s">
+        <v>46</v>
+      </c>
+      <c r="H93" t="s">
+        <v>288</v>
+      </c>
+      <c r="I93" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J93" s="1"/>
+      <c r="M93" t="s">
+        <v>7</v>
+      </c>
+      <c r="N93" t="s">
+        <v>50</v>
+      </c>
+      <c r="O93" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A94" t="s">
+        <v>127</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="E94" t="s">
+        <v>395</v>
+      </c>
+      <c r="F94" t="s">
+        <v>43</v>
+      </c>
+      <c r="G94" t="s">
+        <v>47</v>
+      </c>
+      <c r="H94" t="s">
+        <v>288</v>
+      </c>
+      <c r="I94" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J94" s="1"/>
+      <c r="M94" t="s">
+        <v>7</v>
+      </c>
+      <c r="N94" t="s">
+        <v>50</v>
+      </c>
+      <c r="O94" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A95" t="s">
+        <v>122</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="E95" t="s">
+        <v>399</v>
+      </c>
+      <c r="F95" t="s">
+        <v>20</v>
+      </c>
+      <c r="G95" t="s">
+        <v>46</v>
+      </c>
+      <c r="H95" t="s">
+        <v>288</v>
+      </c>
+      <c r="I95" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J95" s="1"/>
+      <c r="M95" t="s">
+        <v>7</v>
+      </c>
+      <c r="N95" t="s">
+        <v>50</v>
+      </c>
+      <c r="O95" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A96" t="s">
+        <v>127</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="E96" t="s">
+        <v>402</v>
+      </c>
+      <c r="F96" t="s">
+        <v>1</v>
+      </c>
+      <c r="G96" t="s">
+        <v>44</v>
+      </c>
+      <c r="H96" t="s">
+        <v>288</v>
+      </c>
+      <c r="I96" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J96" s="1"/>
+      <c r="M96" t="s">
+        <v>7</v>
+      </c>
+      <c r="N96" t="s">
+        <v>50</v>
+      </c>
+      <c r="O96" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A97" t="s">
+        <v>2</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="E97" t="s">
+        <v>406</v>
+      </c>
+      <c r="F97" t="s">
+        <v>3</v>
+      </c>
+      <c r="G97" t="s">
+        <v>47</v>
+      </c>
+      <c r="H97" t="s">
+        <v>288</v>
+      </c>
+      <c r="I97" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J97" s="1"/>
+      <c r="M97" t="s">
+        <v>7</v>
+      </c>
+      <c r="N97" t="s">
+        <v>50</v>
+      </c>
+      <c r="O97" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="98" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A98" t="s">
+        <v>122</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="E98" t="s">
+        <v>410</v>
+      </c>
+      <c r="F98" t="s">
+        <v>20</v>
+      </c>
+      <c r="G98" t="s">
+        <v>48</v>
+      </c>
+      <c r="H98" t="s">
+        <v>288</v>
+      </c>
+      <c r="I98" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J98" s="1"/>
+      <c r="M98" t="s">
+        <v>7</v>
+      </c>
+      <c r="N98" t="s">
+        <v>50</v>
+      </c>
+      <c r="O98" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A99" t="s">
+        <v>14</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="E99" t="s">
+        <v>414</v>
+      </c>
+      <c r="F99" t="s">
+        <v>42</v>
+      </c>
+      <c r="H99" t="s">
+        <v>288</v>
+      </c>
+      <c r="I99" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J99" s="1"/>
+      <c r="M99" t="s">
+        <v>7</v>
+      </c>
+      <c r="N99" t="s">
+        <v>50</v>
+      </c>
+      <c r="O99" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A100" t="s">
+        <v>14</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="E100" t="s">
+        <v>418</v>
+      </c>
+      <c r="F100" t="s">
+        <v>42</v>
+      </c>
+      <c r="G100" t="s">
+        <v>419</v>
+      </c>
+      <c r="H100" t="s">
+        <v>288</v>
+      </c>
+      <c r="I100" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J100" s="1"/>
+      <c r="L100" t="s">
+        <v>512</v>
+      </c>
+      <c r="M100" t="s">
+        <v>513</v>
+      </c>
+      <c r="N100" t="s">
+        <v>514</v>
+      </c>
+      <c r="O100" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="101" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A101" t="s">
+        <v>2</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="E101" t="s">
+        <v>423</v>
+      </c>
+      <c r="F101" t="s">
+        <v>17</v>
+      </c>
+      <c r="G101" t="s">
+        <v>45</v>
+      </c>
+      <c r="H101" t="s">
+        <v>288</v>
+      </c>
+      <c r="I101" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J101" s="1"/>
+      <c r="M101" t="s">
+        <v>513</v>
+      </c>
+      <c r="N101" t="s">
+        <v>514</v>
+      </c>
+      <c r="O101" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="102" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A102" t="s">
+        <v>122</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="E102" t="s">
+        <v>427</v>
+      </c>
+      <c r="F102" t="s">
+        <v>21</v>
+      </c>
+      <c r="G102" t="s">
+        <v>287</v>
+      </c>
+      <c r="H102" t="s">
+        <v>288</v>
+      </c>
+      <c r="I102" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J102" s="1"/>
+      <c r="M102" t="s">
+        <v>513</v>
+      </c>
+      <c r="N102" t="s">
+        <v>514</v>
+      </c>
+      <c r="O102" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="103" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A103" t="s">
+        <v>2</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="E103" t="s">
+        <v>431</v>
+      </c>
+      <c r="F103" t="s">
+        <v>17</v>
+      </c>
+      <c r="G103" t="s">
+        <v>49</v>
+      </c>
+      <c r="H103" t="s">
+        <v>288</v>
+      </c>
+      <c r="I103" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J103" s="1"/>
+      <c r="M103" t="s">
+        <v>513</v>
+      </c>
+      <c r="N103" t="s">
+        <v>514</v>
+      </c>
+      <c r="O103" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="104" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A104" t="s">
+        <v>14</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E104" t="s">
+        <v>435</v>
+      </c>
+      <c r="G104" t="s">
+        <v>46</v>
+      </c>
+      <c r="H104" t="s">
+        <v>288</v>
+      </c>
+      <c r="I104" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J104" s="1"/>
+      <c r="M104" t="s">
+        <v>513</v>
+      </c>
+      <c r="N104" t="s">
+        <v>514</v>
+      </c>
+      <c r="O104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="105" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A105" t="s">
+        <v>127</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="D105" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="E105" t="s">
+        <v>439</v>
+      </c>
+      <c r="F105" t="s">
+        <v>43</v>
+      </c>
+      <c r="G105" t="s">
+        <v>45</v>
+      </c>
+      <c r="H105" t="s">
+        <v>288</v>
+      </c>
+      <c r="I105" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J105" s="1"/>
+      <c r="M105" t="s">
+        <v>513</v>
+      </c>
+      <c r="N105" t="s">
+        <v>514</v>
+      </c>
+      <c r="O105" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="106" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A106" t="s">
+        <v>122</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="D106" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="F106" t="s">
+        <v>20</v>
+      </c>
+      <c r="G106" t="s">
+        <v>287</v>
+      </c>
+      <c r="H106" t="s">
+        <v>288</v>
+      </c>
+      <c r="I106" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J106" s="1"/>
+      <c r="M106" t="s">
+        <v>513</v>
+      </c>
+      <c r="N106" t="s">
+        <v>514</v>
+      </c>
+      <c r="O106" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="107" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A107" t="s">
+        <v>2</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="D107" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="E107" t="s">
+        <v>446</v>
+      </c>
+      <c r="F107" t="s">
+        <v>17</v>
+      </c>
+      <c r="G107" t="s">
+        <v>45</v>
+      </c>
+      <c r="H107" t="s">
+        <v>288</v>
+      </c>
+      <c r="I107" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J107" s="1"/>
+      <c r="M107" t="s">
+        <v>513</v>
+      </c>
+      <c r="N107" t="s">
+        <v>514</v>
+      </c>
+      <c r="O107" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="108" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A108" t="s">
+        <v>14</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="D108" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="E108" t="s">
+        <v>450</v>
+      </c>
+      <c r="F108" t="s">
+        <v>20</v>
+      </c>
+      <c r="G108" t="s">
+        <v>48</v>
+      </c>
+      <c r="H108" t="s">
+        <v>288</v>
+      </c>
+      <c r="I108" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J108" s="1"/>
+      <c r="M108" t="s">
+        <v>513</v>
+      </c>
+      <c r="N108" t="s">
+        <v>514</v>
+      </c>
+      <c r="O108" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="109" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A109" t="s">
+        <v>14</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="D109" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="E109" t="s">
+        <v>454</v>
+      </c>
+      <c r="G109" t="s">
+        <v>46</v>
+      </c>
+      <c r="H109" t="s">
+        <v>288</v>
+      </c>
+      <c r="I109" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J109" s="1"/>
+      <c r="M109" t="s">
+        <v>513</v>
+      </c>
+      <c r="N109" t="s">
+        <v>514</v>
+      </c>
+      <c r="O109" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A110" t="s">
+        <v>2</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="D110" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="E110" t="s">
+        <v>458</v>
+      </c>
+      <c r="F110" t="s">
+        <v>17</v>
+      </c>
+      <c r="G110" t="s">
+        <v>45</v>
+      </c>
+      <c r="H110" t="s">
+        <v>288</v>
+      </c>
+      <c r="I110" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J110" s="1"/>
+      <c r="M110" t="s">
+        <v>513</v>
+      </c>
+      <c r="N110" t="s">
+        <v>514</v>
+      </c>
+      <c r="O110" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="111" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A111" t="s">
+        <v>32</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="E111" t="s">
+        <v>462</v>
+      </c>
+      <c r="F111" t="s">
+        <v>4</v>
+      </c>
+      <c r="H111" t="s">
+        <v>288</v>
+      </c>
+      <c r="I111" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J111" s="1"/>
+      <c r="M111" t="s">
+        <v>513</v>
+      </c>
+      <c r="N111" t="s">
+        <v>514</v>
+      </c>
+      <c r="O111" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="112" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A112" t="s">
+        <v>127</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="D112" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="F112" t="s">
+        <v>43</v>
+      </c>
+      <c r="G112" t="s">
+        <v>49</v>
+      </c>
+      <c r="H112" t="s">
+        <v>288</v>
+      </c>
+      <c r="I112" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J112" s="1"/>
+      <c r="M112" t="s">
+        <v>513</v>
+      </c>
+      <c r="N112" t="s">
+        <v>514</v>
+      </c>
+      <c r="O112" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="113" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A113" t="s">
+        <v>14</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="D113" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="E113" t="s">
+        <v>468</v>
+      </c>
+      <c r="F113" t="s">
+        <v>20</v>
+      </c>
+      <c r="G113" t="s">
+        <v>46</v>
+      </c>
+      <c r="H113" t="s">
+        <v>288</v>
+      </c>
+      <c r="I113" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J113" s="1"/>
+      <c r="M113" t="s">
+        <v>513</v>
+      </c>
+      <c r="N113" t="s">
+        <v>514</v>
+      </c>
+      <c r="O113" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="114" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A114" t="s">
+        <v>127</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="D114" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="E114" t="s">
+        <v>472</v>
+      </c>
+      <c r="F114" t="s">
+        <v>43</v>
+      </c>
+      <c r="G114" t="s">
+        <v>47</v>
+      </c>
+      <c r="H114" t="s">
+        <v>288</v>
+      </c>
+      <c r="I114" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J114" s="1"/>
+      <c r="M114" t="s">
+        <v>513</v>
+      </c>
+      <c r="N114" t="s">
+        <v>514</v>
+      </c>
+      <c r="O114" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="115" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A115" t="s">
+        <v>122</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="D115" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="E115" t="s">
+        <v>476</v>
+      </c>
+      <c r="F115" t="s">
+        <v>20</v>
+      </c>
+      <c r="G115" t="s">
+        <v>48</v>
+      </c>
+      <c r="H115" t="s">
+        <v>288</v>
+      </c>
+      <c r="I115" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J115" s="1"/>
+      <c r="M115" t="s">
+        <v>513</v>
+      </c>
+      <c r="N115" t="s">
+        <v>514</v>
+      </c>
+      <c r="O115" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="116" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A116" t="s">
+        <v>27</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="D116" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="E116" t="s">
+        <v>480</v>
+      </c>
+      <c r="F116" t="s">
+        <v>15</v>
+      </c>
+      <c r="H116" t="s">
+        <v>288</v>
+      </c>
+      <c r="I116" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J116" s="1"/>
+      <c r="M116" t="s">
+        <v>513</v>
+      </c>
+      <c r="N116" t="s">
+        <v>514</v>
+      </c>
+      <c r="O116" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="117" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A117" t="s">
+        <v>2</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="D117" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="E117" t="s">
+        <v>484</v>
+      </c>
+      <c r="F117" t="s">
+        <v>3</v>
+      </c>
+      <c r="G117" t="s">
+        <v>45</v>
+      </c>
+      <c r="H117" t="s">
+        <v>288</v>
+      </c>
+      <c r="I117" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J117" s="1"/>
+      <c r="M117" t="s">
+        <v>513</v>
+      </c>
+      <c r="N117" t="s">
+        <v>514</v>
+      </c>
+      <c r="O117" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="118" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A118" t="s">
+        <v>122</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="C118" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="D118" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="E118" t="s">
+        <v>488</v>
+      </c>
+      <c r="F118" t="s">
+        <v>20</v>
+      </c>
+      <c r="G118" t="s">
+        <v>48</v>
+      </c>
+      <c r="H118" t="s">
+        <v>288</v>
+      </c>
+      <c r="I118" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J118" s="1"/>
+      <c r="M118" t="s">
+        <v>513</v>
+      </c>
+      <c r="N118" t="s">
+        <v>514</v>
+      </c>
+      <c r="O118" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="119" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A119" t="s">
+        <v>14</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="C119" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="D119" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="E119" t="s">
+        <v>492</v>
+      </c>
+      <c r="G119" t="s">
+        <v>46</v>
+      </c>
+      <c r="H119" t="s">
+        <v>288</v>
+      </c>
+      <c r="I119" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J119" s="1"/>
+      <c r="M119" t="s">
+        <v>513</v>
+      </c>
+      <c r="N119" t="s">
+        <v>514</v>
+      </c>
+      <c r="O119" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="120" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A120" t="s">
+        <v>127</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="C120" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="D120" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="E120" t="s">
+        <v>495</v>
+      </c>
+      <c r="F120" t="s">
+        <v>1</v>
+      </c>
+      <c r="G120" t="s">
+        <v>44</v>
+      </c>
+      <c r="H120" t="s">
+        <v>288</v>
+      </c>
+      <c r="I120" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J120" s="1"/>
+      <c r="M120" t="s">
+        <v>513</v>
+      </c>
+      <c r="N120" t="s">
+        <v>514</v>
+      </c>
+      <c r="O120" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="121" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A121" t="s">
+        <v>2</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="C121" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="D121" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="E121" t="s">
+        <v>498</v>
+      </c>
+      <c r="F121" t="s">
+        <v>18</v>
+      </c>
+      <c r="G121" t="s">
+        <v>47</v>
+      </c>
+      <c r="H121" t="s">
+        <v>288</v>
+      </c>
+      <c r="I121" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J121" s="1"/>
+      <c r="M121" t="s">
+        <v>513</v>
+      </c>
+      <c r="N121" t="s">
+        <v>514</v>
+      </c>
+      <c r="O121" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="122" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A122" t="s">
+        <v>122</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="C122" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="D122" s="3" t="s">
+        <v>501</v>
+      </c>
+      <c r="E122" t="s">
+        <v>502</v>
+      </c>
+      <c r="F122" t="s">
+        <v>20</v>
+      </c>
+      <c r="G122" t="s">
+        <v>46</v>
+      </c>
+      <c r="H122" t="s">
+        <v>288</v>
+      </c>
+      <c r="I122" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J122" s="1"/>
+      <c r="M122" t="s">
+        <v>513</v>
+      </c>
+      <c r="N122" t="s">
+        <v>514</v>
+      </c>
+      <c r="O122" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="123" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A123" t="s">
+        <v>127</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>503</v>
+      </c>
+      <c r="C123" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="D123" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="E123" t="s">
+        <v>506</v>
+      </c>
+      <c r="F123" t="s">
+        <v>43</v>
+      </c>
+      <c r="G123" t="s">
+        <v>49</v>
+      </c>
+      <c r="H123" t="s">
+        <v>288</v>
+      </c>
+      <c r="I123" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J123" s="1"/>
+      <c r="M123" t="s">
+        <v>513</v>
+      </c>
+      <c r="N123" t="s">
+        <v>514</v>
+      </c>
+      <c r="O123" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="124" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A124" t="s">
+        <v>32</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="C124" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="D124" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="E124" t="s">
+        <v>510</v>
+      </c>
+      <c r="F124" t="s">
+        <v>511</v>
+      </c>
+      <c r="H124" t="s">
+        <v>288</v>
+      </c>
+      <c r="I124" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J124" s="1"/>
+      <c r="M124" t="s">
+        <v>513</v>
+      </c>
+      <c r="N124" t="s">
+        <v>514</v>
+      </c>
+      <c r="O124" t="s">
+        <v>55</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/events.xlsx
+++ b/events.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\cantolaoaqp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A85F4F0B-EB85-4E75-A164-F1E033AD3D6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5C64F4A-E0A3-44EF-9D3C-304E7AAECFFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5131,10 +5131,10 @@
         <v>348</v>
       </c>
       <c r="F82" t="s">
+        <v>43</v>
+      </c>
+      <c r="G82" t="s">
         <v>45</v>
-      </c>
-      <c r="G82" t="s">
-        <v>43</v>
       </c>
       <c r="H82" t="s">
         <v>288</v>

--- a/events.xlsx
+++ b/events.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\cantolaoaqp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5C64F4A-E0A3-44EF-9D3C-304E7AAECFFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95A43785-6A3A-4B04-A5FE-2142DC160083}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1474" uniqueCount="515">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2117" uniqueCount="720">
   <si>
     <t>XY</t>
   </si>
@@ -1565,6 +1565,621 @@
   </si>
   <si>
     <t>True</t>
+  </si>
+  <si>
+    <t>40:54</t>
+  </si>
+  <si>
+    <t>40:57</t>
+  </si>
+  <si>
+    <t>41:01</t>
+  </si>
+  <si>
+    <t>41:27</t>
+  </si>
+  <si>
+    <t>41:32</t>
+  </si>
+  <si>
+    <t>41:36</t>
+  </si>
+  <si>
+    <t>16;90</t>
+  </si>
+  <si>
+    <t>41:59</t>
+  </si>
+  <si>
+    <t>42:16</t>
+  </si>
+  <si>
+    <t>12;16</t>
+  </si>
+  <si>
+    <t>42:20</t>
+  </si>
+  <si>
+    <t>42:25</t>
+  </si>
+  <si>
+    <t>42:30</t>
+  </si>
+  <si>
+    <t>87;8</t>
+  </si>
+  <si>
+    <t>42:28</t>
+  </si>
+  <si>
+    <t>42:34</t>
+  </si>
+  <si>
+    <t>42:40</t>
+  </si>
+  <si>
+    <t>42:51</t>
+  </si>
+  <si>
+    <t>42:56</t>
+  </si>
+  <si>
+    <t>43:01</t>
+  </si>
+  <si>
+    <t>25;14</t>
+  </si>
+  <si>
+    <t>42:58</t>
+  </si>
+  <si>
+    <t>43:04</t>
+  </si>
+  <si>
+    <t>43:11</t>
+  </si>
+  <si>
+    <t>26;66</t>
+  </si>
+  <si>
+    <t>43:59</t>
+  </si>
+  <si>
+    <t>44:06</t>
+  </si>
+  <si>
+    <t>31;31</t>
+  </si>
+  <si>
+    <t>44:03</t>
+  </si>
+  <si>
+    <t>44:10</t>
+  </si>
+  <si>
+    <t>44:17</t>
+  </si>
+  <si>
+    <t>39;41</t>
+  </si>
+  <si>
+    <t>44:12</t>
+  </si>
+  <si>
+    <t>44:22</t>
+  </si>
+  <si>
+    <t>40;16</t>
+  </si>
+  <si>
+    <t>44:32</t>
+  </si>
+  <si>
+    <t>44:36</t>
+  </si>
+  <si>
+    <t>44:40</t>
+  </si>
+  <si>
+    <t>54;23</t>
+  </si>
+  <si>
+    <t>45:17</t>
+  </si>
+  <si>
+    <t>45:20</t>
+  </si>
+  <si>
+    <t>45:24</t>
+  </si>
+  <si>
+    <t>75;62</t>
+  </si>
+  <si>
+    <t>45:39</t>
+  </si>
+  <si>
+    <t>45:44</t>
+  </si>
+  <si>
+    <t>45:48</t>
+  </si>
+  <si>
+    <t>92;91</t>
+  </si>
+  <si>
+    <t>Corner en contra</t>
+  </si>
+  <si>
+    <t>45:47</t>
+  </si>
+  <si>
+    <t>45:52</t>
+  </si>
+  <si>
+    <t>45:56</t>
+  </si>
+  <si>
+    <t>95;51</t>
+  </si>
+  <si>
+    <t>46:22</t>
+  </si>
+  <si>
+    <t>46:26</t>
+  </si>
+  <si>
+    <t>46:29</t>
+  </si>
+  <si>
+    <t>73;14</t>
+  </si>
+  <si>
+    <t>46:30</t>
+  </si>
+  <si>
+    <t>46:34</t>
+  </si>
+  <si>
+    <t>46:37</t>
+  </si>
+  <si>
+    <t>78;85</t>
+  </si>
+  <si>
+    <t>46:46</t>
+  </si>
+  <si>
+    <t>46:55</t>
+  </si>
+  <si>
+    <t>69;84</t>
+  </si>
+  <si>
+    <t>47:25</t>
+  </si>
+  <si>
+    <t>47:29</t>
+  </si>
+  <si>
+    <t>47:33</t>
+  </si>
+  <si>
+    <t>43;82</t>
+  </si>
+  <si>
+    <t>47:32</t>
+  </si>
+  <si>
+    <t>47:40</t>
+  </si>
+  <si>
+    <t>47:48</t>
+  </si>
+  <si>
+    <t>51;44</t>
+  </si>
+  <si>
+    <t>47:46</t>
+  </si>
+  <si>
+    <t>47:51</t>
+  </si>
+  <si>
+    <t>47:57</t>
+  </si>
+  <si>
+    <t>48;34</t>
+  </si>
+  <si>
+    <t>48:09</t>
+  </si>
+  <si>
+    <t>48:13</t>
+  </si>
+  <si>
+    <t>48:18</t>
+  </si>
+  <si>
+    <t>19;91</t>
+  </si>
+  <si>
+    <t>48:15</t>
+  </si>
+  <si>
+    <t>48:22</t>
+  </si>
+  <si>
+    <t>33;65</t>
+  </si>
+  <si>
+    <t>48:29</t>
+  </si>
+  <si>
+    <t>48:33</t>
+  </si>
+  <si>
+    <t>48:37</t>
+  </si>
+  <si>
+    <t>19;36</t>
+  </si>
+  <si>
+    <t>48:34</t>
+  </si>
+  <si>
+    <t>48:39</t>
+  </si>
+  <si>
+    <t>48:43</t>
+  </si>
+  <si>
+    <t>31;91</t>
+  </si>
+  <si>
+    <t>49:24</t>
+  </si>
+  <si>
+    <t>49:27</t>
+  </si>
+  <si>
+    <t>49:30</t>
+  </si>
+  <si>
+    <t>14;94</t>
+  </si>
+  <si>
+    <t>49:48</t>
+  </si>
+  <si>
+    <t>50:05</t>
+  </si>
+  <si>
+    <t>24;15</t>
+  </si>
+  <si>
+    <t>50:20</t>
+  </si>
+  <si>
+    <t>50:25</t>
+  </si>
+  <si>
+    <t>50:29</t>
+  </si>
+  <si>
+    <t>53;15</t>
+  </si>
+  <si>
+    <t>50:39</t>
+  </si>
+  <si>
+    <t>50:46</t>
+  </si>
+  <si>
+    <t>50:54</t>
+  </si>
+  <si>
+    <t>74;12</t>
+  </si>
+  <si>
+    <t>51:09</t>
+  </si>
+  <si>
+    <t>51:19</t>
+  </si>
+  <si>
+    <t>51:29</t>
+  </si>
+  <si>
+    <t>87;85</t>
+  </si>
+  <si>
+    <t>51:31</t>
+  </si>
+  <si>
+    <t>51:39</t>
+  </si>
+  <si>
+    <t>51:46</t>
+  </si>
+  <si>
+    <t>32;27</t>
+  </si>
+  <si>
+    <t>51:54</t>
+  </si>
+  <si>
+    <t>51:59</t>
+  </si>
+  <si>
+    <t>52:03</t>
+  </si>
+  <si>
+    <t>16;73</t>
+  </si>
+  <si>
+    <t>53:22</t>
+  </si>
+  <si>
+    <t>53:28</t>
+  </si>
+  <si>
+    <t>53:34</t>
+  </si>
+  <si>
+    <t>67;27</t>
+  </si>
+  <si>
+    <t>54:14</t>
+  </si>
+  <si>
+    <t>54:19</t>
+  </si>
+  <si>
+    <t>54:25</t>
+  </si>
+  <si>
+    <t>30;52</t>
+  </si>
+  <si>
+    <t>54:47</t>
+  </si>
+  <si>
+    <t>54:49</t>
+  </si>
+  <si>
+    <t>54:52</t>
+  </si>
+  <si>
+    <t>23;60</t>
+  </si>
+  <si>
+    <t>54:51</t>
+  </si>
+  <si>
+    <t>54:54</t>
+  </si>
+  <si>
+    <t>54:57</t>
+  </si>
+  <si>
+    <t>25;81</t>
+  </si>
+  <si>
+    <t>55:18</t>
+  </si>
+  <si>
+    <t>55:24</t>
+  </si>
+  <si>
+    <t>55:30</t>
+  </si>
+  <si>
+    <t>9;61</t>
+  </si>
+  <si>
+    <t>55:31</t>
+  </si>
+  <si>
+    <t>55:35</t>
+  </si>
+  <si>
+    <t>55:39</t>
+  </si>
+  <si>
+    <t>60;32</t>
+  </si>
+  <si>
+    <t>55:43</t>
+  </si>
+  <si>
+    <t>55:48</t>
+  </si>
+  <si>
+    <t>92;47</t>
+  </si>
+  <si>
+    <t>55:45</t>
+  </si>
+  <si>
+    <t>55:51</t>
+  </si>
+  <si>
+    <t>55:57</t>
+  </si>
+  <si>
+    <t>68;23</t>
+  </si>
+  <si>
+    <t>56:17</t>
+  </si>
+  <si>
+    <t>56:29</t>
+  </si>
+  <si>
+    <t>56:40</t>
+  </si>
+  <si>
+    <t>91;35</t>
+  </si>
+  <si>
+    <t>57:13</t>
+  </si>
+  <si>
+    <t>57:17</t>
+  </si>
+  <si>
+    <t>57:22</t>
+  </si>
+  <si>
+    <t>8;86</t>
+  </si>
+  <si>
+    <t>57:27</t>
+  </si>
+  <si>
+    <t>57:31</t>
+  </si>
+  <si>
+    <t>57:35</t>
+  </si>
+  <si>
+    <t>6;47</t>
+  </si>
+  <si>
+    <t>57:39</t>
+  </si>
+  <si>
+    <t>57:44</t>
+  </si>
+  <si>
+    <t>32;22</t>
+  </si>
+  <si>
+    <t>57:52</t>
+  </si>
+  <si>
+    <t>57:58</t>
+  </si>
+  <si>
+    <t>58:03</t>
+  </si>
+  <si>
+    <t>20;92</t>
+  </si>
+  <si>
+    <t>58:12</t>
+  </si>
+  <si>
+    <t>58:17</t>
+  </si>
+  <si>
+    <t>58:22</t>
+  </si>
+  <si>
+    <t>67;79</t>
+  </si>
+  <si>
+    <t>59:01</t>
+  </si>
+  <si>
+    <t>59:11</t>
+  </si>
+  <si>
+    <t>59:20</t>
+  </si>
+  <si>
+    <t>60:07</t>
+  </si>
+  <si>
+    <t>60:22</t>
+  </si>
+  <si>
+    <t>60:37</t>
+  </si>
+  <si>
+    <t>41;66</t>
+  </si>
+  <si>
+    <t>60:35</t>
+  </si>
+  <si>
+    <t>60:40</t>
+  </si>
+  <si>
+    <t>60:45</t>
+  </si>
+  <si>
+    <t>19;10</t>
+  </si>
+  <si>
+    <t>60:48</t>
+  </si>
+  <si>
+    <t>60:52</t>
+  </si>
+  <si>
+    <t>13;86</t>
+  </si>
+  <si>
+    <t>60:51</t>
+  </si>
+  <si>
+    <t>60:56</t>
+  </si>
+  <si>
+    <t>61:00</t>
+  </si>
+  <si>
+    <t>32;74</t>
+  </si>
+  <si>
+    <t>61:04</t>
+  </si>
+  <si>
+    <t>61:08</t>
+  </si>
+  <si>
+    <t>61:12</t>
+  </si>
+  <si>
+    <t>39;49</t>
+  </si>
+  <si>
+    <t>61:11</t>
+  </si>
+  <si>
+    <t>61:14</t>
+  </si>
+  <si>
+    <t>61:17</t>
+  </si>
+  <si>
+    <t>68;53</t>
+  </si>
+  <si>
+    <t>61:16</t>
+  </si>
+  <si>
+    <t>61:20</t>
+  </si>
+  <si>
+    <t>61:24</t>
+  </si>
+  <si>
+    <t>49;60</t>
+  </si>
+  <si>
+    <t>61:21</t>
+  </si>
+  <si>
+    <t>61:26</t>
+  </si>
+  <si>
+    <t>61:32</t>
+  </si>
+  <si>
+    <t>43;74</t>
   </si>
 </sst>
 </file>
@@ -1647,8 +2262,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C1975CA6-E80E-40A4-A9D5-728F867A63BD}" name="Tabla1" displayName="Tabla1" ref="A1:O124" totalsRowShown="0">
-  <autoFilter ref="A1:O124" xr:uid="{C1975CA6-E80E-40A4-A9D5-728F867A63BD}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C1975CA6-E80E-40A4-A9D5-728F867A63BD}" name="Tabla1" displayName="Tabla1" ref="A1:O178" totalsRowShown="0">
+  <autoFilter ref="A1:O178" xr:uid="{C1975CA6-E80E-40A4-A9D5-728F867A63BD}"/>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{45CCCD5A-AFCF-487D-ADA1-0BFBB6505772}" name="Event"/>
     <tableColumn id="2" xr3:uid="{4A939A0F-B787-4665-B94F-35DE80E0B243}" name="start_time" dataDxfId="2"/>
@@ -1957,7 +2572,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77939FC4-FC73-4262-977F-310955BE7B1D}">
-  <dimension ref="A1:O124"/>
+  <dimension ref="A1:O178"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23.5703125" customWidth="1"/>
@@ -6764,6 +7379,2097 @@
         <v>55</v>
       </c>
     </row>
+    <row r="125" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A125" t="s">
+        <v>127</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="C125" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="D125" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="E125" t="s">
+        <v>245</v>
+      </c>
+      <c r="F125" t="s">
+        <v>43</v>
+      </c>
+      <c r="G125" t="s">
+        <v>44</v>
+      </c>
+      <c r="H125" t="s">
+        <v>288</v>
+      </c>
+      <c r="I125" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J125" s="1"/>
+      <c r="M125" t="s">
+        <v>513</v>
+      </c>
+      <c r="N125" t="s">
+        <v>514</v>
+      </c>
+      <c r="O125" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="126" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A126" t="s">
+        <v>32</v>
+      </c>
+      <c r="B126" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="C126" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="D126" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="E126" t="s">
+        <v>521</v>
+      </c>
+      <c r="F126" t="s">
+        <v>4</v>
+      </c>
+      <c r="G126" t="s">
+        <v>49</v>
+      </c>
+      <c r="H126" t="s">
+        <v>288</v>
+      </c>
+      <c r="I126" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J126" s="1"/>
+      <c r="M126" t="s">
+        <v>513</v>
+      </c>
+      <c r="N126" t="s">
+        <v>514</v>
+      </c>
+      <c r="O126" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="127" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A127" t="s">
+        <v>14</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="C127" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="D127" s="3" t="s">
+        <v>523</v>
+      </c>
+      <c r="E127" t="s">
+        <v>524</v>
+      </c>
+      <c r="F127" t="s">
+        <v>42</v>
+      </c>
+      <c r="G127" t="s">
+        <v>287</v>
+      </c>
+      <c r="H127" t="s">
+        <v>288</v>
+      </c>
+      <c r="I127" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J127" s="1"/>
+      <c r="M127" t="s">
+        <v>513</v>
+      </c>
+      <c r="N127" t="s">
+        <v>514</v>
+      </c>
+      <c r="O127" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="128" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A128" t="s">
+        <v>14</v>
+      </c>
+      <c r="B128" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="C128" s="3" t="s">
+        <v>526</v>
+      </c>
+      <c r="D128" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="E128" t="s">
+        <v>528</v>
+      </c>
+      <c r="F128" t="s">
+        <v>20</v>
+      </c>
+      <c r="G128" t="s">
+        <v>46</v>
+      </c>
+      <c r="H128" t="s">
+        <v>288</v>
+      </c>
+      <c r="I128" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J128" s="1"/>
+      <c r="M128" t="s">
+        <v>513</v>
+      </c>
+      <c r="N128" t="s">
+        <v>514</v>
+      </c>
+      <c r="O128" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="129" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A129" t="s">
+        <v>127</v>
+      </c>
+      <c r="B129" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="C129" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="D129" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="E129" t="s">
+        <v>402</v>
+      </c>
+      <c r="F129" t="s">
+        <v>43</v>
+      </c>
+      <c r="G129" t="s">
+        <v>45</v>
+      </c>
+      <c r="H129" t="s">
+        <v>288</v>
+      </c>
+      <c r="I129" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J129" s="1"/>
+      <c r="M129" t="s">
+        <v>513</v>
+      </c>
+      <c r="N129" t="s">
+        <v>514</v>
+      </c>
+      <c r="O129" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="130" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A130" t="s">
+        <v>14</v>
+      </c>
+      <c r="B130" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="C130" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="D130" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="E130" t="s">
+        <v>535</v>
+      </c>
+      <c r="F130" t="s">
+        <v>20</v>
+      </c>
+      <c r="G130" t="s">
+        <v>287</v>
+      </c>
+      <c r="H130" t="s">
+        <v>288</v>
+      </c>
+      <c r="I130" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J130" s="1"/>
+      <c r="M130" t="s">
+        <v>513</v>
+      </c>
+      <c r="N130" t="s">
+        <v>514</v>
+      </c>
+      <c r="O130" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="131" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A131" t="s">
+        <v>127</v>
+      </c>
+      <c r="B131" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="C131" s="3" t="s">
+        <v>537</v>
+      </c>
+      <c r="D131" s="3" t="s">
+        <v>538</v>
+      </c>
+      <c r="E131" t="s">
+        <v>539</v>
+      </c>
+      <c r="F131" t="s">
+        <v>43</v>
+      </c>
+      <c r="G131" t="s">
+        <v>49</v>
+      </c>
+      <c r="H131" t="s">
+        <v>288</v>
+      </c>
+      <c r="I131" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J131" s="1"/>
+      <c r="L131" t="s">
+        <v>512</v>
+      </c>
+      <c r="M131" t="s">
+        <v>513</v>
+      </c>
+      <c r="N131" t="s">
+        <v>514</v>
+      </c>
+      <c r="O131" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="132" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A132" t="s">
+        <v>14</v>
+      </c>
+      <c r="B132" s="3" t="s">
+        <v>540</v>
+      </c>
+      <c r="C132" s="3" t="s">
+        <v>540</v>
+      </c>
+      <c r="D132" s="3" t="s">
+        <v>541</v>
+      </c>
+      <c r="E132" t="s">
+        <v>542</v>
+      </c>
+      <c r="F132" t="s">
+        <v>20</v>
+      </c>
+      <c r="G132" t="s">
+        <v>46</v>
+      </c>
+      <c r="H132" t="s">
+        <v>288</v>
+      </c>
+      <c r="I132" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J132" s="1"/>
+      <c r="M132" t="s">
+        <v>513</v>
+      </c>
+      <c r="N132" t="s">
+        <v>514</v>
+      </c>
+      <c r="O132" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="133" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A133" t="s">
+        <v>127</v>
+      </c>
+      <c r="B133" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="C133" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="D133" s="3" t="s">
+        <v>545</v>
+      </c>
+      <c r="E133" t="s">
+        <v>546</v>
+      </c>
+      <c r="F133" t="s">
+        <v>1</v>
+      </c>
+      <c r="G133" t="s">
+        <v>47</v>
+      </c>
+      <c r="H133" t="s">
+        <v>288</v>
+      </c>
+      <c r="I133" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J133" s="1"/>
+      <c r="M133" t="s">
+        <v>513</v>
+      </c>
+      <c r="N133" t="s">
+        <v>514</v>
+      </c>
+      <c r="O133" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="134" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A134" t="s">
+        <v>122</v>
+      </c>
+      <c r="B134" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="C134" s="3" t="s">
+        <v>545</v>
+      </c>
+      <c r="D134" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="E134" t="s">
+        <v>549</v>
+      </c>
+      <c r="F134" t="s">
+        <v>20</v>
+      </c>
+      <c r="G134" t="s">
+        <v>48</v>
+      </c>
+      <c r="H134" t="s">
+        <v>288</v>
+      </c>
+      <c r="I134" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J134" s="1"/>
+      <c r="M134" t="s">
+        <v>513</v>
+      </c>
+      <c r="N134" t="s">
+        <v>514</v>
+      </c>
+      <c r="O134" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="135" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A135" t="s">
+        <v>27</v>
+      </c>
+      <c r="B135" s="3" t="s">
+        <v>550</v>
+      </c>
+      <c r="C135" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="D135" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="E135" t="s">
+        <v>553</v>
+      </c>
+      <c r="F135" t="s">
+        <v>15</v>
+      </c>
+      <c r="H135" t="s">
+        <v>288</v>
+      </c>
+      <c r="I135" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J135" s="1"/>
+      <c r="M135" t="s">
+        <v>513</v>
+      </c>
+      <c r="N135" t="s">
+        <v>514</v>
+      </c>
+      <c r="O135" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="136" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A136" t="s">
+        <v>27</v>
+      </c>
+      <c r="B136" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="C136" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="D136" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="E136" t="s">
+        <v>557</v>
+      </c>
+      <c r="F136" t="s">
+        <v>15</v>
+      </c>
+      <c r="G136" t="s">
+        <v>49</v>
+      </c>
+      <c r="H136" t="s">
+        <v>288</v>
+      </c>
+      <c r="I136" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J136" s="1"/>
+      <c r="M136" t="s">
+        <v>513</v>
+      </c>
+      <c r="N136" t="s">
+        <v>514</v>
+      </c>
+      <c r="O136" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="137" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A137" t="s">
+        <v>27</v>
+      </c>
+      <c r="B137" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="C137" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="D137" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="E137" t="s">
+        <v>561</v>
+      </c>
+      <c r="F137" t="s">
+        <v>562</v>
+      </c>
+      <c r="H137" t="s">
+        <v>288</v>
+      </c>
+      <c r="I137" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J137" s="1"/>
+      <c r="M137" t="s">
+        <v>513</v>
+      </c>
+      <c r="N137" t="s">
+        <v>514</v>
+      </c>
+      <c r="O137" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="138" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A138" t="s">
+        <v>127</v>
+      </c>
+      <c r="B138" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="C138" s="3" t="s">
+        <v>564</v>
+      </c>
+      <c r="D138" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="E138" t="s">
+        <v>566</v>
+      </c>
+      <c r="F138" t="s">
+        <v>43</v>
+      </c>
+      <c r="G138" t="s">
+        <v>47</v>
+      </c>
+      <c r="H138" t="s">
+        <v>288</v>
+      </c>
+      <c r="I138" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J138" s="1"/>
+      <c r="M138" t="s">
+        <v>513</v>
+      </c>
+      <c r="N138" t="s">
+        <v>514</v>
+      </c>
+      <c r="O138" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="139" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A139" t="s">
+        <v>27</v>
+      </c>
+      <c r="B139" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="C139" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="D139" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="E139" t="s">
+        <v>570</v>
+      </c>
+      <c r="F139" t="s">
+        <v>15</v>
+      </c>
+      <c r="H139" t="s">
+        <v>288</v>
+      </c>
+      <c r="I139" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J139" s="1"/>
+      <c r="M139" t="s">
+        <v>513</v>
+      </c>
+      <c r="N139" t="s">
+        <v>514</v>
+      </c>
+      <c r="O139" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="140" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A140" t="s">
+        <v>127</v>
+      </c>
+      <c r="B140" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="C140" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="D140" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="E140" t="s">
+        <v>574</v>
+      </c>
+      <c r="F140" t="s">
+        <v>43</v>
+      </c>
+      <c r="G140" t="s">
+        <v>44</v>
+      </c>
+      <c r="H140" t="s">
+        <v>288</v>
+      </c>
+      <c r="I140" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J140" s="1"/>
+      <c r="M140" t="s">
+        <v>513</v>
+      </c>
+      <c r="N140" t="s">
+        <v>514</v>
+      </c>
+      <c r="O140" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="141" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A141" t="s">
+        <v>2</v>
+      </c>
+      <c r="B141" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="C141" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="D141" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="E141" t="s">
+        <v>577</v>
+      </c>
+      <c r="F141" t="s">
+        <v>17</v>
+      </c>
+      <c r="G141" t="s">
+        <v>47</v>
+      </c>
+      <c r="H141" t="s">
+        <v>288</v>
+      </c>
+      <c r="I141" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J141" s="1"/>
+      <c r="M141" t="s">
+        <v>513</v>
+      </c>
+      <c r="N141" t="s">
+        <v>514</v>
+      </c>
+      <c r="O141" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="142" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A142" t="s">
+        <v>127</v>
+      </c>
+      <c r="B142" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="C142" s="3" t="s">
+        <v>579</v>
+      </c>
+      <c r="D142" s="3" t="s">
+        <v>580</v>
+      </c>
+      <c r="E142" t="s">
+        <v>581</v>
+      </c>
+      <c r="F142" t="s">
+        <v>1</v>
+      </c>
+      <c r="G142" t="s">
+        <v>47</v>
+      </c>
+      <c r="H142" t="s">
+        <v>288</v>
+      </c>
+      <c r="I142" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J142" s="1"/>
+      <c r="M142" t="s">
+        <v>513</v>
+      </c>
+      <c r="N142" t="s">
+        <v>514</v>
+      </c>
+      <c r="O142" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="143" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A143" t="s">
+        <v>122</v>
+      </c>
+      <c r="B143" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="C143" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="D143" s="3" t="s">
+        <v>584</v>
+      </c>
+      <c r="E143" t="s">
+        <v>585</v>
+      </c>
+      <c r="F143" t="s">
+        <v>20</v>
+      </c>
+      <c r="G143" t="s">
+        <v>46</v>
+      </c>
+      <c r="H143" t="s">
+        <v>288</v>
+      </c>
+      <c r="I143" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J143" s="1"/>
+      <c r="M143" t="s">
+        <v>513</v>
+      </c>
+      <c r="N143" t="s">
+        <v>514</v>
+      </c>
+      <c r="O143" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="144" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A144" t="s">
+        <v>127</v>
+      </c>
+      <c r="B144" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="C144" s="3" t="s">
+        <v>587</v>
+      </c>
+      <c r="D144" s="3" t="s">
+        <v>588</v>
+      </c>
+      <c r="E144" t="s">
+        <v>589</v>
+      </c>
+      <c r="F144" t="s">
+        <v>43</v>
+      </c>
+      <c r="G144" t="s">
+        <v>47</v>
+      </c>
+      <c r="H144" t="s">
+        <v>288</v>
+      </c>
+      <c r="I144" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J144" s="1"/>
+      <c r="M144" t="s">
+        <v>513</v>
+      </c>
+      <c r="N144" t="s">
+        <v>514</v>
+      </c>
+      <c r="O144" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="145" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A145" t="s">
+        <v>14</v>
+      </c>
+      <c r="B145" s="3" t="s">
+        <v>590</v>
+      </c>
+      <c r="C145" s="3" t="s">
+        <v>591</v>
+      </c>
+      <c r="D145" s="3" t="s">
+        <v>592</v>
+      </c>
+      <c r="E145" t="s">
+        <v>593</v>
+      </c>
+      <c r="F145" t="s">
+        <v>20</v>
+      </c>
+      <c r="G145" t="s">
+        <v>46</v>
+      </c>
+      <c r="H145" t="s">
+        <v>288</v>
+      </c>
+      <c r="I145" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J145" s="1"/>
+      <c r="M145" t="s">
+        <v>513</v>
+      </c>
+      <c r="N145" t="s">
+        <v>514</v>
+      </c>
+      <c r="O145" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="146" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A146" t="s">
+        <v>127</v>
+      </c>
+      <c r="B146" s="3" t="s">
+        <v>594</v>
+      </c>
+      <c r="C146" s="3" t="s">
+        <v>592</v>
+      </c>
+      <c r="D146" s="3" t="s">
+        <v>595</v>
+      </c>
+      <c r="E146" t="s">
+        <v>596</v>
+      </c>
+      <c r="F146" t="s">
+        <v>43</v>
+      </c>
+      <c r="G146" t="s">
+        <v>47</v>
+      </c>
+      <c r="H146" t="s">
+        <v>288</v>
+      </c>
+      <c r="I146" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J146" s="1"/>
+      <c r="M146" t="s">
+        <v>513</v>
+      </c>
+      <c r="N146" t="s">
+        <v>514</v>
+      </c>
+      <c r="O146" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="147" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A147" t="s">
+        <v>14</v>
+      </c>
+      <c r="B147" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="C147" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="D147" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="E147" t="s">
+        <v>600</v>
+      </c>
+      <c r="F147" t="s">
+        <v>42</v>
+      </c>
+      <c r="G147" t="s">
+        <v>46</v>
+      </c>
+      <c r="H147" t="s">
+        <v>288</v>
+      </c>
+      <c r="I147" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J147" s="1"/>
+      <c r="M147" t="s">
+        <v>513</v>
+      </c>
+      <c r="N147" t="s">
+        <v>514</v>
+      </c>
+      <c r="O147" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="148" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A148" t="s">
+        <v>127</v>
+      </c>
+      <c r="B148" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="C148" s="3" t="s">
+        <v>602</v>
+      </c>
+      <c r="D148" s="3" t="s">
+        <v>603</v>
+      </c>
+      <c r="E148" t="s">
+        <v>604</v>
+      </c>
+      <c r="F148" t="s">
+        <v>43</v>
+      </c>
+      <c r="G148" t="s">
+        <v>44</v>
+      </c>
+      <c r="H148" t="s">
+        <v>288</v>
+      </c>
+      <c r="I148" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J148" s="1"/>
+      <c r="M148" t="s">
+        <v>513</v>
+      </c>
+      <c r="N148" t="s">
+        <v>514</v>
+      </c>
+      <c r="O148" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="149" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A149" t="s">
+        <v>32</v>
+      </c>
+      <c r="B149" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="C149" s="3" t="s">
+        <v>606</v>
+      </c>
+      <c r="D149" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="E149" t="s">
+        <v>608</v>
+      </c>
+      <c r="F149" t="s">
+        <v>4</v>
+      </c>
+      <c r="H149" t="s">
+        <v>288</v>
+      </c>
+      <c r="I149" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J149" s="1"/>
+      <c r="M149" t="s">
+        <v>513</v>
+      </c>
+      <c r="N149" t="s">
+        <v>514</v>
+      </c>
+      <c r="O149" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="150" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A150" t="s">
+        <v>14</v>
+      </c>
+      <c r="B150" s="3" t="s">
+        <v>609</v>
+      </c>
+      <c r="C150" s="3" t="s">
+        <v>609</v>
+      </c>
+      <c r="D150" s="3" t="s">
+        <v>610</v>
+      </c>
+      <c r="E150" t="s">
+        <v>611</v>
+      </c>
+      <c r="F150" t="s">
+        <v>20</v>
+      </c>
+      <c r="G150" t="s">
+        <v>287</v>
+      </c>
+      <c r="H150" t="s">
+        <v>288</v>
+      </c>
+      <c r="I150" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J150" s="1"/>
+      <c r="M150" t="s">
+        <v>513</v>
+      </c>
+      <c r="N150" t="s">
+        <v>514</v>
+      </c>
+      <c r="O150" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="151" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A151" t="s">
+        <v>27</v>
+      </c>
+      <c r="B151" s="3" t="s">
+        <v>612</v>
+      </c>
+      <c r="C151" s="3" t="s">
+        <v>613</v>
+      </c>
+      <c r="D151" s="3" t="s">
+        <v>614</v>
+      </c>
+      <c r="E151" t="s">
+        <v>615</v>
+      </c>
+      <c r="F151" t="s">
+        <v>15</v>
+      </c>
+      <c r="H151" t="s">
+        <v>288</v>
+      </c>
+      <c r="I151" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J151" s="1"/>
+      <c r="M151" t="s">
+        <v>513</v>
+      </c>
+      <c r="N151" t="s">
+        <v>514</v>
+      </c>
+      <c r="O151" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="152" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A152" t="s">
+        <v>14</v>
+      </c>
+      <c r="B152" s="3" t="s">
+        <v>616</v>
+      </c>
+      <c r="C152" s="3" t="s">
+        <v>617</v>
+      </c>
+      <c r="D152" s="3" t="s">
+        <v>618</v>
+      </c>
+      <c r="E152" t="s">
+        <v>619</v>
+      </c>
+      <c r="F152" t="s">
+        <v>20</v>
+      </c>
+      <c r="G152" t="s">
+        <v>48</v>
+      </c>
+      <c r="H152" t="s">
+        <v>288</v>
+      </c>
+      <c r="I152" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J152" s="1"/>
+      <c r="M152" t="s">
+        <v>513</v>
+      </c>
+      <c r="N152" t="s">
+        <v>514</v>
+      </c>
+      <c r="O152" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="153" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A153" t="s">
+        <v>127</v>
+      </c>
+      <c r="B153" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="C153" s="3" t="s">
+        <v>621</v>
+      </c>
+      <c r="D153" s="3" t="s">
+        <v>622</v>
+      </c>
+      <c r="E153" t="s">
+        <v>623</v>
+      </c>
+      <c r="F153" t="s">
+        <v>43</v>
+      </c>
+      <c r="G153" t="s">
+        <v>45</v>
+      </c>
+      <c r="H153" t="s">
+        <v>288</v>
+      </c>
+      <c r="I153" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J153" s="1"/>
+      <c r="M153" t="s">
+        <v>513</v>
+      </c>
+      <c r="N153" t="s">
+        <v>514</v>
+      </c>
+      <c r="O153" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="154" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A154" t="s">
+        <v>127</v>
+      </c>
+      <c r="B154" s="3" t="s">
+        <v>624</v>
+      </c>
+      <c r="C154" s="3" t="s">
+        <v>625</v>
+      </c>
+      <c r="D154" s="3" t="s">
+        <v>626</v>
+      </c>
+      <c r="E154" t="s">
+        <v>627</v>
+      </c>
+      <c r="F154" t="s">
+        <v>43</v>
+      </c>
+      <c r="G154" t="s">
+        <v>49</v>
+      </c>
+      <c r="H154" t="s">
+        <v>288</v>
+      </c>
+      <c r="I154" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J154" s="1"/>
+      <c r="M154" t="s">
+        <v>513</v>
+      </c>
+      <c r="N154" t="s">
+        <v>514</v>
+      </c>
+      <c r="O154" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="155" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A155" t="s">
+        <v>14</v>
+      </c>
+      <c r="B155" s="3" t="s">
+        <v>628</v>
+      </c>
+      <c r="C155" s="3" t="s">
+        <v>629</v>
+      </c>
+      <c r="D155" s="3" t="s">
+        <v>630</v>
+      </c>
+      <c r="E155" t="s">
+        <v>631</v>
+      </c>
+      <c r="F155" t="s">
+        <v>20</v>
+      </c>
+      <c r="G155" t="s">
+        <v>48</v>
+      </c>
+      <c r="H155" t="s">
+        <v>288</v>
+      </c>
+      <c r="I155" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J155" s="1"/>
+      <c r="M155" t="s">
+        <v>513</v>
+      </c>
+      <c r="N155" t="s">
+        <v>514</v>
+      </c>
+      <c r="O155" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="156" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A156" t="s">
+        <v>2</v>
+      </c>
+      <c r="B156" s="3" t="s">
+        <v>632</v>
+      </c>
+      <c r="C156" s="3" t="s">
+        <v>633</v>
+      </c>
+      <c r="D156" s="3" t="s">
+        <v>634</v>
+      </c>
+      <c r="E156" t="s">
+        <v>635</v>
+      </c>
+      <c r="F156" t="s">
+        <v>3</v>
+      </c>
+      <c r="G156" t="s">
+        <v>44</v>
+      </c>
+      <c r="H156" t="s">
+        <v>288</v>
+      </c>
+      <c r="I156" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J156" s="1"/>
+      <c r="M156" t="s">
+        <v>513</v>
+      </c>
+      <c r="N156" t="s">
+        <v>514</v>
+      </c>
+      <c r="O156" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="157" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A157" t="s">
+        <v>32</v>
+      </c>
+      <c r="B157" s="3" t="s">
+        <v>636</v>
+      </c>
+      <c r="C157" s="3" t="s">
+        <v>637</v>
+      </c>
+      <c r="D157" s="3" t="s">
+        <v>638</v>
+      </c>
+      <c r="E157" t="s">
+        <v>639</v>
+      </c>
+      <c r="F157" t="s">
+        <v>4</v>
+      </c>
+      <c r="G157" t="s">
+        <v>49</v>
+      </c>
+      <c r="H157" t="s">
+        <v>288</v>
+      </c>
+      <c r="I157" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J157" s="1"/>
+      <c r="M157" t="s">
+        <v>513</v>
+      </c>
+      <c r="N157" t="s">
+        <v>514</v>
+      </c>
+      <c r="O157" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="158" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A158" t="s">
+        <v>14</v>
+      </c>
+      <c r="B158" s="3" t="s">
+        <v>640</v>
+      </c>
+      <c r="C158" s="3" t="s">
+        <v>641</v>
+      </c>
+      <c r="D158" s="3" t="s">
+        <v>642</v>
+      </c>
+      <c r="E158" t="s">
+        <v>643</v>
+      </c>
+      <c r="F158" t="s">
+        <v>20</v>
+      </c>
+      <c r="G158" t="s">
+        <v>46</v>
+      </c>
+      <c r="H158" t="s">
+        <v>288</v>
+      </c>
+      <c r="I158" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J158" s="1"/>
+      <c r="M158" t="s">
+        <v>513</v>
+      </c>
+      <c r="N158" t="s">
+        <v>514</v>
+      </c>
+      <c r="O158" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="159" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A159" t="s">
+        <v>127</v>
+      </c>
+      <c r="B159" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="C159" s="3" t="s">
+        <v>645</v>
+      </c>
+      <c r="D159" s="3" t="s">
+        <v>646</v>
+      </c>
+      <c r="E159" t="s">
+        <v>647</v>
+      </c>
+      <c r="F159" t="s">
+        <v>43</v>
+      </c>
+      <c r="G159" t="s">
+        <v>44</v>
+      </c>
+      <c r="H159" t="s">
+        <v>288</v>
+      </c>
+      <c r="I159" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J159" s="1"/>
+      <c r="M159" t="s">
+        <v>513</v>
+      </c>
+      <c r="N159" t="s">
+        <v>514</v>
+      </c>
+      <c r="O159" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="160" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A160" t="s">
+        <v>32</v>
+      </c>
+      <c r="B160" s="3" t="s">
+        <v>648</v>
+      </c>
+      <c r="C160" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="D160" s="3" t="s">
+        <v>650</v>
+      </c>
+      <c r="E160" t="s">
+        <v>651</v>
+      </c>
+      <c r="F160" t="s">
+        <v>511</v>
+      </c>
+      <c r="H160" t="s">
+        <v>288</v>
+      </c>
+      <c r="I160" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J160" s="1"/>
+      <c r="M160" t="s">
+        <v>513</v>
+      </c>
+      <c r="N160" t="s">
+        <v>514</v>
+      </c>
+      <c r="O160" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="161" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A161" t="s">
+        <v>14</v>
+      </c>
+      <c r="B161" s="3" t="s">
+        <v>652</v>
+      </c>
+      <c r="C161" s="3" t="s">
+        <v>653</v>
+      </c>
+      <c r="D161" s="3" t="s">
+        <v>654</v>
+      </c>
+      <c r="E161" t="s">
+        <v>655</v>
+      </c>
+      <c r="G161" t="s">
+        <v>46</v>
+      </c>
+      <c r="H161" t="s">
+        <v>288</v>
+      </c>
+      <c r="I161" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J161" s="1"/>
+      <c r="M161" t="s">
+        <v>513</v>
+      </c>
+      <c r="N161" t="s">
+        <v>514</v>
+      </c>
+      <c r="O161" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="162" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A162" t="s">
+        <v>127</v>
+      </c>
+      <c r="B162" s="3" t="s">
+        <v>654</v>
+      </c>
+      <c r="C162" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="D162" s="3" t="s">
+        <v>657</v>
+      </c>
+      <c r="E162" t="s">
+        <v>658</v>
+      </c>
+      <c r="F162" t="s">
+        <v>43</v>
+      </c>
+      <c r="G162" t="s">
+        <v>47</v>
+      </c>
+      <c r="H162" t="s">
+        <v>288</v>
+      </c>
+      <c r="I162" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J162" s="1"/>
+      <c r="M162" t="s">
+        <v>513</v>
+      </c>
+      <c r="N162" t="s">
+        <v>514</v>
+      </c>
+      <c r="O162" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="163" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A163" t="s">
+        <v>122</v>
+      </c>
+      <c r="B163" s="3" t="s">
+        <v>659</v>
+      </c>
+      <c r="C163" s="3" t="s">
+        <v>660</v>
+      </c>
+      <c r="D163" s="3" t="s">
+        <v>661</v>
+      </c>
+      <c r="E163" t="s">
+        <v>662</v>
+      </c>
+      <c r="F163" t="s">
+        <v>20</v>
+      </c>
+      <c r="G163" t="s">
+        <v>419</v>
+      </c>
+      <c r="H163" t="s">
+        <v>288</v>
+      </c>
+      <c r="I163" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J163" s="1"/>
+      <c r="M163" t="s">
+        <v>513</v>
+      </c>
+      <c r="N163" t="s">
+        <v>514</v>
+      </c>
+      <c r="O163" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="164" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A164" t="s">
+        <v>2</v>
+      </c>
+      <c r="B164" s="3" t="s">
+        <v>663</v>
+      </c>
+      <c r="C164" s="3" t="s">
+        <v>664</v>
+      </c>
+      <c r="D164" s="3" t="s">
+        <v>665</v>
+      </c>
+      <c r="E164" t="s">
+        <v>666</v>
+      </c>
+      <c r="F164" t="s">
+        <v>17</v>
+      </c>
+      <c r="G164" t="s">
+        <v>45</v>
+      </c>
+      <c r="H164" t="s">
+        <v>288</v>
+      </c>
+      <c r="I164" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J164" s="1"/>
+      <c r="M164" t="s">
+        <v>513</v>
+      </c>
+      <c r="N164" t="s">
+        <v>514</v>
+      </c>
+      <c r="O164" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="165" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A165" t="s">
+        <v>32</v>
+      </c>
+      <c r="B165" s="3" t="s">
+        <v>667</v>
+      </c>
+      <c r="C165" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="D165" s="3" t="s">
+        <v>669</v>
+      </c>
+      <c r="E165" t="s">
+        <v>670</v>
+      </c>
+      <c r="F165" t="s">
+        <v>4</v>
+      </c>
+      <c r="G165" t="s">
+        <v>49</v>
+      </c>
+      <c r="H165" t="s">
+        <v>288</v>
+      </c>
+      <c r="I165" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J165" s="1"/>
+      <c r="M165" t="s">
+        <v>513</v>
+      </c>
+      <c r="N165" t="s">
+        <v>514</v>
+      </c>
+      <c r="O165" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="166" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A166" t="s">
+        <v>122</v>
+      </c>
+      <c r="B166" s="3" t="s">
+        <v>671</v>
+      </c>
+      <c r="C166" s="3" t="s">
+        <v>672</v>
+      </c>
+      <c r="D166" s="3" t="s">
+        <v>673</v>
+      </c>
+      <c r="E166" t="s">
+        <v>674</v>
+      </c>
+      <c r="F166" t="s">
+        <v>21</v>
+      </c>
+      <c r="G166" t="s">
+        <v>46</v>
+      </c>
+      <c r="H166" t="s">
+        <v>288</v>
+      </c>
+      <c r="I166" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J166" s="1"/>
+      <c r="M166" t="s">
+        <v>513</v>
+      </c>
+      <c r="N166" t="s">
+        <v>514</v>
+      </c>
+      <c r="O166" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="167" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A167" t="s">
+        <v>127</v>
+      </c>
+      <c r="B167" s="3" t="s">
+        <v>673</v>
+      </c>
+      <c r="C167" s="3" t="s">
+        <v>675</v>
+      </c>
+      <c r="D167" s="3" t="s">
+        <v>676</v>
+      </c>
+      <c r="E167" t="s">
+        <v>677</v>
+      </c>
+      <c r="F167" t="s">
+        <v>43</v>
+      </c>
+      <c r="G167" t="s">
+        <v>47</v>
+      </c>
+      <c r="H167" t="s">
+        <v>288</v>
+      </c>
+      <c r="I167" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J167" s="1"/>
+      <c r="M167" t="s">
+        <v>513</v>
+      </c>
+      <c r="N167" t="s">
+        <v>514</v>
+      </c>
+      <c r="O167" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="168" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A168" t="s">
+        <v>14</v>
+      </c>
+      <c r="B168" s="3" t="s">
+        <v>678</v>
+      </c>
+      <c r="C168" s="3" t="s">
+        <v>679</v>
+      </c>
+      <c r="D168" s="3" t="s">
+        <v>680</v>
+      </c>
+      <c r="E168" t="s">
+        <v>681</v>
+      </c>
+      <c r="F168" t="s">
+        <v>20</v>
+      </c>
+      <c r="G168" t="s">
+        <v>48</v>
+      </c>
+      <c r="H168" t="s">
+        <v>288</v>
+      </c>
+      <c r="I168" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J168" s="1"/>
+      <c r="M168" t="s">
+        <v>513</v>
+      </c>
+      <c r="N168" t="s">
+        <v>514</v>
+      </c>
+      <c r="O168" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="169" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A169" t="s">
+        <v>14</v>
+      </c>
+      <c r="B169" s="3" t="s">
+        <v>682</v>
+      </c>
+      <c r="C169" s="3" t="s">
+        <v>683</v>
+      </c>
+      <c r="D169" s="3" t="s">
+        <v>684</v>
+      </c>
+      <c r="E169" t="s">
+        <v>685</v>
+      </c>
+      <c r="F169" t="s">
+        <v>42</v>
+      </c>
+      <c r="G169" t="s">
+        <v>287</v>
+      </c>
+      <c r="H169" t="s">
+        <v>288</v>
+      </c>
+      <c r="I169" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J169" s="1"/>
+      <c r="M169" t="s">
+        <v>513</v>
+      </c>
+      <c r="N169" t="s">
+        <v>514</v>
+      </c>
+      <c r="O169" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="170" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A170" t="s">
+        <v>2</v>
+      </c>
+      <c r="B170" s="3" t="s">
+        <v>686</v>
+      </c>
+      <c r="C170" s="3" t="s">
+        <v>687</v>
+      </c>
+      <c r="D170" s="3" t="s">
+        <v>688</v>
+      </c>
+      <c r="E170" t="s">
+        <v>566</v>
+      </c>
+      <c r="F170" t="s">
+        <v>17</v>
+      </c>
+      <c r="G170" t="s">
+        <v>49</v>
+      </c>
+      <c r="H170" t="s">
+        <v>288</v>
+      </c>
+      <c r="I170" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J170" s="1"/>
+      <c r="L170" t="s">
+        <v>512</v>
+      </c>
+      <c r="M170" t="s">
+        <v>513</v>
+      </c>
+      <c r="N170" t="s">
+        <v>514</v>
+      </c>
+      <c r="O170" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="171" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A171" t="s">
+        <v>14</v>
+      </c>
+      <c r="B171" s="3" t="s">
+        <v>689</v>
+      </c>
+      <c r="C171" s="3" t="s">
+        <v>690</v>
+      </c>
+      <c r="D171" s="3" t="s">
+        <v>691</v>
+      </c>
+      <c r="E171" t="s">
+        <v>692</v>
+      </c>
+      <c r="F171" t="s">
+        <v>20</v>
+      </c>
+      <c r="G171" t="s">
+        <v>46</v>
+      </c>
+      <c r="H171" t="s">
+        <v>288</v>
+      </c>
+      <c r="I171" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J171" s="1"/>
+      <c r="M171" t="s">
+        <v>513</v>
+      </c>
+      <c r="N171" t="s">
+        <v>514</v>
+      </c>
+      <c r="O171" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="172" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A172" t="s">
+        <v>127</v>
+      </c>
+      <c r="B172" s="3" t="s">
+        <v>693</v>
+      </c>
+      <c r="C172" s="3" t="s">
+        <v>694</v>
+      </c>
+      <c r="D172" s="3" t="s">
+        <v>695</v>
+      </c>
+      <c r="E172" t="s">
+        <v>696</v>
+      </c>
+      <c r="F172" t="s">
+        <v>43</v>
+      </c>
+      <c r="G172" t="s">
+        <v>49</v>
+      </c>
+      <c r="H172" t="s">
+        <v>288</v>
+      </c>
+      <c r="I172" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J172" s="1"/>
+      <c r="M172" t="s">
+        <v>513</v>
+      </c>
+      <c r="N172" t="s">
+        <v>514</v>
+      </c>
+      <c r="O172" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="173" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A173" t="s">
+        <v>122</v>
+      </c>
+      <c r="B173" s="3" t="s">
+        <v>695</v>
+      </c>
+      <c r="C173" s="3" t="s">
+        <v>697</v>
+      </c>
+      <c r="D173" s="3" t="s">
+        <v>698</v>
+      </c>
+      <c r="E173" t="s">
+        <v>699</v>
+      </c>
+      <c r="F173" t="s">
+        <v>20</v>
+      </c>
+      <c r="G173" t="s">
+        <v>46</v>
+      </c>
+      <c r="H173" t="s">
+        <v>288</v>
+      </c>
+      <c r="I173" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J173" s="1"/>
+      <c r="M173" t="s">
+        <v>513</v>
+      </c>
+      <c r="N173" t="s">
+        <v>514</v>
+      </c>
+      <c r="O173" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="174" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A174" t="s">
+        <v>2</v>
+      </c>
+      <c r="B174" s="3" t="s">
+        <v>700</v>
+      </c>
+      <c r="C174" s="3" t="s">
+        <v>701</v>
+      </c>
+      <c r="D174" s="3" t="s">
+        <v>702</v>
+      </c>
+      <c r="E174" t="s">
+        <v>703</v>
+      </c>
+      <c r="F174" t="s">
+        <v>17</v>
+      </c>
+      <c r="G174" t="s">
+        <v>47</v>
+      </c>
+      <c r="H174" t="s">
+        <v>288</v>
+      </c>
+      <c r="I174" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J174" s="1"/>
+      <c r="M174" t="s">
+        <v>513</v>
+      </c>
+      <c r="N174" t="s">
+        <v>514</v>
+      </c>
+      <c r="O174" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="175" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A175" t="s">
+        <v>122</v>
+      </c>
+      <c r="B175" s="3" t="s">
+        <v>704</v>
+      </c>
+      <c r="C175" s="3" t="s">
+        <v>705</v>
+      </c>
+      <c r="D175" s="3" t="s">
+        <v>706</v>
+      </c>
+      <c r="E175" t="s">
+        <v>707</v>
+      </c>
+      <c r="F175" t="s">
+        <v>20</v>
+      </c>
+      <c r="G175" t="s">
+        <v>46</v>
+      </c>
+      <c r="H175" t="s">
+        <v>288</v>
+      </c>
+      <c r="I175" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J175" s="1"/>
+      <c r="M175" t="s">
+        <v>513</v>
+      </c>
+      <c r="N175" t="s">
+        <v>514</v>
+      </c>
+      <c r="O175" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="176" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A176" t="s">
+        <v>127</v>
+      </c>
+      <c r="B176" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="C176" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="D176" s="3" t="s">
+        <v>710</v>
+      </c>
+      <c r="E176" t="s">
+        <v>711</v>
+      </c>
+      <c r="F176" t="s">
+        <v>43</v>
+      </c>
+      <c r="G176" t="s">
+        <v>47</v>
+      </c>
+      <c r="H176" t="s">
+        <v>288</v>
+      </c>
+      <c r="I176" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J176" s="1"/>
+      <c r="M176" t="s">
+        <v>513</v>
+      </c>
+      <c r="N176" t="s">
+        <v>514</v>
+      </c>
+      <c r="O176" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="177" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A177" t="s">
+        <v>122</v>
+      </c>
+      <c r="B177" s="3" t="s">
+        <v>712</v>
+      </c>
+      <c r="C177" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="D177" s="3" t="s">
+        <v>714</v>
+      </c>
+      <c r="E177" t="s">
+        <v>715</v>
+      </c>
+      <c r="F177" t="s">
+        <v>20</v>
+      </c>
+      <c r="G177" t="s">
+        <v>46</v>
+      </c>
+      <c r="H177" t="s">
+        <v>288</v>
+      </c>
+      <c r="I177" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J177" s="1"/>
+      <c r="M177" t="s">
+        <v>513</v>
+      </c>
+      <c r="N177" t="s">
+        <v>514</v>
+      </c>
+      <c r="O177" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="178" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A178" t="s">
+        <v>127</v>
+      </c>
+      <c r="B178" s="3" t="s">
+        <v>716</v>
+      </c>
+      <c r="C178" s="3" t="s">
+        <v>717</v>
+      </c>
+      <c r="D178" s="3" t="s">
+        <v>718</v>
+      </c>
+      <c r="E178" t="s">
+        <v>719</v>
+      </c>
+      <c r="F178" t="s">
+        <v>43</v>
+      </c>
+      <c r="G178" t="s">
+        <v>44</v>
+      </c>
+      <c r="H178" t="s">
+        <v>288</v>
+      </c>
+      <c r="I178" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J178" s="1"/>
+      <c r="M178" t="s">
+        <v>513</v>
+      </c>
+      <c r="N178" t="s">
+        <v>514</v>
+      </c>
+      <c r="O178" t="s">
+        <v>55</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/events.xlsx
+++ b/events.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\cantolaoaqp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95A43785-6A3A-4B04-A5FE-2142DC160083}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C8B8E58-C77E-4E4B-BB47-30AA183E9FBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7828,7 +7828,7 @@
         <v>15</v>
       </c>
       <c r="G136" t="s">
-        <v>49</v>
+        <v>419</v>
       </c>
       <c r="H136" t="s">
         <v>288</v>

--- a/events.xlsx
+++ b/events.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\cantolaoaqp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C8B8E58-C77E-4E4B-BB47-30AA183E9FBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A00E0F7-A882-4874-83E6-645BCA327336}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2117" uniqueCount="720">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3343" uniqueCount="999">
   <si>
     <t>XY</t>
   </si>
@@ -2180,6 +2180,843 @@
   </si>
   <si>
     <t>43;74</t>
+  </si>
+  <si>
+    <t>02:27</t>
+  </si>
+  <si>
+    <t>36;81</t>
+  </si>
+  <si>
+    <t>02:19</t>
+  </si>
+  <si>
+    <t>2;56</t>
+  </si>
+  <si>
+    <t>03:05</t>
+  </si>
+  <si>
+    <t>76;85</t>
+  </si>
+  <si>
+    <t>03:10</t>
+  </si>
+  <si>
+    <t>03:21</t>
+  </si>
+  <si>
+    <t>42;90</t>
+  </si>
+  <si>
+    <t>03:20</t>
+  </si>
+  <si>
+    <t>03:33</t>
+  </si>
+  <si>
+    <t>56;70</t>
+  </si>
+  <si>
+    <t>03:30</t>
+  </si>
+  <si>
+    <t>03:40</t>
+  </si>
+  <si>
+    <t>52;81</t>
+  </si>
+  <si>
+    <t>03:52</t>
+  </si>
+  <si>
+    <t>04:00</t>
+  </si>
+  <si>
+    <t>64;89</t>
+  </si>
+  <si>
+    <t>04:05</t>
+  </si>
+  <si>
+    <t>22;66</t>
+  </si>
+  <si>
+    <t>04:40</t>
+  </si>
+  <si>
+    <t>68;75</t>
+  </si>
+  <si>
+    <t>04:37</t>
+  </si>
+  <si>
+    <t>04:56</t>
+  </si>
+  <si>
+    <t>24;70</t>
+  </si>
+  <si>
+    <t>04:55</t>
+  </si>
+  <si>
+    <t>05:03</t>
+  </si>
+  <si>
+    <t>57;26</t>
+  </si>
+  <si>
+    <t>05:00</t>
+  </si>
+  <si>
+    <t>05:06</t>
+  </si>
+  <si>
+    <t>58;33</t>
+  </si>
+  <si>
+    <t>05:10</t>
+  </si>
+  <si>
+    <t>44;87</t>
+  </si>
+  <si>
+    <t>05:16</t>
+  </si>
+  <si>
+    <t>05:24</t>
+  </si>
+  <si>
+    <t>49;21</t>
+  </si>
+  <si>
+    <t>05:32</t>
+  </si>
+  <si>
+    <t>52;78</t>
+  </si>
+  <si>
+    <t>06:35</t>
+  </si>
+  <si>
+    <t>06:46</t>
+  </si>
+  <si>
+    <t>53;84</t>
+  </si>
+  <si>
+    <t>07:03</t>
+  </si>
+  <si>
+    <t>66;10</t>
+  </si>
+  <si>
+    <t>07:07</t>
+  </si>
+  <si>
+    <t>07:25</t>
+  </si>
+  <si>
+    <t>39;95</t>
+  </si>
+  <si>
+    <t>07:46</t>
+  </si>
+  <si>
+    <t>07:54</t>
+  </si>
+  <si>
+    <t>64;10</t>
+  </si>
+  <si>
+    <t>08:44</t>
+  </si>
+  <si>
+    <t>09:05</t>
+  </si>
+  <si>
+    <t>42;4</t>
+  </si>
+  <si>
+    <t>09:26</t>
+  </si>
+  <si>
+    <t>55;84</t>
+  </si>
+  <si>
+    <t>09:23</t>
+  </si>
+  <si>
+    <t>09:34</t>
+  </si>
+  <si>
+    <t>29;92</t>
+  </si>
+  <si>
+    <t>09:33</t>
+  </si>
+  <si>
+    <t>65;78</t>
+  </si>
+  <si>
+    <t>10:10</t>
+  </si>
+  <si>
+    <t>10:17</t>
+  </si>
+  <si>
+    <t>43;90</t>
+  </si>
+  <si>
+    <t>10:41</t>
+  </si>
+  <si>
+    <t>27;53</t>
+  </si>
+  <si>
+    <t>11:01</t>
+  </si>
+  <si>
+    <t>11:13</t>
+  </si>
+  <si>
+    <t>75;14</t>
+  </si>
+  <si>
+    <t>11:31</t>
+  </si>
+  <si>
+    <t>11:42</t>
+  </si>
+  <si>
+    <t>78;23</t>
+  </si>
+  <si>
+    <t>11:39</t>
+  </si>
+  <si>
+    <t>11:54</t>
+  </si>
+  <si>
+    <t>37;26</t>
+  </si>
+  <si>
+    <t>12:28</t>
+  </si>
+  <si>
+    <t>12:33</t>
+  </si>
+  <si>
+    <t>86;34</t>
+  </si>
+  <si>
+    <t>12:31</t>
+  </si>
+  <si>
+    <t>12:45</t>
+  </si>
+  <si>
+    <t>69;20</t>
+  </si>
+  <si>
+    <t>13:20</t>
+  </si>
+  <si>
+    <t>13:27</t>
+  </si>
+  <si>
+    <t>91;66</t>
+  </si>
+  <si>
+    <t>65;23</t>
+  </si>
+  <si>
+    <t>13:56</t>
+  </si>
+  <si>
+    <t>14:04</t>
+  </si>
+  <si>
+    <t>77;5</t>
+  </si>
+  <si>
+    <t>15:02</t>
+  </si>
+  <si>
+    <t>15:26</t>
+  </si>
+  <si>
+    <t>55;5</t>
+  </si>
+  <si>
+    <t>15:24</t>
+  </si>
+  <si>
+    <t>15:30</t>
+  </si>
+  <si>
+    <t>56;17</t>
+  </si>
+  <si>
+    <t>15:29</t>
+  </si>
+  <si>
+    <t>15:37</t>
+  </si>
+  <si>
+    <t>36;17</t>
+  </si>
+  <si>
+    <t>15:38</t>
+  </si>
+  <si>
+    <t>15:48</t>
+  </si>
+  <si>
+    <t>30;68</t>
+  </si>
+  <si>
+    <t>15:56</t>
+  </si>
+  <si>
+    <t>65;93</t>
+  </si>
+  <si>
+    <t>16:23</t>
+  </si>
+  <si>
+    <t>16:48</t>
+  </si>
+  <si>
+    <t>63;32</t>
+  </si>
+  <si>
+    <t>16:46</t>
+  </si>
+  <si>
+    <t>17:01</t>
+  </si>
+  <si>
+    <t>37;21</t>
+  </si>
+  <si>
+    <t>17:24</t>
+  </si>
+  <si>
+    <t>82;93</t>
+  </si>
+  <si>
+    <t>17:40</t>
+  </si>
+  <si>
+    <t>17:58</t>
+  </si>
+  <si>
+    <t>71;4</t>
+  </si>
+  <si>
+    <t>18:03</t>
+  </si>
+  <si>
+    <t>18:10</t>
+  </si>
+  <si>
+    <t>14;57</t>
+  </si>
+  <si>
+    <t>18:08</t>
+  </si>
+  <si>
+    <t>18:16</t>
+  </si>
+  <si>
+    <t>31;69</t>
+  </si>
+  <si>
+    <t>18:25</t>
+  </si>
+  <si>
+    <t>18:38</t>
+  </si>
+  <si>
+    <t>6;58</t>
+  </si>
+  <si>
+    <t>55;42</t>
+  </si>
+  <si>
+    <t>55;16</t>
+  </si>
+  <si>
+    <t>19:40</t>
+  </si>
+  <si>
+    <t>19:50</t>
+  </si>
+  <si>
+    <t>13;57</t>
+  </si>
+  <si>
+    <t>19:59</t>
+  </si>
+  <si>
+    <t>20:11</t>
+  </si>
+  <si>
+    <t>5;46</t>
+  </si>
+  <si>
+    <t>20:07</t>
+  </si>
+  <si>
+    <t>20:14</t>
+  </si>
+  <si>
+    <t>36;27</t>
+  </si>
+  <si>
+    <t>20:20</t>
+  </si>
+  <si>
+    <t>20:27</t>
+  </si>
+  <si>
+    <t>14;62</t>
+  </si>
+  <si>
+    <t>20:24</t>
+  </si>
+  <si>
+    <t>20:32</t>
+  </si>
+  <si>
+    <t>36;94</t>
+  </si>
+  <si>
+    <t>20:30</t>
+  </si>
+  <si>
+    <t>20:37</t>
+  </si>
+  <si>
+    <t>32;86</t>
+  </si>
+  <si>
+    <t>20:35</t>
+  </si>
+  <si>
+    <t>20:44</t>
+  </si>
+  <si>
+    <t>41;75</t>
+  </si>
+  <si>
+    <t>21:08</t>
+  </si>
+  <si>
+    <t>21:19</t>
+  </si>
+  <si>
+    <t>29;63</t>
+  </si>
+  <si>
+    <t>21:16</t>
+  </si>
+  <si>
+    <t>21:32</t>
+  </si>
+  <si>
+    <t>21:31</t>
+  </si>
+  <si>
+    <t>21:48</t>
+  </si>
+  <si>
+    <t>28;56</t>
+  </si>
+  <si>
+    <t>21:47</t>
+  </si>
+  <si>
+    <t>87;36</t>
+  </si>
+  <si>
+    <t>22:59</t>
+  </si>
+  <si>
+    <t>23:23</t>
+  </si>
+  <si>
+    <t>5;44</t>
+  </si>
+  <si>
+    <t>23:44</t>
+  </si>
+  <si>
+    <t>24:14</t>
+  </si>
+  <si>
+    <t>76;61</t>
+  </si>
+  <si>
+    <t>24:28</t>
+  </si>
+  <si>
+    <t>25:01</t>
+  </si>
+  <si>
+    <t>27;95</t>
+  </si>
+  <si>
+    <t>25:02</t>
+  </si>
+  <si>
+    <t>25:07</t>
+  </si>
+  <si>
+    <t>9;55</t>
+  </si>
+  <si>
+    <t>25:13</t>
+  </si>
+  <si>
+    <t>25:31</t>
+  </si>
+  <si>
+    <t>74;42</t>
+  </si>
+  <si>
+    <t>25:34</t>
+  </si>
+  <si>
+    <t>25:47</t>
+  </si>
+  <si>
+    <t>37;79</t>
+  </si>
+  <si>
+    <t>26:05</t>
+  </si>
+  <si>
+    <t>26:34</t>
+  </si>
+  <si>
+    <t>92;69</t>
+  </si>
+  <si>
+    <t>27:10</t>
+  </si>
+  <si>
+    <t>27:22</t>
+  </si>
+  <si>
+    <t>27:25</t>
+  </si>
+  <si>
+    <t>27:31</t>
+  </si>
+  <si>
+    <t>33;93</t>
+  </si>
+  <si>
+    <t>27:29</t>
+  </si>
+  <si>
+    <t>27:49</t>
+  </si>
+  <si>
+    <t>35;29</t>
+  </si>
+  <si>
+    <t>27:54</t>
+  </si>
+  <si>
+    <t>28:04</t>
+  </si>
+  <si>
+    <t>80;93</t>
+  </si>
+  <si>
+    <t>28:03</t>
+  </si>
+  <si>
+    <t>28:15</t>
+  </si>
+  <si>
+    <t>84;51</t>
+  </si>
+  <si>
+    <t>28:13</t>
+  </si>
+  <si>
+    <t>28:24</t>
+  </si>
+  <si>
+    <t>45;63</t>
+  </si>
+  <si>
+    <t>46;77</t>
+  </si>
+  <si>
+    <t>28:32</t>
+  </si>
+  <si>
+    <t>28:37</t>
+  </si>
+  <si>
+    <t>71;69</t>
+  </si>
+  <si>
+    <t>28:34</t>
+  </si>
+  <si>
+    <t>28:40</t>
+  </si>
+  <si>
+    <t>69;73</t>
+  </si>
+  <si>
+    <t>29:13</t>
+  </si>
+  <si>
+    <t>79;18</t>
+  </si>
+  <si>
+    <t>29:46</t>
+  </si>
+  <si>
+    <t>29:59</t>
+  </si>
+  <si>
+    <t>92;79</t>
+  </si>
+  <si>
+    <t>30:27</t>
+  </si>
+  <si>
+    <t>30:40</t>
+  </si>
+  <si>
+    <t>41;49</t>
+  </si>
+  <si>
+    <t>31:14</t>
+  </si>
+  <si>
+    <t>31:24</t>
+  </si>
+  <si>
+    <t>31:45</t>
+  </si>
+  <si>
+    <t>31:55</t>
+  </si>
+  <si>
+    <t>94;80</t>
+  </si>
+  <si>
+    <t>32:12</t>
+  </si>
+  <si>
+    <t>60;90</t>
+  </si>
+  <si>
+    <t>32:08</t>
+  </si>
+  <si>
+    <t>32:18</t>
+  </si>
+  <si>
+    <t>82;9</t>
+  </si>
+  <si>
+    <t>32:40</t>
+  </si>
+  <si>
+    <t>32:46</t>
+  </si>
+  <si>
+    <t>44;42</t>
+  </si>
+  <si>
+    <t>32:44</t>
+  </si>
+  <si>
+    <t>32:58</t>
+  </si>
+  <si>
+    <t>52;47</t>
+  </si>
+  <si>
+    <t>32:55</t>
+  </si>
+  <si>
+    <t>33:03</t>
+  </si>
+  <si>
+    <t>62;4</t>
+  </si>
+  <si>
+    <t>33:02</t>
+  </si>
+  <si>
+    <t>33:14</t>
+  </si>
+  <si>
+    <t>33;17</t>
+  </si>
+  <si>
+    <t>33:13</t>
+  </si>
+  <si>
+    <t>33:19</t>
+  </si>
+  <si>
+    <t>33;70</t>
+  </si>
+  <si>
+    <t>33:22</t>
+  </si>
+  <si>
+    <t>33:37</t>
+  </si>
+  <si>
+    <t>76;58</t>
+  </si>
+  <si>
+    <t>33:36</t>
+  </si>
+  <si>
+    <t>60;26</t>
+  </si>
+  <si>
+    <t>34:27</t>
+  </si>
+  <si>
+    <t>72;29</t>
+  </si>
+  <si>
+    <t>34:40</t>
+  </si>
+  <si>
+    <t>34:58</t>
+  </si>
+  <si>
+    <t>34:55</t>
+  </si>
+  <si>
+    <t>35:02</t>
+  </si>
+  <si>
+    <t>8;26</t>
+  </si>
+  <si>
+    <t>35:47</t>
+  </si>
+  <si>
+    <t>35:51</t>
+  </si>
+  <si>
+    <t>28;7</t>
+  </si>
+  <si>
+    <t>35:50</t>
+  </si>
+  <si>
+    <t>35:55</t>
+  </si>
+  <si>
+    <t>43;17</t>
+  </si>
+  <si>
+    <t>35:54</t>
+  </si>
+  <si>
+    <t>36:03</t>
+  </si>
+  <si>
+    <t>36;34</t>
+  </si>
+  <si>
+    <t>36:46</t>
+  </si>
+  <si>
+    <t>36:59</t>
+  </si>
+  <si>
+    <t>80;6</t>
+  </si>
+  <si>
+    <t>37:22</t>
+  </si>
+  <si>
+    <t>37:36</t>
+  </si>
+  <si>
+    <t>91;71</t>
+  </si>
+  <si>
+    <t>37:42</t>
+  </si>
+  <si>
+    <t>60;60</t>
+  </si>
+  <si>
+    <t>37:59</t>
+  </si>
+  <si>
+    <t>69;56</t>
+  </si>
+  <si>
+    <t>38:01</t>
+  </si>
+  <si>
+    <t>38:12</t>
+  </si>
+  <si>
+    <t>57;49</t>
+  </si>
+  <si>
+    <t>38:40</t>
+  </si>
+  <si>
+    <t>73;86</t>
+  </si>
+  <si>
+    <t>38:58</t>
+  </si>
+  <si>
+    <t>39:24</t>
+  </si>
+  <si>
+    <t>30;60</t>
+  </si>
+  <si>
+    <t>40:09</t>
+  </si>
+  <si>
+    <t>88;84</t>
+  </si>
+  <si>
+    <t>40:37</t>
+  </si>
+  <si>
+    <t>94;34</t>
+  </si>
+  <si>
+    <t>41:18</t>
+  </si>
+  <si>
+    <t>41:25</t>
+  </si>
+  <si>
+    <t>65;16</t>
+  </si>
+  <si>
+    <t>ADEPA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/4A_U7duurO8 </t>
   </si>
 </sst>
 </file>
@@ -2262,8 +3099,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C1975CA6-E80E-40A4-A9D5-728F867A63BD}" name="Tabla1" displayName="Tabla1" ref="A1:O178" totalsRowShown="0">
-  <autoFilter ref="A1:O178" xr:uid="{C1975CA6-E80E-40A4-A9D5-728F867A63BD}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C1975CA6-E80E-40A4-A9D5-728F867A63BD}" name="Tabla1" displayName="Tabla1" ref="A1:O282" totalsRowShown="0">
+  <autoFilter ref="A1:O282" xr:uid="{C1975CA6-E80E-40A4-A9D5-728F867A63BD}"/>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{45CCCD5A-AFCF-487D-ADA1-0BFBB6505772}" name="Event"/>
     <tableColumn id="2" xr3:uid="{4A939A0F-B787-4665-B94F-35DE80E0B243}" name="start_time" dataDxfId="2"/>
@@ -2572,7 +3409,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77939FC4-FC73-4262-977F-310955BE7B1D}">
-  <dimension ref="A1:O178"/>
+  <dimension ref="A1:O282"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23.5703125" customWidth="1"/>
@@ -2580,7 +3417,7 @@
     <col min="6" max="6" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="30.28515625" customWidth="1"/>
     <col min="10" max="11" width="16.85546875" customWidth="1"/>
     <col min="12" max="12" width="13.28515625" bestFit="1" customWidth="1"/>
   </cols>
@@ -9470,12 +10307,4108 @@
         <v>55</v>
       </c>
     </row>
+    <row r="179" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A179" t="s">
+        <v>27</v>
+      </c>
+      <c r="B179" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C179" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D179" s="3" t="s">
+        <v>720</v>
+      </c>
+      <c r="E179" t="s">
+        <v>721</v>
+      </c>
+      <c r="F179" t="s">
+        <v>15</v>
+      </c>
+      <c r="H179" t="s">
+        <v>997</v>
+      </c>
+      <c r="I179" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J179" s="1"/>
+      <c r="M179" t="s">
+        <v>7</v>
+      </c>
+      <c r="N179" t="s">
+        <v>50</v>
+      </c>
+      <c r="O179" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="180" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A180" t="s">
+        <v>27</v>
+      </c>
+      <c r="B180" s="3" t="s">
+        <v>722</v>
+      </c>
+      <c r="C180" s="3" t="s">
+        <v>722</v>
+      </c>
+      <c r="D180" s="3" t="s">
+        <v>720</v>
+      </c>
+      <c r="E180" t="s">
+        <v>723</v>
+      </c>
+      <c r="F180" t="s">
+        <v>562</v>
+      </c>
+      <c r="H180" t="s">
+        <v>997</v>
+      </c>
+      <c r="I180" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J180" s="1"/>
+      <c r="M180" t="s">
+        <v>7</v>
+      </c>
+      <c r="N180" t="s">
+        <v>50</v>
+      </c>
+      <c r="O180" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="181" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A181" t="s">
+        <v>27</v>
+      </c>
+      <c r="B181" s="3" t="s">
+        <v>724</v>
+      </c>
+      <c r="C181" s="3" t="s">
+        <v>724</v>
+      </c>
+      <c r="D181" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E181" t="s">
+        <v>725</v>
+      </c>
+      <c r="F181" t="s">
+        <v>15</v>
+      </c>
+      <c r="H181" t="s">
+        <v>997</v>
+      </c>
+      <c r="I181" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J181" s="1"/>
+      <c r="M181" t="s">
+        <v>7</v>
+      </c>
+      <c r="N181" t="s">
+        <v>50</v>
+      </c>
+      <c r="O181" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="182" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A182" t="s">
+        <v>127</v>
+      </c>
+      <c r="B182" s="3" t="s">
+        <v>726</v>
+      </c>
+      <c r="C182" s="3" t="s">
+        <v>726</v>
+      </c>
+      <c r="D182" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="E182" t="s">
+        <v>728</v>
+      </c>
+      <c r="F182" t="s">
+        <v>1</v>
+      </c>
+      <c r="G182" t="s">
+        <v>47</v>
+      </c>
+      <c r="H182" t="s">
+        <v>997</v>
+      </c>
+      <c r="I182" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J182" s="1"/>
+      <c r="M182" t="s">
+        <v>7</v>
+      </c>
+      <c r="N182" t="s">
+        <v>50</v>
+      </c>
+      <c r="O182" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="183" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A183" t="s">
+        <v>122</v>
+      </c>
+      <c r="B183" s="3" t="s">
+        <v>729</v>
+      </c>
+      <c r="C183" s="3" t="s">
+        <v>729</v>
+      </c>
+      <c r="D183" s="3" t="s">
+        <v>730</v>
+      </c>
+      <c r="E183" t="s">
+        <v>731</v>
+      </c>
+      <c r="F183" t="s">
+        <v>20</v>
+      </c>
+      <c r="G183" t="s">
+        <v>46</v>
+      </c>
+      <c r="H183" t="s">
+        <v>997</v>
+      </c>
+      <c r="I183" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J183" s="1"/>
+      <c r="M183" t="s">
+        <v>7</v>
+      </c>
+      <c r="N183" t="s">
+        <v>50</v>
+      </c>
+      <c r="O183" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="184" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A184" t="s">
+        <v>127</v>
+      </c>
+      <c r="B184" s="3" t="s">
+        <v>732</v>
+      </c>
+      <c r="C184" s="3" t="s">
+        <v>732</v>
+      </c>
+      <c r="D184" s="3" t="s">
+        <v>733</v>
+      </c>
+      <c r="E184" t="s">
+        <v>734</v>
+      </c>
+      <c r="F184" t="s">
+        <v>43</v>
+      </c>
+      <c r="G184" t="s">
+        <v>47</v>
+      </c>
+      <c r="H184" t="s">
+        <v>997</v>
+      </c>
+      <c r="I184" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J184" s="1"/>
+      <c r="M184" t="s">
+        <v>7</v>
+      </c>
+      <c r="N184" t="s">
+        <v>50</v>
+      </c>
+      <c r="O184" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="185" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A185" t="s">
+        <v>27</v>
+      </c>
+      <c r="B185" s="3" t="s">
+        <v>735</v>
+      </c>
+      <c r="C185" s="3" t="s">
+        <v>735</v>
+      </c>
+      <c r="D185" s="3" t="s">
+        <v>736</v>
+      </c>
+      <c r="E185" t="s">
+        <v>737</v>
+      </c>
+      <c r="F185" t="s">
+        <v>15</v>
+      </c>
+      <c r="H185" t="s">
+        <v>997</v>
+      </c>
+      <c r="I185" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J185" s="1"/>
+      <c r="M185" t="s">
+        <v>7</v>
+      </c>
+      <c r="N185" t="s">
+        <v>50</v>
+      </c>
+      <c r="O185" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="186" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A186" t="s">
+        <v>127</v>
+      </c>
+      <c r="B186" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C186" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D186" s="3" t="s">
+        <v>738</v>
+      </c>
+      <c r="E186" t="s">
+        <v>739</v>
+      </c>
+      <c r="F186" t="s">
+        <v>43</v>
+      </c>
+      <c r="G186" t="s">
+        <v>45</v>
+      </c>
+      <c r="H186" t="s">
+        <v>997</v>
+      </c>
+      <c r="I186" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J186" s="1"/>
+      <c r="M186" t="s">
+        <v>7</v>
+      </c>
+      <c r="N186" t="s">
+        <v>50</v>
+      </c>
+      <c r="O186" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="187" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A187" t="s">
+        <v>27</v>
+      </c>
+      <c r="B187" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C187" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D187" s="3" t="s">
+        <v>740</v>
+      </c>
+      <c r="E187" t="s">
+        <v>741</v>
+      </c>
+      <c r="F187" t="s">
+        <v>15</v>
+      </c>
+      <c r="H187" t="s">
+        <v>997</v>
+      </c>
+      <c r="I187" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J187" s="1"/>
+      <c r="M187" t="s">
+        <v>7</v>
+      </c>
+      <c r="N187" t="s">
+        <v>50</v>
+      </c>
+      <c r="O187" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="188" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A188" t="s">
+        <v>127</v>
+      </c>
+      <c r="B188" s="3" t="s">
+        <v>742</v>
+      </c>
+      <c r="C188" s="3" t="s">
+        <v>742</v>
+      </c>
+      <c r="D188" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E188" t="s">
+        <v>744</v>
+      </c>
+      <c r="F188" t="s">
+        <v>43</v>
+      </c>
+      <c r="G188" t="s">
+        <v>45</v>
+      </c>
+      <c r="H188" t="s">
+        <v>997</v>
+      </c>
+      <c r="I188" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J188" s="1"/>
+      <c r="M188" t="s">
+        <v>7</v>
+      </c>
+      <c r="N188" t="s">
+        <v>50</v>
+      </c>
+      <c r="O188" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="189" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A189" t="s">
+        <v>122</v>
+      </c>
+      <c r="B189" s="3" t="s">
+        <v>745</v>
+      </c>
+      <c r="C189" s="3" t="s">
+        <v>745</v>
+      </c>
+      <c r="D189" s="3" t="s">
+        <v>746</v>
+      </c>
+      <c r="E189" t="s">
+        <v>747</v>
+      </c>
+      <c r="F189" t="s">
+        <v>20</v>
+      </c>
+      <c r="G189" t="s">
+        <v>46</v>
+      </c>
+      <c r="H189" t="s">
+        <v>997</v>
+      </c>
+      <c r="I189" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J189" s="1"/>
+      <c r="M189" t="s">
+        <v>7</v>
+      </c>
+      <c r="N189" t="s">
+        <v>50</v>
+      </c>
+      <c r="O189" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="190" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A190" t="s">
+        <v>127</v>
+      </c>
+      <c r="B190" s="3" t="s">
+        <v>748</v>
+      </c>
+      <c r="C190" s="3" t="s">
+        <v>748</v>
+      </c>
+      <c r="D190" s="3" t="s">
+        <v>749</v>
+      </c>
+      <c r="E190" t="s">
+        <v>750</v>
+      </c>
+      <c r="F190" t="s">
+        <v>43</v>
+      </c>
+      <c r="G190" t="s">
+        <v>47</v>
+      </c>
+      <c r="H190" t="s">
+        <v>997</v>
+      </c>
+      <c r="I190" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J190" s="1"/>
+      <c r="M190" t="s">
+        <v>7</v>
+      </c>
+      <c r="N190" t="s">
+        <v>50</v>
+      </c>
+      <c r="O190" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="191" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A191" t="s">
+        <v>122</v>
+      </c>
+      <c r="B191" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C191" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D191" s="3" t="s">
+        <v>751</v>
+      </c>
+      <c r="E191" t="s">
+        <v>752</v>
+      </c>
+      <c r="F191" t="s">
+        <v>42</v>
+      </c>
+      <c r="G191" t="s">
+        <v>46</v>
+      </c>
+      <c r="H191" t="s">
+        <v>997</v>
+      </c>
+      <c r="I191" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J191" s="1"/>
+      <c r="M191" t="s">
+        <v>7</v>
+      </c>
+      <c r="N191" t="s">
+        <v>50</v>
+      </c>
+      <c r="O191" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="192" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A192" t="s">
+        <v>127</v>
+      </c>
+      <c r="B192" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="C192" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="D192" s="3" t="s">
+        <v>754</v>
+      </c>
+      <c r="E192" t="s">
+        <v>755</v>
+      </c>
+      <c r="F192" t="s">
+        <v>43</v>
+      </c>
+      <c r="G192" t="s">
+        <v>45</v>
+      </c>
+      <c r="H192" t="s">
+        <v>997</v>
+      </c>
+      <c r="I192" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J192" s="1"/>
+      <c r="M192" t="s">
+        <v>7</v>
+      </c>
+      <c r="N192" t="s">
+        <v>50</v>
+      </c>
+      <c r="O192" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="193" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A193" t="s">
+        <v>14</v>
+      </c>
+      <c r="B193" s="3" t="s">
+        <v>756</v>
+      </c>
+      <c r="C193" s="3" t="s">
+        <v>756</v>
+      </c>
+      <c r="D193" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E193" t="s">
+        <v>757</v>
+      </c>
+      <c r="F193" t="s">
+        <v>42</v>
+      </c>
+      <c r="G193" t="s">
+        <v>48</v>
+      </c>
+      <c r="H193" t="s">
+        <v>997</v>
+      </c>
+      <c r="I193" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J193" s="1"/>
+      <c r="M193" t="s">
+        <v>7</v>
+      </c>
+      <c r="N193" t="s">
+        <v>50</v>
+      </c>
+      <c r="O193" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="194" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A194" t="s">
+        <v>2</v>
+      </c>
+      <c r="B194" s="3" t="s">
+        <v>758</v>
+      </c>
+      <c r="C194" s="3" t="s">
+        <v>758</v>
+      </c>
+      <c r="D194" s="3" t="s">
+        <v>759</v>
+      </c>
+      <c r="E194" t="s">
+        <v>760</v>
+      </c>
+      <c r="F194" t="s">
+        <v>17</v>
+      </c>
+      <c r="G194" t="s">
+        <v>47</v>
+      </c>
+      <c r="H194" t="s">
+        <v>997</v>
+      </c>
+      <c r="I194" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J194" s="1"/>
+      <c r="M194" t="s">
+        <v>7</v>
+      </c>
+      <c r="N194" t="s">
+        <v>50</v>
+      </c>
+      <c r="O194" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="195" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A195" t="s">
+        <v>122</v>
+      </c>
+      <c r="B195" s="3" t="s">
+        <v>759</v>
+      </c>
+      <c r="C195" s="3" t="s">
+        <v>759</v>
+      </c>
+      <c r="D195" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="E195" t="s">
+        <v>762</v>
+      </c>
+      <c r="F195" t="s">
+        <v>20</v>
+      </c>
+      <c r="G195" t="s">
+        <v>287</v>
+      </c>
+      <c r="H195" t="s">
+        <v>997</v>
+      </c>
+      <c r="I195" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J195" s="1"/>
+      <c r="M195" t="s">
+        <v>7</v>
+      </c>
+      <c r="N195" t="s">
+        <v>50</v>
+      </c>
+      <c r="O195" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="196" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A196" t="s">
+        <v>2</v>
+      </c>
+      <c r="B196" s="3" t="s">
+        <v>763</v>
+      </c>
+      <c r="C196" s="3" t="s">
+        <v>763</v>
+      </c>
+      <c r="D196" s="3" t="s">
+        <v>764</v>
+      </c>
+      <c r="E196" t="s">
+        <v>765</v>
+      </c>
+      <c r="F196" t="s">
+        <v>17</v>
+      </c>
+      <c r="G196" t="s">
+        <v>49</v>
+      </c>
+      <c r="H196" t="s">
+        <v>997</v>
+      </c>
+      <c r="I196" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J196" s="1"/>
+      <c r="M196" t="s">
+        <v>7</v>
+      </c>
+      <c r="N196" t="s">
+        <v>50</v>
+      </c>
+      <c r="O196" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="197" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A197" t="s">
+        <v>14</v>
+      </c>
+      <c r="B197" s="3" t="s">
+        <v>766</v>
+      </c>
+      <c r="C197" s="3" t="s">
+        <v>766</v>
+      </c>
+      <c r="D197" s="3" t="s">
+        <v>767</v>
+      </c>
+      <c r="E197" t="s">
+        <v>768</v>
+      </c>
+      <c r="F197" t="s">
+        <v>20</v>
+      </c>
+      <c r="G197" t="s">
+        <v>48</v>
+      </c>
+      <c r="H197" t="s">
+        <v>997</v>
+      </c>
+      <c r="I197" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J197" s="1"/>
+      <c r="M197" t="s">
+        <v>7</v>
+      </c>
+      <c r="N197" t="s">
+        <v>50</v>
+      </c>
+      <c r="O197" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="198" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A198" t="s">
+        <v>2</v>
+      </c>
+      <c r="B198" s="3" t="s">
+        <v>769</v>
+      </c>
+      <c r="C198" s="3" t="s">
+        <v>769</v>
+      </c>
+      <c r="D198" s="3" t="s">
+        <v>770</v>
+      </c>
+      <c r="E198" t="s">
+        <v>771</v>
+      </c>
+      <c r="F198" t="s">
+        <v>17</v>
+      </c>
+      <c r="G198" t="s">
+        <v>45</v>
+      </c>
+      <c r="H198" t="s">
+        <v>997</v>
+      </c>
+      <c r="I198" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J198" s="1"/>
+      <c r="M198" t="s">
+        <v>7</v>
+      </c>
+      <c r="N198" t="s">
+        <v>50</v>
+      </c>
+      <c r="O198" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="199" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A199" t="s">
+        <v>14</v>
+      </c>
+      <c r="B199" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="C199" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="D199" s="3" t="s">
+        <v>772</v>
+      </c>
+      <c r="E199" t="s">
+        <v>773</v>
+      </c>
+      <c r="G199" t="s">
+        <v>46</v>
+      </c>
+      <c r="H199" t="s">
+        <v>997</v>
+      </c>
+      <c r="I199" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J199" s="1"/>
+      <c r="M199" t="s">
+        <v>7</v>
+      </c>
+      <c r="N199" t="s">
+        <v>50</v>
+      </c>
+      <c r="O199" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="200" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A200" t="s">
+        <v>127</v>
+      </c>
+      <c r="B200" s="3" t="s">
+        <v>774</v>
+      </c>
+      <c r="C200" s="3" t="s">
+        <v>774</v>
+      </c>
+      <c r="D200" s="3" t="s">
+        <v>775</v>
+      </c>
+      <c r="E200" t="s">
+        <v>776</v>
+      </c>
+      <c r="F200" t="s">
+        <v>43</v>
+      </c>
+      <c r="G200" t="s">
+        <v>45</v>
+      </c>
+      <c r="H200" t="s">
+        <v>997</v>
+      </c>
+      <c r="I200" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J200" s="1"/>
+      <c r="M200" t="s">
+        <v>7</v>
+      </c>
+      <c r="N200" t="s">
+        <v>50</v>
+      </c>
+      <c r="O200" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="201" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A201" t="s">
+        <v>122</v>
+      </c>
+      <c r="B201" s="3" t="s">
+        <v>777</v>
+      </c>
+      <c r="C201" s="3" t="s">
+        <v>777</v>
+      </c>
+      <c r="D201" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E201" t="s">
+        <v>778</v>
+      </c>
+      <c r="F201" t="s">
+        <v>20</v>
+      </c>
+      <c r="G201" t="s">
+        <v>48</v>
+      </c>
+      <c r="H201" t="s">
+        <v>997</v>
+      </c>
+      <c r="I201" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J201" s="1"/>
+      <c r="M201" t="s">
+        <v>7</v>
+      </c>
+      <c r="N201" t="s">
+        <v>50</v>
+      </c>
+      <c r="O201" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="202" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A202" t="s">
+        <v>27</v>
+      </c>
+      <c r="B202" s="3" t="s">
+        <v>779</v>
+      </c>
+      <c r="C202" s="3" t="s">
+        <v>779</v>
+      </c>
+      <c r="D202" s="3" t="s">
+        <v>780</v>
+      </c>
+      <c r="E202" t="s">
+        <v>781</v>
+      </c>
+      <c r="F202" t="s">
+        <v>15</v>
+      </c>
+      <c r="H202" t="s">
+        <v>997</v>
+      </c>
+      <c r="I202" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J202" s="1"/>
+      <c r="M202" t="s">
+        <v>7</v>
+      </c>
+      <c r="N202" t="s">
+        <v>50</v>
+      </c>
+      <c r="O202" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="203" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A203" t="s">
+        <v>127</v>
+      </c>
+      <c r="B203" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="C203" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="D203" s="3" t="s">
+        <v>782</v>
+      </c>
+      <c r="E203" t="s">
+        <v>783</v>
+      </c>
+      <c r="F203" t="s">
+        <v>43</v>
+      </c>
+      <c r="G203" t="s">
+        <v>45</v>
+      </c>
+      <c r="H203" t="s">
+        <v>997</v>
+      </c>
+      <c r="I203" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J203" s="1"/>
+      <c r="M203" t="s">
+        <v>7</v>
+      </c>
+      <c r="N203" t="s">
+        <v>50</v>
+      </c>
+      <c r="O203" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="204" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A204" t="s">
+        <v>2</v>
+      </c>
+      <c r="B204" s="3" t="s">
+        <v>784</v>
+      </c>
+      <c r="C204" s="3" t="s">
+        <v>784</v>
+      </c>
+      <c r="D204" s="3" t="s">
+        <v>785</v>
+      </c>
+      <c r="E204" t="s">
+        <v>786</v>
+      </c>
+      <c r="F204" t="s">
+        <v>17</v>
+      </c>
+      <c r="G204" t="s">
+        <v>47</v>
+      </c>
+      <c r="H204" t="s">
+        <v>997</v>
+      </c>
+      <c r="I204" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J204" s="1"/>
+      <c r="M204" t="s">
+        <v>7</v>
+      </c>
+      <c r="N204" t="s">
+        <v>50</v>
+      </c>
+      <c r="O204" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="205" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A205" t="s">
+        <v>27</v>
+      </c>
+      <c r="B205" s="3" t="s">
+        <v>787</v>
+      </c>
+      <c r="C205" s="3" t="s">
+        <v>787</v>
+      </c>
+      <c r="D205" s="3" t="s">
+        <v>788</v>
+      </c>
+      <c r="E205" t="s">
+        <v>789</v>
+      </c>
+      <c r="F205" t="s">
+        <v>15</v>
+      </c>
+      <c r="H205" t="s">
+        <v>997</v>
+      </c>
+      <c r="I205" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J205" s="1"/>
+      <c r="M205" t="s">
+        <v>7</v>
+      </c>
+      <c r="N205" t="s">
+        <v>50</v>
+      </c>
+      <c r="O205" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="206" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A206" t="s">
+        <v>127</v>
+      </c>
+      <c r="B206" s="3" t="s">
+        <v>790</v>
+      </c>
+      <c r="C206" s="3" t="s">
+        <v>790</v>
+      </c>
+      <c r="D206" s="3" t="s">
+        <v>791</v>
+      </c>
+      <c r="E206" t="s">
+        <v>792</v>
+      </c>
+      <c r="F206" t="s">
+        <v>43</v>
+      </c>
+      <c r="G206" t="s">
+        <v>49</v>
+      </c>
+      <c r="H206" t="s">
+        <v>997</v>
+      </c>
+      <c r="I206" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J206" s="1"/>
+      <c r="M206" t="s">
+        <v>7</v>
+      </c>
+      <c r="N206" t="s">
+        <v>50</v>
+      </c>
+      <c r="O206" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="207" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A207" t="s">
+        <v>14</v>
+      </c>
+      <c r="B207" s="3" t="s">
+        <v>793</v>
+      </c>
+      <c r="C207" s="3" t="s">
+        <v>793</v>
+      </c>
+      <c r="D207" s="3" t="s">
+        <v>794</v>
+      </c>
+      <c r="E207" t="s">
+        <v>795</v>
+      </c>
+      <c r="F207" t="s">
+        <v>42</v>
+      </c>
+      <c r="G207" t="s">
+        <v>46</v>
+      </c>
+      <c r="H207" t="s">
+        <v>997</v>
+      </c>
+      <c r="I207" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J207" s="1"/>
+      <c r="M207" t="s">
+        <v>7</v>
+      </c>
+      <c r="N207" t="s">
+        <v>50</v>
+      </c>
+      <c r="O207" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="208" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A208" t="s">
+        <v>127</v>
+      </c>
+      <c r="B208" s="3" t="s">
+        <v>796</v>
+      </c>
+      <c r="C208" s="3" t="s">
+        <v>796</v>
+      </c>
+      <c r="D208" s="3" t="s">
+        <v>797</v>
+      </c>
+      <c r="E208" t="s">
+        <v>798</v>
+      </c>
+      <c r="F208" t="s">
+        <v>43</v>
+      </c>
+      <c r="G208" t="s">
+        <v>49</v>
+      </c>
+      <c r="H208" t="s">
+        <v>997</v>
+      </c>
+      <c r="I208" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J208" s="1"/>
+      <c r="M208" t="s">
+        <v>7</v>
+      </c>
+      <c r="N208" t="s">
+        <v>50</v>
+      </c>
+      <c r="O208" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="209" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A209" t="s">
+        <v>32</v>
+      </c>
+      <c r="B209" s="3" t="s">
+        <v>799</v>
+      </c>
+      <c r="C209" s="3" t="s">
+        <v>799</v>
+      </c>
+      <c r="D209" s="3" t="s">
+        <v>800</v>
+      </c>
+      <c r="E209" t="s">
+        <v>801</v>
+      </c>
+      <c r="F209" t="s">
+        <v>511</v>
+      </c>
+      <c r="H209" t="s">
+        <v>997</v>
+      </c>
+      <c r="I209" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J209" s="1"/>
+      <c r="M209" t="s">
+        <v>7</v>
+      </c>
+      <c r="N209" t="s">
+        <v>50</v>
+      </c>
+      <c r="O209" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="210" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A210" t="s">
+        <v>122</v>
+      </c>
+      <c r="B210" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="C210" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="D210" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="E210" t="s">
+        <v>802</v>
+      </c>
+      <c r="F210" t="s">
+        <v>21</v>
+      </c>
+      <c r="G210" t="s">
+        <v>48</v>
+      </c>
+      <c r="H210" t="s">
+        <v>997</v>
+      </c>
+      <c r="I210" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J210" s="1"/>
+      <c r="M210" t="s">
+        <v>7</v>
+      </c>
+      <c r="N210" t="s">
+        <v>50</v>
+      </c>
+      <c r="O210" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="211" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A211" t="s">
+        <v>2</v>
+      </c>
+      <c r="B211" s="3" t="s">
+        <v>803</v>
+      </c>
+      <c r="C211" s="3" t="s">
+        <v>803</v>
+      </c>
+      <c r="D211" s="3" t="s">
+        <v>804</v>
+      </c>
+      <c r="E211" t="s">
+        <v>805</v>
+      </c>
+      <c r="F211" t="s">
+        <v>17</v>
+      </c>
+      <c r="G211" t="s">
+        <v>45</v>
+      </c>
+      <c r="H211" t="s">
+        <v>997</v>
+      </c>
+      <c r="I211" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J211" s="1"/>
+      <c r="M211" t="s">
+        <v>7</v>
+      </c>
+      <c r="N211" t="s">
+        <v>50</v>
+      </c>
+      <c r="O211" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="212" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A212" t="s">
+        <v>2</v>
+      </c>
+      <c r="B212" s="3" t="s">
+        <v>806</v>
+      </c>
+      <c r="C212" s="3" t="s">
+        <v>806</v>
+      </c>
+      <c r="D212" s="3" t="s">
+        <v>807</v>
+      </c>
+      <c r="E212" t="s">
+        <v>808</v>
+      </c>
+      <c r="F212" t="s">
+        <v>17</v>
+      </c>
+      <c r="G212" t="s">
+        <v>47</v>
+      </c>
+      <c r="H212" t="s">
+        <v>997</v>
+      </c>
+      <c r="I212" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J212" s="1"/>
+      <c r="M212" t="s">
+        <v>7</v>
+      </c>
+      <c r="N212" t="s">
+        <v>50</v>
+      </c>
+      <c r="O212" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="213" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A213" t="s">
+        <v>122</v>
+      </c>
+      <c r="B213" s="3" t="s">
+        <v>809</v>
+      </c>
+      <c r="C213" s="3" t="s">
+        <v>809</v>
+      </c>
+      <c r="D213" s="3" t="s">
+        <v>810</v>
+      </c>
+      <c r="E213" t="s">
+        <v>811</v>
+      </c>
+      <c r="F213" t="s">
+        <v>21</v>
+      </c>
+      <c r="G213" t="s">
+        <v>46</v>
+      </c>
+      <c r="H213" t="s">
+        <v>997</v>
+      </c>
+      <c r="I213" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J213" s="1"/>
+      <c r="M213" t="s">
+        <v>7</v>
+      </c>
+      <c r="N213" t="s">
+        <v>50</v>
+      </c>
+      <c r="O213" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="214" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A214" t="s">
+        <v>127</v>
+      </c>
+      <c r="B214" s="3" t="s">
+        <v>812</v>
+      </c>
+      <c r="C214" s="3" t="s">
+        <v>812</v>
+      </c>
+      <c r="D214" s="3" t="s">
+        <v>813</v>
+      </c>
+      <c r="E214" t="s">
+        <v>814</v>
+      </c>
+      <c r="F214" t="s">
+        <v>1</v>
+      </c>
+      <c r="G214" t="s">
+        <v>44</v>
+      </c>
+      <c r="H214" t="s">
+        <v>997</v>
+      </c>
+      <c r="I214" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J214" s="1"/>
+      <c r="M214" t="s">
+        <v>7</v>
+      </c>
+      <c r="N214" t="s">
+        <v>50</v>
+      </c>
+      <c r="O214" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="215" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A215" t="s">
+        <v>2</v>
+      </c>
+      <c r="B215" s="3" t="s">
+        <v>815</v>
+      </c>
+      <c r="C215" s="3" t="s">
+        <v>815</v>
+      </c>
+      <c r="D215" s="3" t="s">
+        <v>816</v>
+      </c>
+      <c r="E215" t="s">
+        <v>817</v>
+      </c>
+      <c r="F215" t="s">
+        <v>17</v>
+      </c>
+      <c r="G215" t="s">
+        <v>44</v>
+      </c>
+      <c r="H215" t="s">
+        <v>997</v>
+      </c>
+      <c r="I215" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J215" s="1"/>
+      <c r="M215" t="s">
+        <v>7</v>
+      </c>
+      <c r="N215" t="s">
+        <v>50</v>
+      </c>
+      <c r="O215" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="216" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A216" t="s">
+        <v>2</v>
+      </c>
+      <c r="B216" s="3" t="s">
+        <v>818</v>
+      </c>
+      <c r="C216" s="3" t="s">
+        <v>818</v>
+      </c>
+      <c r="D216" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="E216" t="s">
+        <v>819</v>
+      </c>
+      <c r="F216" t="s">
+        <v>17</v>
+      </c>
+      <c r="G216" t="s">
+        <v>49</v>
+      </c>
+      <c r="H216" t="s">
+        <v>997</v>
+      </c>
+      <c r="I216" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J216" s="1"/>
+      <c r="M216" t="s">
+        <v>7</v>
+      </c>
+      <c r="N216" t="s">
+        <v>50</v>
+      </c>
+      <c r="O216" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="217" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A217" t="s">
+        <v>14</v>
+      </c>
+      <c r="B217" s="3" t="s">
+        <v>820</v>
+      </c>
+      <c r="C217" s="3" t="s">
+        <v>820</v>
+      </c>
+      <c r="D217" s="3" t="s">
+        <v>821</v>
+      </c>
+      <c r="E217" t="s">
+        <v>822</v>
+      </c>
+      <c r="G217" t="s">
+        <v>46</v>
+      </c>
+      <c r="H217" t="s">
+        <v>997</v>
+      </c>
+      <c r="I217" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J217" s="1"/>
+      <c r="M217" t="s">
+        <v>7</v>
+      </c>
+      <c r="N217" t="s">
+        <v>50</v>
+      </c>
+      <c r="O217" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="218" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A218" t="s">
+        <v>127</v>
+      </c>
+      <c r="B218" s="3" t="s">
+        <v>823</v>
+      </c>
+      <c r="C218" s="3" t="s">
+        <v>823</v>
+      </c>
+      <c r="D218" s="3" t="s">
+        <v>824</v>
+      </c>
+      <c r="E218" t="s">
+        <v>825</v>
+      </c>
+      <c r="F218" t="s">
+        <v>43</v>
+      </c>
+      <c r="G218" t="s">
+        <v>47</v>
+      </c>
+      <c r="H218" t="s">
+        <v>997</v>
+      </c>
+      <c r="I218" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J218" s="1"/>
+      <c r="M218" t="s">
+        <v>7</v>
+      </c>
+      <c r="N218" t="s">
+        <v>50</v>
+      </c>
+      <c r="O218" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="219" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A219" t="s">
+        <v>122</v>
+      </c>
+      <c r="B219" s="3" t="s">
+        <v>826</v>
+      </c>
+      <c r="C219" s="3" t="s">
+        <v>826</v>
+      </c>
+      <c r="D219" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="E219" t="s">
+        <v>827</v>
+      </c>
+      <c r="G219" t="s">
+        <v>48</v>
+      </c>
+      <c r="H219" t="s">
+        <v>997</v>
+      </c>
+      <c r="I219" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J219" s="1"/>
+      <c r="M219" t="s">
+        <v>7</v>
+      </c>
+      <c r="N219" t="s">
+        <v>50</v>
+      </c>
+      <c r="O219" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="220" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A220" t="s">
+        <v>14</v>
+      </c>
+      <c r="B220" s="3" t="s">
+        <v>828</v>
+      </c>
+      <c r="C220" s="3" t="s">
+        <v>828</v>
+      </c>
+      <c r="D220" s="3" t="s">
+        <v>829</v>
+      </c>
+      <c r="E220" t="s">
+        <v>830</v>
+      </c>
+      <c r="F220" t="s">
+        <v>20</v>
+      </c>
+      <c r="G220" t="s">
+        <v>287</v>
+      </c>
+      <c r="H220" t="s">
+        <v>997</v>
+      </c>
+      <c r="I220" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J220" s="1"/>
+      <c r="M220" t="s">
+        <v>7</v>
+      </c>
+      <c r="N220" t="s">
+        <v>50</v>
+      </c>
+      <c r="O220" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="221" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A221" t="s">
+        <v>2</v>
+      </c>
+      <c r="B221" s="3" t="s">
+        <v>831</v>
+      </c>
+      <c r="C221" s="3" t="s">
+        <v>831</v>
+      </c>
+      <c r="D221" s="3" t="s">
+        <v>832</v>
+      </c>
+      <c r="E221" t="s">
+        <v>833</v>
+      </c>
+      <c r="F221" t="s">
+        <v>3</v>
+      </c>
+      <c r="G221" t="s">
+        <v>47</v>
+      </c>
+      <c r="H221" t="s">
+        <v>997</v>
+      </c>
+      <c r="I221" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J221" s="1"/>
+      <c r="M221" t="s">
+        <v>7</v>
+      </c>
+      <c r="N221" t="s">
+        <v>50</v>
+      </c>
+      <c r="O221" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="222" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A222" t="s">
+        <v>122</v>
+      </c>
+      <c r="B222" s="3" t="s">
+        <v>834</v>
+      </c>
+      <c r="C222" s="3" t="s">
+        <v>834</v>
+      </c>
+      <c r="D222" s="3" t="s">
+        <v>835</v>
+      </c>
+      <c r="E222" t="s">
+        <v>836</v>
+      </c>
+      <c r="F222" t="s">
+        <v>20</v>
+      </c>
+      <c r="G222" t="s">
+        <v>419</v>
+      </c>
+      <c r="H222" t="s">
+        <v>997</v>
+      </c>
+      <c r="I222" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J222" s="1"/>
+      <c r="M222" t="s">
+        <v>7</v>
+      </c>
+      <c r="N222" t="s">
+        <v>50</v>
+      </c>
+      <c r="O222" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="223" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A223" t="s">
+        <v>2</v>
+      </c>
+      <c r="B223" s="3" t="s">
+        <v>837</v>
+      </c>
+      <c r="C223" s="3" t="s">
+        <v>837</v>
+      </c>
+      <c r="D223" s="3" t="s">
+        <v>838</v>
+      </c>
+      <c r="E223" t="s">
+        <v>839</v>
+      </c>
+      <c r="F223" t="s">
+        <v>17</v>
+      </c>
+      <c r="G223" t="s">
+        <v>47</v>
+      </c>
+      <c r="H223" t="s">
+        <v>997</v>
+      </c>
+      <c r="I223" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J223" s="1"/>
+      <c r="M223" t="s">
+        <v>7</v>
+      </c>
+      <c r="N223" t="s">
+        <v>50</v>
+      </c>
+      <c r="O223" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="224" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A224" t="s">
+        <v>122</v>
+      </c>
+      <c r="B224" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="C224" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="D224" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="E224" t="s">
+        <v>840</v>
+      </c>
+      <c r="F224" t="s">
+        <v>20</v>
+      </c>
+      <c r="G224" t="s">
+        <v>287</v>
+      </c>
+      <c r="H224" t="s">
+        <v>997</v>
+      </c>
+      <c r="I224" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J224" s="1"/>
+      <c r="M224" t="s">
+        <v>7</v>
+      </c>
+      <c r="N224" t="s">
+        <v>50</v>
+      </c>
+      <c r="O224" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="225" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A225" t="s">
+        <v>14</v>
+      </c>
+      <c r="B225" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="C225" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="D225" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="E225" t="s">
+        <v>841</v>
+      </c>
+      <c r="F225" t="s">
+        <v>20</v>
+      </c>
+      <c r="G225" t="s">
+        <v>287</v>
+      </c>
+      <c r="H225" t="s">
+        <v>997</v>
+      </c>
+      <c r="I225" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J225" s="1"/>
+      <c r="M225" t="s">
+        <v>7</v>
+      </c>
+      <c r="N225" t="s">
+        <v>50</v>
+      </c>
+      <c r="O225" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="226" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A226" t="s">
+        <v>27</v>
+      </c>
+      <c r="B226" s="3" t="s">
+        <v>842</v>
+      </c>
+      <c r="C226" s="3" t="s">
+        <v>842</v>
+      </c>
+      <c r="D226" s="3" t="s">
+        <v>843</v>
+      </c>
+      <c r="E226" t="s">
+        <v>844</v>
+      </c>
+      <c r="F226" t="s">
+        <v>562</v>
+      </c>
+      <c r="H226" t="s">
+        <v>997</v>
+      </c>
+      <c r="I226" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J226" s="1"/>
+      <c r="M226" t="s">
+        <v>7</v>
+      </c>
+      <c r="N226" t="s">
+        <v>50</v>
+      </c>
+      <c r="O226" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="227" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A227" t="s">
+        <v>2</v>
+      </c>
+      <c r="B227" s="3" t="s">
+        <v>845</v>
+      </c>
+      <c r="C227" s="3" t="s">
+        <v>845</v>
+      </c>
+      <c r="D227" s="3" t="s">
+        <v>846</v>
+      </c>
+      <c r="E227" t="s">
+        <v>847</v>
+      </c>
+      <c r="F227" t="s">
+        <v>17</v>
+      </c>
+      <c r="G227" t="s">
+        <v>47</v>
+      </c>
+      <c r="H227" t="s">
+        <v>997</v>
+      </c>
+      <c r="I227" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J227" s="1"/>
+      <c r="M227" t="s">
+        <v>7</v>
+      </c>
+      <c r="N227" t="s">
+        <v>50</v>
+      </c>
+      <c r="O227" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="228" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A228" t="s">
+        <v>122</v>
+      </c>
+      <c r="B228" s="3" t="s">
+        <v>848</v>
+      </c>
+      <c r="C228" s="3" t="s">
+        <v>848</v>
+      </c>
+      <c r="D228" s="3" t="s">
+        <v>849</v>
+      </c>
+      <c r="E228" t="s">
+        <v>850</v>
+      </c>
+      <c r="G228" t="s">
+        <v>419</v>
+      </c>
+      <c r="H228" t="s">
+        <v>997</v>
+      </c>
+      <c r="I228" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J228" s="1"/>
+      <c r="M228" t="s">
+        <v>7</v>
+      </c>
+      <c r="N228" t="s">
+        <v>50</v>
+      </c>
+      <c r="O228" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="229" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A229" t="s">
+        <v>2</v>
+      </c>
+      <c r="B229" s="3" t="s">
+        <v>851</v>
+      </c>
+      <c r="C229" s="3" t="s">
+        <v>851</v>
+      </c>
+      <c r="D229" s="3" t="s">
+        <v>852</v>
+      </c>
+      <c r="E229" t="s">
+        <v>853</v>
+      </c>
+      <c r="F229" t="s">
+        <v>3</v>
+      </c>
+      <c r="G229" t="s">
+        <v>47</v>
+      </c>
+      <c r="H229" t="s">
+        <v>997</v>
+      </c>
+      <c r="I229" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J229" s="1"/>
+      <c r="M229" t="s">
+        <v>7</v>
+      </c>
+      <c r="N229" t="s">
+        <v>50</v>
+      </c>
+      <c r="O229" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="230" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A230" t="s">
+        <v>122</v>
+      </c>
+      <c r="B230" s="3" t="s">
+        <v>854</v>
+      </c>
+      <c r="C230" s="3" t="s">
+        <v>854</v>
+      </c>
+      <c r="D230" s="3" t="s">
+        <v>855</v>
+      </c>
+      <c r="E230" t="s">
+        <v>856</v>
+      </c>
+      <c r="F230" t="s">
+        <v>20</v>
+      </c>
+      <c r="G230" t="s">
+        <v>46</v>
+      </c>
+      <c r="H230" t="s">
+        <v>997</v>
+      </c>
+      <c r="I230" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J230" s="1"/>
+      <c r="M230" t="s">
+        <v>7</v>
+      </c>
+      <c r="N230" t="s">
+        <v>50</v>
+      </c>
+      <c r="O230" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="231" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A231" t="s">
+        <v>127</v>
+      </c>
+      <c r="B231" s="3" t="s">
+        <v>857</v>
+      </c>
+      <c r="C231" s="3" t="s">
+        <v>857</v>
+      </c>
+      <c r="D231" s="3" t="s">
+        <v>858</v>
+      </c>
+      <c r="E231" t="s">
+        <v>859</v>
+      </c>
+      <c r="F231" t="s">
+        <v>43</v>
+      </c>
+      <c r="G231" t="s">
+        <v>47</v>
+      </c>
+      <c r="H231" t="s">
+        <v>997</v>
+      </c>
+      <c r="I231" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J231" s="1"/>
+      <c r="M231" t="s">
+        <v>7</v>
+      </c>
+      <c r="N231" t="s">
+        <v>50</v>
+      </c>
+      <c r="O231" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="232" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A232" t="s">
+        <v>122</v>
+      </c>
+      <c r="B232" s="3" t="s">
+        <v>860</v>
+      </c>
+      <c r="C232" s="3" t="s">
+        <v>860</v>
+      </c>
+      <c r="D232" s="3" t="s">
+        <v>861</v>
+      </c>
+      <c r="E232" t="s">
+        <v>862</v>
+      </c>
+      <c r="F232" t="s">
+        <v>21</v>
+      </c>
+      <c r="G232" t="s">
+        <v>419</v>
+      </c>
+      <c r="H232" t="s">
+        <v>997</v>
+      </c>
+      <c r="I232" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J232" s="1"/>
+      <c r="M232" t="s">
+        <v>7</v>
+      </c>
+      <c r="N232" t="s">
+        <v>50</v>
+      </c>
+      <c r="O232" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="233" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A233" t="s">
+        <v>32</v>
+      </c>
+      <c r="B233" s="3" t="s">
+        <v>863</v>
+      </c>
+      <c r="C233" s="3" t="s">
+        <v>863</v>
+      </c>
+      <c r="D233" s="3" t="s">
+        <v>864</v>
+      </c>
+      <c r="E233" t="s">
+        <v>865</v>
+      </c>
+      <c r="F233" t="s">
+        <v>4</v>
+      </c>
+      <c r="H233" t="s">
+        <v>997</v>
+      </c>
+      <c r="I233" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J233" s="1"/>
+      <c r="M233" t="s">
+        <v>7</v>
+      </c>
+      <c r="N233" t="s">
+        <v>50</v>
+      </c>
+      <c r="O233" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="234" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A234" t="s">
+        <v>122</v>
+      </c>
+      <c r="B234" s="3" t="s">
+        <v>866</v>
+      </c>
+      <c r="C234" s="3" t="s">
+        <v>866</v>
+      </c>
+      <c r="D234" s="3" t="s">
+        <v>867</v>
+      </c>
+      <c r="E234" t="s">
+        <v>264</v>
+      </c>
+      <c r="F234" t="s">
+        <v>21</v>
+      </c>
+      <c r="G234" t="s">
+        <v>46</v>
+      </c>
+      <c r="H234" t="s">
+        <v>997</v>
+      </c>
+      <c r="I234" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J234" s="1"/>
+      <c r="M234" t="s">
+        <v>7</v>
+      </c>
+      <c r="N234" t="s">
+        <v>50</v>
+      </c>
+      <c r="O234" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="235" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A235" t="s">
+        <v>127</v>
+      </c>
+      <c r="B235" s="3" t="s">
+        <v>868</v>
+      </c>
+      <c r="C235" s="3" t="s">
+        <v>868</v>
+      </c>
+      <c r="D235" s="3" t="s">
+        <v>869</v>
+      </c>
+      <c r="E235" t="s">
+        <v>870</v>
+      </c>
+      <c r="F235" t="s">
+        <v>43</v>
+      </c>
+      <c r="G235" t="s">
+        <v>45</v>
+      </c>
+      <c r="H235" t="s">
+        <v>997</v>
+      </c>
+      <c r="I235" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J235" s="1"/>
+      <c r="M235" t="s">
+        <v>7</v>
+      </c>
+      <c r="N235" t="s">
+        <v>50</v>
+      </c>
+      <c r="O235" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="236" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A236" t="s">
+        <v>122</v>
+      </c>
+      <c r="B236" s="3" t="s">
+        <v>871</v>
+      </c>
+      <c r="C236" s="3" t="s">
+        <v>871</v>
+      </c>
+      <c r="D236" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="E236" t="s">
+        <v>872</v>
+      </c>
+      <c r="F236" t="s">
+        <v>21</v>
+      </c>
+      <c r="G236" t="s">
+        <v>48</v>
+      </c>
+      <c r="H236" t="s">
+        <v>997</v>
+      </c>
+      <c r="I236" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J236" s="1"/>
+      <c r="M236" t="s">
+        <v>7</v>
+      </c>
+      <c r="N236" t="s">
+        <v>50</v>
+      </c>
+      <c r="O236" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="237" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A237" t="s">
+        <v>2</v>
+      </c>
+      <c r="B237" s="3" t="s">
+        <v>873</v>
+      </c>
+      <c r="C237" s="3" t="s">
+        <v>873</v>
+      </c>
+      <c r="D237" s="3" t="s">
+        <v>874</v>
+      </c>
+      <c r="E237" t="s">
+        <v>875</v>
+      </c>
+      <c r="F237" t="s">
+        <v>3</v>
+      </c>
+      <c r="G237" t="s">
+        <v>45</v>
+      </c>
+      <c r="H237" t="s">
+        <v>997</v>
+      </c>
+      <c r="I237" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J237" s="1"/>
+      <c r="M237" t="s">
+        <v>7</v>
+      </c>
+      <c r="N237" t="s">
+        <v>50</v>
+      </c>
+      <c r="O237" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="238" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A238" t="s">
+        <v>14</v>
+      </c>
+      <c r="B238" s="3" t="s">
+        <v>876</v>
+      </c>
+      <c r="C238" s="3" t="s">
+        <v>876</v>
+      </c>
+      <c r="D238" s="3" t="s">
+        <v>877</v>
+      </c>
+      <c r="E238" t="s">
+        <v>878</v>
+      </c>
+      <c r="F238" t="s">
+        <v>42</v>
+      </c>
+      <c r="G238" t="s">
+        <v>287</v>
+      </c>
+      <c r="H238" t="s">
+        <v>997</v>
+      </c>
+      <c r="I238" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J238" s="1"/>
+      <c r="M238" t="s">
+        <v>7</v>
+      </c>
+      <c r="N238" t="s">
+        <v>50</v>
+      </c>
+      <c r="O238" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="239" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A239" t="s">
+        <v>14</v>
+      </c>
+      <c r="B239" s="3" t="s">
+        <v>879</v>
+      </c>
+      <c r="C239" s="3" t="s">
+        <v>879</v>
+      </c>
+      <c r="D239" s="3" t="s">
+        <v>880</v>
+      </c>
+      <c r="E239" t="s">
+        <v>881</v>
+      </c>
+      <c r="F239" t="s">
+        <v>20</v>
+      </c>
+      <c r="G239" t="s">
+        <v>419</v>
+      </c>
+      <c r="H239" t="s">
+        <v>997</v>
+      </c>
+      <c r="I239" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J239" s="1"/>
+      <c r="M239" t="s">
+        <v>7</v>
+      </c>
+      <c r="N239" t="s">
+        <v>50</v>
+      </c>
+      <c r="O239" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="240" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A240" t="s">
+        <v>127</v>
+      </c>
+      <c r="B240" s="3" t="s">
+        <v>882</v>
+      </c>
+      <c r="C240" s="3" t="s">
+        <v>882</v>
+      </c>
+      <c r="D240" s="3" t="s">
+        <v>883</v>
+      </c>
+      <c r="E240" t="s">
+        <v>884</v>
+      </c>
+      <c r="F240" t="s">
+        <v>43</v>
+      </c>
+      <c r="G240" t="s">
+        <v>47</v>
+      </c>
+      <c r="H240" t="s">
+        <v>997</v>
+      </c>
+      <c r="I240" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J240" s="1"/>
+      <c r="M240" t="s">
+        <v>7</v>
+      </c>
+      <c r="N240" t="s">
+        <v>50</v>
+      </c>
+      <c r="O240" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="241" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A241" t="s">
+        <v>14</v>
+      </c>
+      <c r="B241" s="3" t="s">
+        <v>885</v>
+      </c>
+      <c r="C241" s="3" t="s">
+        <v>885</v>
+      </c>
+      <c r="D241" s="3" t="s">
+        <v>886</v>
+      </c>
+      <c r="E241" t="s">
+        <v>887</v>
+      </c>
+      <c r="F241" t="s">
+        <v>42</v>
+      </c>
+      <c r="G241" t="s">
+        <v>287</v>
+      </c>
+      <c r="H241" t="s">
+        <v>997</v>
+      </c>
+      <c r="I241" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J241" s="1"/>
+      <c r="M241" t="s">
+        <v>7</v>
+      </c>
+      <c r="N241" t="s">
+        <v>50</v>
+      </c>
+      <c r="O241" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="242" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A242" t="s">
+        <v>127</v>
+      </c>
+      <c r="B242" s="3" t="s">
+        <v>888</v>
+      </c>
+      <c r="C242" s="3" t="s">
+        <v>888</v>
+      </c>
+      <c r="D242" s="3" t="s">
+        <v>889</v>
+      </c>
+      <c r="E242" t="s">
+        <v>890</v>
+      </c>
+      <c r="F242" t="s">
+        <v>43</v>
+      </c>
+      <c r="G242" t="s">
+        <v>49</v>
+      </c>
+      <c r="H242" t="s">
+        <v>997</v>
+      </c>
+      <c r="I242" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J242" s="1"/>
+      <c r="M242" t="s">
+        <v>7</v>
+      </c>
+      <c r="N242" t="s">
+        <v>50</v>
+      </c>
+      <c r="O242" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="243" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A243" t="s">
+        <v>14</v>
+      </c>
+      <c r="B243" s="3" t="s">
+        <v>891</v>
+      </c>
+      <c r="C243" s="3" t="s">
+        <v>891</v>
+      </c>
+      <c r="D243" s="3" t="s">
+        <v>892</v>
+      </c>
+      <c r="E243" t="s">
+        <v>893</v>
+      </c>
+      <c r="F243" t="s">
+        <v>20</v>
+      </c>
+      <c r="G243" t="s">
+        <v>287</v>
+      </c>
+      <c r="H243" t="s">
+        <v>997</v>
+      </c>
+      <c r="I243" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J243" s="1"/>
+      <c r="M243" t="s">
+        <v>7</v>
+      </c>
+      <c r="N243" t="s">
+        <v>50</v>
+      </c>
+      <c r="O243" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="244" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A244" t="s">
+        <v>27</v>
+      </c>
+      <c r="B244" s="3" t="s">
+        <v>894</v>
+      </c>
+      <c r="C244" s="3" t="s">
+        <v>894</v>
+      </c>
+      <c r="D244" s="3" t="s">
+        <v>895</v>
+      </c>
+      <c r="E244" t="s">
+        <v>776</v>
+      </c>
+      <c r="F244" t="s">
+        <v>15</v>
+      </c>
+      <c r="H244" t="s">
+        <v>997</v>
+      </c>
+      <c r="I244" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J244" s="1"/>
+      <c r="M244" t="s">
+        <v>7</v>
+      </c>
+      <c r="N244" t="s">
+        <v>50</v>
+      </c>
+      <c r="O244" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="245" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A245" t="s">
+        <v>14</v>
+      </c>
+      <c r="B245" s="3" t="s">
+        <v>896</v>
+      </c>
+      <c r="C245" s="3" t="s">
+        <v>896</v>
+      </c>
+      <c r="D245" s="3" t="s">
+        <v>897</v>
+      </c>
+      <c r="E245" t="s">
+        <v>898</v>
+      </c>
+      <c r="F245" t="s">
+        <v>20</v>
+      </c>
+      <c r="G245" t="s">
+        <v>46</v>
+      </c>
+      <c r="H245" t="s">
+        <v>997</v>
+      </c>
+      <c r="I245" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J245" s="1"/>
+      <c r="M245" t="s">
+        <v>7</v>
+      </c>
+      <c r="N245" t="s">
+        <v>50</v>
+      </c>
+      <c r="O245" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="246" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A246" t="s">
+        <v>127</v>
+      </c>
+      <c r="B246" s="3" t="s">
+        <v>899</v>
+      </c>
+      <c r="C246" s="3" t="s">
+        <v>899</v>
+      </c>
+      <c r="D246" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="E246" t="s">
+        <v>901</v>
+      </c>
+      <c r="F246" t="s">
+        <v>43</v>
+      </c>
+      <c r="G246" t="s">
+        <v>44</v>
+      </c>
+      <c r="H246" t="s">
+        <v>997</v>
+      </c>
+      <c r="I246" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J246" s="1"/>
+      <c r="M246" t="s">
+        <v>7</v>
+      </c>
+      <c r="N246" t="s">
+        <v>50</v>
+      </c>
+      <c r="O246" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="247" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A247" t="s">
+        <v>2</v>
+      </c>
+      <c r="B247" s="3" t="s">
+        <v>902</v>
+      </c>
+      <c r="C247" s="3" t="s">
+        <v>902</v>
+      </c>
+      <c r="D247" s="3" t="s">
+        <v>903</v>
+      </c>
+      <c r="E247" t="s">
+        <v>904</v>
+      </c>
+      <c r="G247" t="s">
+        <v>47</v>
+      </c>
+      <c r="H247" t="s">
+        <v>997</v>
+      </c>
+      <c r="I247" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J247" s="1"/>
+      <c r="M247" t="s">
+        <v>7</v>
+      </c>
+      <c r="N247" t="s">
+        <v>50</v>
+      </c>
+      <c r="O247" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="248" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A248" t="s">
+        <v>122</v>
+      </c>
+      <c r="B248" s="3" t="s">
+        <v>905</v>
+      </c>
+      <c r="C248" s="3" t="s">
+        <v>905</v>
+      </c>
+      <c r="D248" s="3" t="s">
+        <v>906</v>
+      </c>
+      <c r="E248" t="s">
+        <v>907</v>
+      </c>
+      <c r="F248" t="s">
+        <v>21</v>
+      </c>
+      <c r="G248" t="s">
+        <v>46</v>
+      </c>
+      <c r="H248" t="s">
+        <v>997</v>
+      </c>
+      <c r="I248" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J248" s="1"/>
+      <c r="M248" t="s">
+        <v>7</v>
+      </c>
+      <c r="N248" t="s">
+        <v>50</v>
+      </c>
+      <c r="O248" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="249" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A249" t="s">
+        <v>127</v>
+      </c>
+      <c r="B249" s="3" t="s">
+        <v>908</v>
+      </c>
+      <c r="C249" s="3" t="s">
+        <v>908</v>
+      </c>
+      <c r="D249" s="3" t="s">
+        <v>909</v>
+      </c>
+      <c r="E249" t="s">
+        <v>910</v>
+      </c>
+      <c r="F249" t="s">
+        <v>1</v>
+      </c>
+      <c r="G249" t="s">
+        <v>44</v>
+      </c>
+      <c r="H249" t="s">
+        <v>997</v>
+      </c>
+      <c r="I249" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J249" s="1"/>
+      <c r="M249" t="s">
+        <v>7</v>
+      </c>
+      <c r="N249" t="s">
+        <v>50</v>
+      </c>
+      <c r="O249" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="250" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A250" t="s">
+        <v>2</v>
+      </c>
+      <c r="B250" s="3" t="s">
+        <v>909</v>
+      </c>
+      <c r="C250" s="3" t="s">
+        <v>909</v>
+      </c>
+      <c r="D250" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="E250" t="s">
+        <v>911</v>
+      </c>
+      <c r="F250" t="s">
+        <v>17</v>
+      </c>
+      <c r="G250" t="s">
+        <v>45</v>
+      </c>
+      <c r="H250" t="s">
+        <v>997</v>
+      </c>
+      <c r="I250" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J250" s="1"/>
+      <c r="M250" t="s">
+        <v>7</v>
+      </c>
+      <c r="N250" t="s">
+        <v>50</v>
+      </c>
+      <c r="O250" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="251" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A251" t="s">
+        <v>122</v>
+      </c>
+      <c r="B251" s="3" t="s">
+        <v>912</v>
+      </c>
+      <c r="C251" s="3" t="s">
+        <v>912</v>
+      </c>
+      <c r="D251" s="3" t="s">
+        <v>913</v>
+      </c>
+      <c r="E251" t="s">
+        <v>914</v>
+      </c>
+      <c r="F251" t="s">
+        <v>20</v>
+      </c>
+      <c r="G251" t="s">
+        <v>46</v>
+      </c>
+      <c r="H251" t="s">
+        <v>997</v>
+      </c>
+      <c r="I251" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J251" s="1"/>
+      <c r="M251" t="s">
+        <v>7</v>
+      </c>
+      <c r="N251" t="s">
+        <v>50</v>
+      </c>
+      <c r="O251" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="252" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A252" t="s">
+        <v>127</v>
+      </c>
+      <c r="B252" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="C252" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="D252" s="3" t="s">
+        <v>916</v>
+      </c>
+      <c r="E252" t="s">
+        <v>917</v>
+      </c>
+      <c r="F252" t="s">
+        <v>43</v>
+      </c>
+      <c r="G252" t="s">
+        <v>45</v>
+      </c>
+      <c r="H252" t="s">
+        <v>997</v>
+      </c>
+      <c r="I252" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J252" s="1"/>
+      <c r="M252" t="s">
+        <v>7</v>
+      </c>
+      <c r="N252" t="s">
+        <v>50</v>
+      </c>
+      <c r="O252" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="253" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A253" t="s">
+        <v>2</v>
+      </c>
+      <c r="B253" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="C253" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="D253" s="3" t="s">
+        <v>918</v>
+      </c>
+      <c r="E253" t="s">
+        <v>919</v>
+      </c>
+      <c r="F253" t="s">
+        <v>17</v>
+      </c>
+      <c r="G253" t="s">
+        <v>49</v>
+      </c>
+      <c r="H253" t="s">
+        <v>997</v>
+      </c>
+      <c r="I253" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J253" s="1"/>
+      <c r="M253" t="s">
+        <v>7</v>
+      </c>
+      <c r="N253" t="s">
+        <v>50</v>
+      </c>
+      <c r="O253" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="254" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A254" t="s">
+        <v>14</v>
+      </c>
+      <c r="B254" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="C254" s="3" t="s">
+        <v>920</v>
+      </c>
+      <c r="D254" s="3" t="s">
+        <v>921</v>
+      </c>
+      <c r="E254" t="s">
+        <v>922</v>
+      </c>
+      <c r="F254" t="s">
+        <v>20</v>
+      </c>
+      <c r="G254" t="s">
+        <v>419</v>
+      </c>
+      <c r="H254" t="s">
+        <v>997</v>
+      </c>
+      <c r="I254" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J254" s="1"/>
+      <c r="L254" t="s">
+        <v>512</v>
+      </c>
+      <c r="M254" t="s">
+        <v>7</v>
+      </c>
+      <c r="N254" t="s">
+        <v>50</v>
+      </c>
+      <c r="O254" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="255" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A255" t="s">
+        <v>2</v>
+      </c>
+      <c r="B255" s="3" t="s">
+        <v>923</v>
+      </c>
+      <c r="C255" s="3" t="s">
+        <v>923</v>
+      </c>
+      <c r="D255" s="3" t="s">
+        <v>924</v>
+      </c>
+      <c r="E255" t="s">
+        <v>925</v>
+      </c>
+      <c r="F255" t="s">
+        <v>3</v>
+      </c>
+      <c r="G255" t="s">
+        <v>45</v>
+      </c>
+      <c r="H255" t="s">
+        <v>997</v>
+      </c>
+      <c r="I255" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J255" s="1"/>
+      <c r="M255" t="s">
+        <v>7</v>
+      </c>
+      <c r="N255" t="s">
+        <v>50</v>
+      </c>
+      <c r="O255" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="256" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A256" t="s">
+        <v>32</v>
+      </c>
+      <c r="B256" s="3" t="s">
+        <v>926</v>
+      </c>
+      <c r="C256" s="3" t="s">
+        <v>926</v>
+      </c>
+      <c r="D256" s="3" t="s">
+        <v>927</v>
+      </c>
+      <c r="E256" t="s">
+        <v>922</v>
+      </c>
+      <c r="F256" t="s">
+        <v>4</v>
+      </c>
+      <c r="H256" t="s">
+        <v>997</v>
+      </c>
+      <c r="I256" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J256" s="1"/>
+      <c r="M256" t="s">
+        <v>7</v>
+      </c>
+      <c r="N256" t="s">
+        <v>50</v>
+      </c>
+      <c r="O256" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="257" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A257" t="s">
+        <v>14</v>
+      </c>
+      <c r="B257" s="3" t="s">
+        <v>928</v>
+      </c>
+      <c r="C257" s="3" t="s">
+        <v>928</v>
+      </c>
+      <c r="D257" s="3" t="s">
+        <v>929</v>
+      </c>
+      <c r="E257" t="s">
+        <v>930</v>
+      </c>
+      <c r="F257" t="s">
+        <v>20</v>
+      </c>
+      <c r="G257" t="s">
+        <v>287</v>
+      </c>
+      <c r="H257" t="s">
+        <v>997</v>
+      </c>
+      <c r="I257" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J257" s="1"/>
+      <c r="M257" t="s">
+        <v>7</v>
+      </c>
+      <c r="N257" t="s">
+        <v>50</v>
+      </c>
+      <c r="O257" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="258" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A258" t="s">
+        <v>127</v>
+      </c>
+      <c r="B258" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="C258" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="D258" s="3" t="s">
+        <v>931</v>
+      </c>
+      <c r="E258" t="s">
+        <v>932</v>
+      </c>
+      <c r="F258" t="s">
+        <v>43</v>
+      </c>
+      <c r="G258" t="s">
+        <v>45</v>
+      </c>
+      <c r="H258" t="s">
+        <v>997</v>
+      </c>
+      <c r="I258" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J258" s="1"/>
+      <c r="M258" t="s">
+        <v>7</v>
+      </c>
+      <c r="N258" t="s">
+        <v>50</v>
+      </c>
+      <c r="O258" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="259" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A259" t="s">
+        <v>122</v>
+      </c>
+      <c r="B259" s="3" t="s">
+        <v>933</v>
+      </c>
+      <c r="C259" s="3" t="s">
+        <v>933</v>
+      </c>
+      <c r="D259" s="3" t="s">
+        <v>934</v>
+      </c>
+      <c r="E259" t="s">
+        <v>935</v>
+      </c>
+      <c r="F259" t="s">
+        <v>20</v>
+      </c>
+      <c r="G259" t="s">
+        <v>287</v>
+      </c>
+      <c r="H259" t="s">
+        <v>997</v>
+      </c>
+      <c r="I259" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J259" s="1"/>
+      <c r="M259" t="s">
+        <v>7</v>
+      </c>
+      <c r="N259" t="s">
+        <v>50</v>
+      </c>
+      <c r="O259" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="260" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A260" t="s">
+        <v>14</v>
+      </c>
+      <c r="B260" s="3" t="s">
+        <v>936</v>
+      </c>
+      <c r="C260" s="3" t="s">
+        <v>936</v>
+      </c>
+      <c r="D260" s="3" t="s">
+        <v>937</v>
+      </c>
+      <c r="E260" t="s">
+        <v>938</v>
+      </c>
+      <c r="G260" t="s">
+        <v>46</v>
+      </c>
+      <c r="H260" t="s">
+        <v>997</v>
+      </c>
+      <c r="I260" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J260" s="1"/>
+      <c r="M260" t="s">
+        <v>7</v>
+      </c>
+      <c r="N260" t="s">
+        <v>50</v>
+      </c>
+      <c r="O260" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="261" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A261" t="s">
+        <v>127</v>
+      </c>
+      <c r="B261" s="3" t="s">
+        <v>939</v>
+      </c>
+      <c r="C261" s="3" t="s">
+        <v>939</v>
+      </c>
+      <c r="D261" s="3" t="s">
+        <v>940</v>
+      </c>
+      <c r="E261" t="s">
+        <v>941</v>
+      </c>
+      <c r="F261" t="s">
+        <v>43</v>
+      </c>
+      <c r="G261" t="s">
+        <v>47</v>
+      </c>
+      <c r="H261" t="s">
+        <v>997</v>
+      </c>
+      <c r="I261" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J261" s="1"/>
+      <c r="M261" t="s">
+        <v>7</v>
+      </c>
+      <c r="N261" t="s">
+        <v>50</v>
+      </c>
+      <c r="O261" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="262" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A262" t="s">
+        <v>122</v>
+      </c>
+      <c r="B262" s="3" t="s">
+        <v>942</v>
+      </c>
+      <c r="C262" s="3" t="s">
+        <v>942</v>
+      </c>
+      <c r="D262" s="3" t="s">
+        <v>943</v>
+      </c>
+      <c r="E262" t="s">
+        <v>944</v>
+      </c>
+      <c r="F262" t="s">
+        <v>21</v>
+      </c>
+      <c r="G262" t="s">
+        <v>46</v>
+      </c>
+      <c r="H262" t="s">
+        <v>997</v>
+      </c>
+      <c r="I262" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J262" s="1"/>
+      <c r="M262" t="s">
+        <v>7</v>
+      </c>
+      <c r="N262" t="s">
+        <v>50</v>
+      </c>
+      <c r="O262" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="263" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A263" t="s">
+        <v>127</v>
+      </c>
+      <c r="B263" s="3" t="s">
+        <v>945</v>
+      </c>
+      <c r="C263" s="3" t="s">
+        <v>945</v>
+      </c>
+      <c r="D263" s="3" t="s">
+        <v>946</v>
+      </c>
+      <c r="E263" t="s">
+        <v>947</v>
+      </c>
+      <c r="F263" t="s">
+        <v>1</v>
+      </c>
+      <c r="G263" t="s">
+        <v>44</v>
+      </c>
+      <c r="H263" t="s">
+        <v>997</v>
+      </c>
+      <c r="I263" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J263" s="1"/>
+      <c r="M263" t="s">
+        <v>7</v>
+      </c>
+      <c r="N263" t="s">
+        <v>50</v>
+      </c>
+      <c r="O263" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="264" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A264" t="s">
+        <v>2</v>
+      </c>
+      <c r="B264" s="3" t="s">
+        <v>948</v>
+      </c>
+      <c r="C264" s="3" t="s">
+        <v>948</v>
+      </c>
+      <c r="D264" s="3" t="s">
+        <v>949</v>
+      </c>
+      <c r="E264" t="s">
+        <v>950</v>
+      </c>
+      <c r="F264" t="s">
+        <v>18</v>
+      </c>
+      <c r="G264" t="s">
+        <v>47</v>
+      </c>
+      <c r="H264" t="s">
+        <v>997</v>
+      </c>
+      <c r="I264" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J264" s="1"/>
+      <c r="M264" t="s">
+        <v>7</v>
+      </c>
+      <c r="N264" t="s">
+        <v>50</v>
+      </c>
+      <c r="O264" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="265" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A265" t="s">
+        <v>122</v>
+      </c>
+      <c r="B265" s="3" t="s">
+        <v>951</v>
+      </c>
+      <c r="C265" s="3" t="s">
+        <v>951</v>
+      </c>
+      <c r="D265" s="3" t="s">
+        <v>952</v>
+      </c>
+      <c r="E265" t="s">
+        <v>953</v>
+      </c>
+      <c r="F265" t="s">
+        <v>20</v>
+      </c>
+      <c r="G265" t="s">
+        <v>46</v>
+      </c>
+      <c r="H265" t="s">
+        <v>997</v>
+      </c>
+      <c r="I265" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J265" s="1"/>
+      <c r="M265" t="s">
+        <v>7</v>
+      </c>
+      <c r="N265" t="s">
+        <v>50</v>
+      </c>
+      <c r="O265" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="266" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A266" t="s">
+        <v>127</v>
+      </c>
+      <c r="B266" s="3" t="s">
+        <v>954</v>
+      </c>
+      <c r="C266" s="3" t="s">
+        <v>954</v>
+      </c>
+      <c r="D266" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="E266" t="s">
+        <v>955</v>
+      </c>
+      <c r="F266" t="s">
+        <v>43</v>
+      </c>
+      <c r="G266" t="s">
+        <v>44</v>
+      </c>
+      <c r="H266" t="s">
+        <v>997</v>
+      </c>
+      <c r="I266" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J266" s="1"/>
+      <c r="M266" t="s">
+        <v>7</v>
+      </c>
+      <c r="N266" t="s">
+        <v>50</v>
+      </c>
+      <c r="O266" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="267" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A267" t="s">
+        <v>32</v>
+      </c>
+      <c r="B267" s="3" t="s">
+        <v>956</v>
+      </c>
+      <c r="C267" s="3" t="s">
+        <v>956</v>
+      </c>
+      <c r="D267" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="E267" t="s">
+        <v>957</v>
+      </c>
+      <c r="F267" t="s">
+        <v>4</v>
+      </c>
+      <c r="H267" t="s">
+        <v>997</v>
+      </c>
+      <c r="I267" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J267" s="1"/>
+      <c r="M267" t="s">
+        <v>7</v>
+      </c>
+      <c r="N267" t="s">
+        <v>50</v>
+      </c>
+      <c r="O267" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="268" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A268" t="s">
+        <v>14</v>
+      </c>
+      <c r="B268" s="3" t="s">
+        <v>958</v>
+      </c>
+      <c r="C268" s="3" t="s">
+        <v>958</v>
+      </c>
+      <c r="D268" s="3" t="s">
+        <v>959</v>
+      </c>
+      <c r="E268" t="s">
+        <v>137</v>
+      </c>
+      <c r="F268" t="s">
+        <v>20</v>
+      </c>
+      <c r="G268" t="s">
+        <v>287</v>
+      </c>
+      <c r="H268" t="s">
+        <v>997</v>
+      </c>
+      <c r="I268" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J268" s="1"/>
+      <c r="M268" t="s">
+        <v>7</v>
+      </c>
+      <c r="N268" t="s">
+        <v>50</v>
+      </c>
+      <c r="O268" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="269" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A269" t="s">
+        <v>127</v>
+      </c>
+      <c r="B269" s="3" t="s">
+        <v>960</v>
+      </c>
+      <c r="C269" s="3" t="s">
+        <v>960</v>
+      </c>
+      <c r="D269" s="3" t="s">
+        <v>961</v>
+      </c>
+      <c r="E269" t="s">
+        <v>962</v>
+      </c>
+      <c r="F269" t="s">
+        <v>1</v>
+      </c>
+      <c r="G269" t="s">
+        <v>47</v>
+      </c>
+      <c r="H269" t="s">
+        <v>997</v>
+      </c>
+      <c r="I269" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J269" s="1"/>
+      <c r="M269" t="s">
+        <v>7</v>
+      </c>
+      <c r="N269" t="s">
+        <v>50</v>
+      </c>
+      <c r="O269" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="270" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A270" t="s">
+        <v>2</v>
+      </c>
+      <c r="B270" s="3" t="s">
+        <v>963</v>
+      </c>
+      <c r="C270" s="3" t="s">
+        <v>963</v>
+      </c>
+      <c r="D270" s="3" t="s">
+        <v>964</v>
+      </c>
+      <c r="E270" t="s">
+        <v>965</v>
+      </c>
+      <c r="F270" t="s">
+        <v>17</v>
+      </c>
+      <c r="G270" t="s">
+        <v>47</v>
+      </c>
+      <c r="H270" t="s">
+        <v>997</v>
+      </c>
+      <c r="I270" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J270" s="1"/>
+      <c r="M270" t="s">
+        <v>7</v>
+      </c>
+      <c r="N270" t="s">
+        <v>50</v>
+      </c>
+      <c r="O270" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="271" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A271" t="s">
+        <v>122</v>
+      </c>
+      <c r="B271" s="3" t="s">
+        <v>966</v>
+      </c>
+      <c r="C271" s="3" t="s">
+        <v>966</v>
+      </c>
+      <c r="D271" s="3" t="s">
+        <v>967</v>
+      </c>
+      <c r="E271" t="s">
+        <v>968</v>
+      </c>
+      <c r="F271" t="s">
+        <v>42</v>
+      </c>
+      <c r="G271" t="s">
+        <v>46</v>
+      </c>
+      <c r="H271" t="s">
+        <v>997</v>
+      </c>
+      <c r="I271" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J271" s="1"/>
+      <c r="M271" t="s">
+        <v>7</v>
+      </c>
+      <c r="N271" t="s">
+        <v>50</v>
+      </c>
+      <c r="O271" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="272" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A272" t="s">
+        <v>127</v>
+      </c>
+      <c r="B272" s="3" t="s">
+        <v>969</v>
+      </c>
+      <c r="C272" s="3" t="s">
+        <v>969</v>
+      </c>
+      <c r="D272" s="3" t="s">
+        <v>970</v>
+      </c>
+      <c r="E272" t="s">
+        <v>971</v>
+      </c>
+      <c r="F272" t="s">
+        <v>43</v>
+      </c>
+      <c r="G272" t="s">
+        <v>45</v>
+      </c>
+      <c r="H272" t="s">
+        <v>997</v>
+      </c>
+      <c r="I272" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J272" s="1"/>
+      <c r="M272" t="s">
+        <v>7</v>
+      </c>
+      <c r="N272" t="s">
+        <v>50</v>
+      </c>
+      <c r="O272" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="273" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A273" t="s">
+        <v>32</v>
+      </c>
+      <c r="B273" s="3" t="s">
+        <v>972</v>
+      </c>
+      <c r="C273" s="3" t="s">
+        <v>972</v>
+      </c>
+      <c r="D273" s="3" t="s">
+        <v>973</v>
+      </c>
+      <c r="E273" t="s">
+        <v>974</v>
+      </c>
+      <c r="F273" t="s">
+        <v>4</v>
+      </c>
+      <c r="H273" t="s">
+        <v>997</v>
+      </c>
+      <c r="I273" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J273" s="1"/>
+      <c r="M273" t="s">
+        <v>7</v>
+      </c>
+      <c r="N273" t="s">
+        <v>50</v>
+      </c>
+      <c r="O273" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="274" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A274" t="s">
+        <v>14</v>
+      </c>
+      <c r="B274" s="3" t="s">
+        <v>975</v>
+      </c>
+      <c r="C274" s="3" t="s">
+        <v>975</v>
+      </c>
+      <c r="D274" s="3" t="s">
+        <v>976</v>
+      </c>
+      <c r="E274" t="s">
+        <v>977</v>
+      </c>
+      <c r="F274" t="s">
+        <v>20</v>
+      </c>
+      <c r="G274" t="s">
+        <v>46</v>
+      </c>
+      <c r="H274" t="s">
+        <v>997</v>
+      </c>
+      <c r="I274" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J274" s="1"/>
+      <c r="M274" t="s">
+        <v>7</v>
+      </c>
+      <c r="N274" t="s">
+        <v>50</v>
+      </c>
+      <c r="O274" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="275" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A275" t="s">
+        <v>32</v>
+      </c>
+      <c r="B275" s="3" t="s">
+        <v>976</v>
+      </c>
+      <c r="C275" s="3" t="s">
+        <v>976</v>
+      </c>
+      <c r="D275" s="3" t="s">
+        <v>978</v>
+      </c>
+      <c r="E275" t="s">
+        <v>979</v>
+      </c>
+      <c r="F275" t="s">
+        <v>4</v>
+      </c>
+      <c r="H275" t="s">
+        <v>997</v>
+      </c>
+      <c r="I275" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J275" s="1"/>
+      <c r="M275" t="s">
+        <v>7</v>
+      </c>
+      <c r="N275" t="s">
+        <v>50</v>
+      </c>
+      <c r="O275" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="276" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A276" t="s">
+        <v>2</v>
+      </c>
+      <c r="B276" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="C276" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="D276" s="3" t="s">
+        <v>980</v>
+      </c>
+      <c r="E276" t="s">
+        <v>981</v>
+      </c>
+      <c r="F276" t="s">
+        <v>17</v>
+      </c>
+      <c r="G276" t="s">
+        <v>49</v>
+      </c>
+      <c r="H276" t="s">
+        <v>997</v>
+      </c>
+      <c r="I276" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J276" s="1"/>
+      <c r="M276" t="s">
+        <v>7</v>
+      </c>
+      <c r="N276" t="s">
+        <v>50</v>
+      </c>
+      <c r="O276" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="277" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A277" t="s">
+        <v>14</v>
+      </c>
+      <c r="B277" s="3" t="s">
+        <v>982</v>
+      </c>
+      <c r="C277" s="3" t="s">
+        <v>982</v>
+      </c>
+      <c r="D277" s="3" t="s">
+        <v>983</v>
+      </c>
+      <c r="E277" t="s">
+        <v>984</v>
+      </c>
+      <c r="G277" t="s">
+        <v>287</v>
+      </c>
+      <c r="H277" t="s">
+        <v>997</v>
+      </c>
+      <c r="I277" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J277" s="1"/>
+      <c r="M277" t="s">
+        <v>7</v>
+      </c>
+      <c r="N277" t="s">
+        <v>50</v>
+      </c>
+      <c r="O277" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="278" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A278" t="s">
+        <v>122</v>
+      </c>
+      <c r="B278" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="C278" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="D278" s="3" t="s">
+        <v>985</v>
+      </c>
+      <c r="E278" t="s">
+        <v>986</v>
+      </c>
+      <c r="F278" t="s">
+        <v>20</v>
+      </c>
+      <c r="G278" t="s">
+        <v>287</v>
+      </c>
+      <c r="H278" t="s">
+        <v>997</v>
+      </c>
+      <c r="I278" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J278" s="1"/>
+      <c r="M278" t="s">
+        <v>7</v>
+      </c>
+      <c r="N278" t="s">
+        <v>50</v>
+      </c>
+      <c r="O278" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="279" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A279" t="s">
+        <v>127</v>
+      </c>
+      <c r="B279" s="3" t="s">
+        <v>987</v>
+      </c>
+      <c r="C279" s="3" t="s">
+        <v>987</v>
+      </c>
+      <c r="D279" s="3" t="s">
+        <v>988</v>
+      </c>
+      <c r="E279" t="s">
+        <v>989</v>
+      </c>
+      <c r="F279" t="s">
+        <v>43</v>
+      </c>
+      <c r="G279" t="s">
+        <v>45</v>
+      </c>
+      <c r="H279" t="s">
+        <v>997</v>
+      </c>
+      <c r="I279" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J279" s="1"/>
+      <c r="M279" t="s">
+        <v>7</v>
+      </c>
+      <c r="N279" t="s">
+        <v>50</v>
+      </c>
+      <c r="O279" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="280" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A280" t="s">
+        <v>2</v>
+      </c>
+      <c r="B280" s="3" t="s">
+        <v>501</v>
+      </c>
+      <c r="C280" s="3" t="s">
+        <v>501</v>
+      </c>
+      <c r="D280" s="3" t="s">
+        <v>990</v>
+      </c>
+      <c r="E280" t="s">
+        <v>991</v>
+      </c>
+      <c r="F280" t="s">
+        <v>17</v>
+      </c>
+      <c r="G280" t="s">
+        <v>49</v>
+      </c>
+      <c r="H280" t="s">
+        <v>997</v>
+      </c>
+      <c r="I280" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J280" s="1"/>
+      <c r="M280" t="s">
+        <v>7</v>
+      </c>
+      <c r="N280" t="s">
+        <v>50</v>
+      </c>
+      <c r="O280" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="281" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A281" t="s">
+        <v>32</v>
+      </c>
+      <c r="B281" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="C281" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="D281" s="3" t="s">
+        <v>992</v>
+      </c>
+      <c r="E281" t="s">
+        <v>993</v>
+      </c>
+      <c r="F281" t="s">
+        <v>511</v>
+      </c>
+      <c r="H281" t="s">
+        <v>997</v>
+      </c>
+      <c r="I281" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J281" s="1"/>
+      <c r="M281" t="s">
+        <v>7</v>
+      </c>
+      <c r="N281" t="s">
+        <v>50</v>
+      </c>
+      <c r="O281" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="282" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A282" t="s">
+        <v>127</v>
+      </c>
+      <c r="B282" s="3" t="s">
+        <v>994</v>
+      </c>
+      <c r="C282" s="3" t="s">
+        <v>994</v>
+      </c>
+      <c r="D282" s="3" t="s">
+        <v>995</v>
+      </c>
+      <c r="E282" t="s">
+        <v>996</v>
+      </c>
+      <c r="F282" t="s">
+        <v>43</v>
+      </c>
+      <c r="G282" t="s">
+        <v>45</v>
+      </c>
+      <c r="H282" t="s">
+        <v>997</v>
+      </c>
+      <c r="I282" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J282" s="1"/>
+      <c r="M282" t="s">
+        <v>7</v>
+      </c>
+      <c r="N282" t="s">
+        <v>50</v>
+      </c>
+      <c r="O282" t="s">
+        <v>55</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="I179" r:id="rId1" xr:uid="{DF7BACFF-362E-4C13-9DEA-49190526F50C}"/>
+    <hyperlink ref="I180" r:id="rId2" xr:uid="{D7B98F00-3289-44BC-AEF6-9AEC8937A468}"/>
+    <hyperlink ref="I181" r:id="rId3" xr:uid="{C22CC0C1-A687-4C29-B775-6F039D5E6DEC}"/>
+    <hyperlink ref="I182" r:id="rId4" xr:uid="{79B42F26-7C81-4DD5-96B4-2359D79F0364}"/>
+    <hyperlink ref="I183" r:id="rId5" xr:uid="{AE91AC2B-3175-467F-9865-73113A52D61D}"/>
+    <hyperlink ref="I184" r:id="rId6" xr:uid="{4B548DF3-A202-4CC6-A90E-5CEA7B06E348}"/>
+    <hyperlink ref="I185" r:id="rId7" xr:uid="{F0C67DE9-D279-4A1D-9B74-46F34E70DD04}"/>
+    <hyperlink ref="I186" r:id="rId8" xr:uid="{135E1FCB-A6CD-4847-8035-6887EA03445E}"/>
+    <hyperlink ref="I187" r:id="rId9" xr:uid="{BDED4B76-AB55-47E6-A7EF-649D1A658D6C}"/>
+    <hyperlink ref="I188" r:id="rId10" xr:uid="{72BC446F-5780-41EA-B9E2-2DD4D1D94139}"/>
+    <hyperlink ref="I189" r:id="rId11" xr:uid="{E9AD0F9D-AEC3-4393-B235-E1BD2BEAD4F1}"/>
+    <hyperlink ref="I190" r:id="rId12" xr:uid="{9F669CB5-AC5E-4665-8AD5-9BCB190A1B01}"/>
+    <hyperlink ref="I191" r:id="rId13" xr:uid="{68FE1755-5598-4B0E-9654-2A96B62788F0}"/>
+    <hyperlink ref="I192" r:id="rId14" xr:uid="{A29F52B6-7AE9-4FD8-B168-F995A780FB12}"/>
+    <hyperlink ref="I193" r:id="rId15" xr:uid="{97C049FD-8188-4C98-853C-F1B6D068169C}"/>
+    <hyperlink ref="I194" r:id="rId16" xr:uid="{B5F69469-37AF-478E-99DC-E87A6A8A3E0F}"/>
+    <hyperlink ref="I195" r:id="rId17" xr:uid="{A7675D7B-DFBE-4C18-AD8C-D5E4795ED8BB}"/>
+    <hyperlink ref="I196" r:id="rId18" xr:uid="{4999C4BB-DAFB-4356-8E32-EF0763D8FA2C}"/>
+    <hyperlink ref="I197" r:id="rId19" xr:uid="{2DE0C150-2921-457D-8E28-496E0A1EDC60}"/>
+    <hyperlink ref="I198" r:id="rId20" xr:uid="{F7B116EF-F8DB-481E-9B3E-87A3584CB92F}"/>
+    <hyperlink ref="I199" r:id="rId21" xr:uid="{E897C17E-2AEE-4832-83B9-3D5776852B0B}"/>
+    <hyperlink ref="I200" r:id="rId22" xr:uid="{03E62B5E-379A-4A2C-9317-2A7C70B4859E}"/>
+    <hyperlink ref="I201" r:id="rId23" xr:uid="{B3CE0EBB-E3D5-40F6-B48F-24777C13A1D9}"/>
+    <hyperlink ref="I202" r:id="rId24" xr:uid="{51C90134-0B32-451A-8AFE-191A7203536D}"/>
+    <hyperlink ref="I203" r:id="rId25" xr:uid="{23854EF0-0B16-46DC-98D2-1C4DBD6E760F}"/>
+    <hyperlink ref="I204" r:id="rId26" xr:uid="{200E78AB-11A4-4543-AD95-EB7AAA2A9549}"/>
+    <hyperlink ref="I205" r:id="rId27" xr:uid="{39B4404A-0DF4-4BC8-B450-6AECDE865F34}"/>
+    <hyperlink ref="I206" r:id="rId28" xr:uid="{EA3C7C97-9F69-4764-9E80-68E9464A1877}"/>
+    <hyperlink ref="I207" r:id="rId29" xr:uid="{DFE83388-D1BC-4F08-8B24-977DC614D09B}"/>
+    <hyperlink ref="I208" r:id="rId30" xr:uid="{25A8440B-013A-450A-BE5E-54F7A5CDC9D4}"/>
+    <hyperlink ref="I209" r:id="rId31" xr:uid="{1B06F431-3898-439A-B932-EF147873F432}"/>
+    <hyperlink ref="I210" r:id="rId32" xr:uid="{54808072-13E6-41A2-AD74-C03821C5D130}"/>
+    <hyperlink ref="I211" r:id="rId33" xr:uid="{0925F796-45E7-4177-94D1-B86CB1F98C05}"/>
+    <hyperlink ref="I212" r:id="rId34" xr:uid="{9101568E-31BC-4E76-BFD0-2D9246D72B59}"/>
+    <hyperlink ref="I213" r:id="rId35" xr:uid="{1511E45E-5783-4658-8753-7D092E83ED9F}"/>
+    <hyperlink ref="I214" r:id="rId36" xr:uid="{623401C5-1CA9-4BC6-BD97-6098055B1161}"/>
+    <hyperlink ref="I215" r:id="rId37" xr:uid="{DCA65EC2-9C5E-403C-99F4-C16115A19A0F}"/>
+    <hyperlink ref="I216" r:id="rId38" xr:uid="{851C36C9-DA0E-4516-BE09-4AE21199CA9C}"/>
+    <hyperlink ref="I217" r:id="rId39" xr:uid="{0DFD2DF2-3067-4C3F-BEA6-74A39ED24C6C}"/>
+    <hyperlink ref="I218" r:id="rId40" xr:uid="{2B5E58DD-9B4B-47A7-8246-526DE0882DAB}"/>
+    <hyperlink ref="I219" r:id="rId41" xr:uid="{B403E6A4-A5E6-48A7-99C3-306F5214F239}"/>
+    <hyperlink ref="I220" r:id="rId42" xr:uid="{1A5D3CE4-752C-4CC3-95C1-C57D48E76D67}"/>
+    <hyperlink ref="I221" r:id="rId43" xr:uid="{B540376A-C49A-4EBF-9766-730E3FA2B480}"/>
+    <hyperlink ref="I222" r:id="rId44" xr:uid="{DC6A0FDB-41EF-4F0A-AEC8-727FE2699271}"/>
+    <hyperlink ref="I223" r:id="rId45" xr:uid="{CC79311B-BFFC-4C45-9084-2E2D0DB1E82D}"/>
+    <hyperlink ref="I224" r:id="rId46" xr:uid="{4AB51D13-6804-4598-BA4D-14CA81EEDF11}"/>
+    <hyperlink ref="I225" r:id="rId47" xr:uid="{8F7CC7DC-0AE7-42EE-8BDF-A54E51F8992C}"/>
+    <hyperlink ref="I226" r:id="rId48" xr:uid="{7C0C6076-AA03-4868-94ED-2DD6908BB850}"/>
+    <hyperlink ref="I227" r:id="rId49" xr:uid="{107FDDA9-8EE8-4E8F-8C35-727EB9596C8C}"/>
+    <hyperlink ref="I228" r:id="rId50" xr:uid="{0602C523-22D1-4AF5-B267-B1F91E51660E}"/>
+    <hyperlink ref="I229" r:id="rId51" xr:uid="{4F7477C1-D496-486D-9F8B-90185A9B9116}"/>
+    <hyperlink ref="I230" r:id="rId52" xr:uid="{AE4F0648-1BF8-4CCF-91F9-D149225111D8}"/>
+    <hyperlink ref="I231" r:id="rId53" xr:uid="{6B91051B-D642-451D-8540-E3EF4B04B516}"/>
+    <hyperlink ref="I232" r:id="rId54" xr:uid="{EE2E8D6C-C5D3-41DC-823A-91710539DD02}"/>
+    <hyperlink ref="I233" r:id="rId55" xr:uid="{949C9C3E-ED06-422F-B1A2-6C8BCA0ABA0F}"/>
+    <hyperlink ref="I234" r:id="rId56" xr:uid="{AA4DBBC4-D25B-4FD2-9DFB-CEE3DC7C4E5D}"/>
+    <hyperlink ref="I235" r:id="rId57" xr:uid="{7F4AFDD4-1D85-4907-ADCD-DD724D3972B5}"/>
+    <hyperlink ref="I236" r:id="rId58" xr:uid="{C3F81D43-4417-4CED-BEE7-107F544F2F67}"/>
+    <hyperlink ref="I237" r:id="rId59" xr:uid="{0E431E78-B11E-4D3D-BF64-93A62B2535EA}"/>
+    <hyperlink ref="I238" r:id="rId60" xr:uid="{F3DC8952-CA94-44A7-9990-313DE68D15C0}"/>
+    <hyperlink ref="I239" r:id="rId61" xr:uid="{389000CC-5D17-4FAB-89A8-EF936DCADD39}"/>
+    <hyperlink ref="I240" r:id="rId62" xr:uid="{DF5056BD-5928-442C-8D36-786187962D4E}"/>
+    <hyperlink ref="I241" r:id="rId63" xr:uid="{B17DDC44-6464-4D49-9245-A5F642B065EA}"/>
+    <hyperlink ref="I242" r:id="rId64" xr:uid="{53DA76D3-2041-4CCC-BAC2-831126E5CCE6}"/>
+    <hyperlink ref="I243" r:id="rId65" xr:uid="{91201E4E-3324-484F-9415-E4FACA7F44E3}"/>
+    <hyperlink ref="I244" r:id="rId66" xr:uid="{94429747-15D6-4F6C-A6FB-6E72A3C13764}"/>
+    <hyperlink ref="I245" r:id="rId67" xr:uid="{C15B058E-1C23-4900-8C24-8D28310E1C2F}"/>
+    <hyperlink ref="I246" r:id="rId68" xr:uid="{B262EA6F-203C-45E9-89B2-791A69C07890}"/>
+    <hyperlink ref="I247" r:id="rId69" xr:uid="{CE01E355-305E-4165-8D9F-15F7FA60BFFE}"/>
+    <hyperlink ref="I248" r:id="rId70" xr:uid="{B558A969-5916-461F-B7DD-7BB172739229}"/>
+    <hyperlink ref="I249" r:id="rId71" xr:uid="{6C2C28C5-7E75-45F2-B014-AAB860E6AE0E}"/>
+    <hyperlink ref="I250" r:id="rId72" xr:uid="{1AD85C81-FFB5-417F-BA25-F1ED78B37431}"/>
+    <hyperlink ref="I251" r:id="rId73" xr:uid="{33A7E291-A210-4714-A7A4-99EE91E7B482}"/>
+    <hyperlink ref="I252" r:id="rId74" xr:uid="{5F8915D4-7E80-430E-BFE7-1ED4CE3CF33A}"/>
+    <hyperlink ref="I253" r:id="rId75" xr:uid="{FB50903D-66DB-4DF8-B592-D7A9E600B0E3}"/>
+    <hyperlink ref="I254" r:id="rId76" xr:uid="{744D1054-4487-4269-8A9E-786CDAAF3407}"/>
+    <hyperlink ref="I255" r:id="rId77" xr:uid="{16C2B0D8-8D7F-466F-AC5D-8425AFA169D9}"/>
+    <hyperlink ref="I256" r:id="rId78" xr:uid="{FA023894-E80B-4578-909B-459FF5CF4C63}"/>
+    <hyperlink ref="I257" r:id="rId79" xr:uid="{E5050E5E-DA5D-45D7-804E-28BE5DB4950C}"/>
+    <hyperlink ref="I258" r:id="rId80" xr:uid="{86E32D4F-C56E-411C-9FFA-F68B33BFB29B}"/>
+    <hyperlink ref="I259" r:id="rId81" xr:uid="{FC987404-74F4-43D6-A78F-4B76C6DB04D6}"/>
+    <hyperlink ref="I260" r:id="rId82" xr:uid="{2B21BE7E-722A-49A4-979D-3B59E25F3D6F}"/>
+    <hyperlink ref="I261" r:id="rId83" xr:uid="{D815703C-A341-4DBD-8917-8EF9F09099D9}"/>
+    <hyperlink ref="I262" r:id="rId84" xr:uid="{D488A61C-7936-4BD3-A5DC-711D84B1CB93}"/>
+    <hyperlink ref="I263" r:id="rId85" xr:uid="{6AE73540-FBFF-456B-AA13-FACDF198EEC7}"/>
+    <hyperlink ref="I264" r:id="rId86" xr:uid="{8C84A141-E54F-4B61-BBE9-CC4376BDB95C}"/>
+    <hyperlink ref="I265" r:id="rId87" xr:uid="{0D4B81F2-A5B4-4D11-B5C9-C6E4E1894805}"/>
+    <hyperlink ref="I266" r:id="rId88" xr:uid="{BE3BA77A-8592-47F6-9E47-2F5CD753016C}"/>
+    <hyperlink ref="I267" r:id="rId89" xr:uid="{34B33867-25D9-4C3D-8D9B-2F54F5579A74}"/>
+    <hyperlink ref="I268" r:id="rId90" xr:uid="{82FB132F-6DBB-4937-8DB2-6537E5A333C1}"/>
+    <hyperlink ref="I269" r:id="rId91" xr:uid="{48CF0644-5B6B-4971-AB15-595D305C86C4}"/>
+    <hyperlink ref="I270" r:id="rId92" xr:uid="{12B4549D-78ED-4156-A808-89A90E705C41}"/>
+    <hyperlink ref="I271" r:id="rId93" xr:uid="{4B34BD40-90A3-4980-BF65-504727C2F416}"/>
+    <hyperlink ref="I272" r:id="rId94" xr:uid="{DA8E8284-C693-4333-AB17-29316BE13318}"/>
+    <hyperlink ref="I273" r:id="rId95" xr:uid="{80DE8E4C-5F58-404C-ACDA-DBD1A7F6A1D8}"/>
+    <hyperlink ref="I274" r:id="rId96" xr:uid="{6DC5C96A-F9CA-42BC-A49B-B1D78CB012C9}"/>
+    <hyperlink ref="I275" r:id="rId97" xr:uid="{76A269FE-ABD2-4F22-A51B-4B135173877B}"/>
+    <hyperlink ref="I276" r:id="rId98" xr:uid="{4B26D222-9CA0-4147-BD85-71FAAA2E8631}"/>
+    <hyperlink ref="I277" r:id="rId99" xr:uid="{891AE600-7F18-4A61-BFCE-F7AB9A5AD2F9}"/>
+    <hyperlink ref="I278" r:id="rId100" xr:uid="{37B3244C-D291-4BA3-BB4E-8336AA957A94}"/>
+    <hyperlink ref="I279" r:id="rId101" xr:uid="{8B680038-2757-46CE-9B33-E6D388D28185}"/>
+    <hyperlink ref="I280" r:id="rId102" xr:uid="{7E71DA76-5C9F-4325-8C94-D6E0812E8639}"/>
+    <hyperlink ref="I281" r:id="rId103" xr:uid="{29AA0BD4-96B3-4978-88C3-ECE774585015}"/>
+    <hyperlink ref="I282" r:id="rId104" xr:uid="{FB9F1E00-700C-4AEB-AB17-AE66C6AD67CC}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId105"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId106"/>
   </tableParts>
 </worksheet>
 </file>